--- a/VerveStacks_NZL_grids/vt_vervestacks_NZL_v1.xlsx
+++ b/VerveStacks_NZL_grids/vt_vervestacks_NZL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6674EA9A-A4BF-4D46-AF3F-0569672462A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FDE875F3-8EA3-4F5A-BA5A-F88BA3761DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5AD920FB-13A8-4C7A-80CA-2CC5902E8BA9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8C80F1A2-CCE3-4879-AB5E-9D87F6C2EFC7}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -108,12 +108,12 @@
     <t>gas</t>
   </si>
   <si>
+    <t>e_w188180344-220</t>
+  </si>
+  <si>
     <t>e_r17609399-220</t>
   </si>
   <si>
-    <t>e_w188180344-220</t>
-  </si>
-  <si>
     <t>ep_gas_combined_cycle_G100000407351</t>
   </si>
   <si>
@@ -276,60 +276,60 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_w412589726-220</t>
+  </si>
+  <si>
+    <t>e_w89637173-220</t>
+  </si>
+  <si>
     <t>e_NZ30-220</t>
   </si>
   <si>
+    <t>e_w93556808-220</t>
+  </si>
+  <si>
+    <t>e_NZ40-220</t>
+  </si>
+  <si>
+    <t>e_NZ33-220</t>
+  </si>
+  <si>
+    <t>e_NZ13-220</t>
+  </si>
+  <si>
+    <t>e_w270018358-220</t>
+  </si>
+  <si>
+    <t>e_w89637174-220</t>
+  </si>
+  <si>
+    <t>e_w89636266-220</t>
+  </si>
+  <si>
+    <t>e_w272522517-220</t>
+  </si>
+  <si>
+    <t>e_NZ14-220</t>
+  </si>
+  <si>
+    <t>e_NZ12-220</t>
+  </si>
+  <si>
+    <t>e_NZ35-220</t>
+  </si>
+  <si>
+    <t>e_NZ11-220</t>
+  </si>
+  <si>
     <t>e_w89664063-220</t>
   </si>
   <si>
     <t>e_w180514007-220</t>
   </si>
   <si>
-    <t>e_w89637173-220</t>
-  </si>
-  <si>
     <t>e_w89411122-220</t>
   </si>
   <si>
-    <t>e_w89637174-220</t>
-  </si>
-  <si>
-    <t>e_w89636266-220</t>
-  </si>
-  <si>
-    <t>e_w272522517-220</t>
-  </si>
-  <si>
-    <t>e_NZ14-220</t>
-  </si>
-  <si>
-    <t>e_NZ12-220</t>
-  </si>
-  <si>
-    <t>e_w412589726-220</t>
-  </si>
-  <si>
-    <t>e_NZ40-220</t>
-  </si>
-  <si>
-    <t>e_NZ35-220</t>
-  </si>
-  <si>
-    <t>e_NZ11-220</t>
-  </si>
-  <si>
-    <t>e_NZ33-220</t>
-  </si>
-  <si>
-    <t>e_NZ13-220</t>
-  </si>
-  <si>
-    <t>e_w270018358-220</t>
-  </si>
-  <si>
-    <t>e_w93556808-220</t>
-  </si>
-  <si>
     <t>e_NZ22-220</t>
   </si>
   <si>
@@ -1260,15 +1260,15 @@
     <t>Huntly power station_4</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/188180344-220_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - relation/17609399-220_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/167293888-220_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/188180344-220_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Stratford power station_CC1</t>
   </si>
   <si>
@@ -1386,66 +1386,66 @@
     <t>Wairakei geothermal power plant_A</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/87928925-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/93556808-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ30-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89637173-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/272522517-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ33-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ22-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89636266-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/180514007-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ35-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ14-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/270018358-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - NZ35-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - NZ40-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - NZ14-220_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - way/89637174-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ13-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ11-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89411122-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89664063-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/412589726-220_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - NZ12-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/89664063-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/412589726-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89411122-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89636266-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/180514007-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ11-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ22-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ33-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/272522517-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ30-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ13-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89637173-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/87928925-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/93556808-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89637174-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Arapuni hydroelectric plant_</t>
   </si>
   <si>
@@ -1629,13 +1629,13 @@
     <t>ccs retrofit of -- Glenbrook power station_1</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/188180344-220_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/167293888-220_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - relation/17609399-220_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/188180344-220_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- McKee power station_2</t>
@@ -2027,7 +2027,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACDFDFF3-DCBA-46E0-8A85-EEAF82E9CD6C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CF9CCC1-E9AA-47AD-A464-AD88D77FFF47}">
   <dimension ref="B9:T38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2271,7 +2271,7 @@
         <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E14">
         <v>0.45937499999999998</v>
@@ -2327,7 +2327,7 @@
         <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E15">
         <v>0.4375</v>
@@ -2439,7 +2439,7 @@
         <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E17">
         <v>0.37624999999999997</v>
@@ -2663,7 +2663,7 @@
         <v>22</v>
       </c>
       <c r="D21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E21">
         <v>0.26250000000000001</v>
@@ -2719,7 +2719,7 @@
         <v>22</v>
       </c>
       <c r="D22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E22">
         <v>0.26250000000000001</v>
@@ -2775,7 +2775,7 @@
         <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E23">
         <v>0.27124999999999999</v>
@@ -2831,7 +2831,7 @@
         <v>22</v>
       </c>
       <c r="D24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E24">
         <v>0.27124999999999999</v>
@@ -2887,7 +2887,7 @@
         <v>22</v>
       </c>
       <c r="D25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E25">
         <v>0.26250000000000001</v>
@@ -2943,7 +2943,7 @@
         <v>22</v>
       </c>
       <c r="D26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E26">
         <v>0.26250000000000001</v>
@@ -3055,7 +3055,7 @@
         <v>126</v>
       </c>
       <c r="D28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E28">
         <v>0.4375</v>
@@ -3111,7 +3111,7 @@
         <v>126</v>
       </c>
       <c r="D29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E29">
         <v>0.42</v>
@@ -3223,7 +3223,7 @@
         <v>126</v>
       </c>
       <c r="D31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E31">
         <v>0.35875000000000001</v>
@@ -3279,7 +3279,7 @@
         <v>126</v>
       </c>
       <c r="D32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E32">
         <v>0.25374999999999998</v>
@@ -3335,7 +3335,7 @@
         <v>126</v>
       </c>
       <c r="D33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E33">
         <v>0.25374999999999998</v>
@@ -3391,7 +3391,7 @@
         <v>126</v>
       </c>
       <c r="D34" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E34">
         <v>0.26250000000000001</v>
@@ -3447,7 +3447,7 @@
         <v>126</v>
       </c>
       <c r="D35" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E35">
         <v>0.26250000000000001</v>
@@ -3503,7 +3503,7 @@
         <v>126</v>
       </c>
       <c r="D36" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E36">
         <v>0.25374999999999998</v>
@@ -3559,7 +3559,7 @@
         <v>126</v>
       </c>
       <c r="D37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E37">
         <v>0.25374999999999998</v>
@@ -3669,7 +3669,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA749AB7-9544-4C07-9F79-C2ED3A79F597}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01616D9F-B003-4136-9A23-7A954210F967}">
   <dimension ref="B9:T260"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4016,19 +4016,19 @@
         <v>2022</v>
       </c>
       <c r="F16">
-        <v>0.29931763879128592</v>
+        <v>3.9117357695010534E-2</v>
       </c>
       <c r="G16">
-        <v>0.57999999999999996</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H16">
-        <v>1150</v>
+        <v>1350</v>
       </c>
       <c r="I16">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J16">
-        <v>3.3000000000000003</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="K16">
         <v>50</v>
@@ -4069,19 +4069,19 @@
         <v>2022</v>
       </c>
       <c r="F17">
-        <v>3.9117357695010534E-2</v>
+        <v>0.29931763879128592</v>
       </c>
       <c r="G17">
-        <v>0.56000000000000005</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H17">
-        <v>1350</v>
+        <v>1150</v>
       </c>
       <c r="I17">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="J17">
-        <v>3.5999999999999996</v>
+        <v>3.3000000000000003</v>
       </c>
       <c r="K17">
         <v>50</v>
@@ -4169,7 +4169,7 @@
         <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E19">
         <v>1998</v>
@@ -4222,7 +4222,7 @@
         <v>22</v>
       </c>
       <c r="D20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E20">
         <v>1996</v>
@@ -4328,7 +4328,7 @@
         <v>22</v>
       </c>
       <c r="D22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E22">
         <v>1987</v>
@@ -4381,7 +4381,7 @@
         <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E23">
         <v>2013</v>
@@ -4434,7 +4434,7 @@
         <v>22</v>
       </c>
       <c r="D24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E24">
         <v>2013</v>
@@ -4487,7 +4487,7 @@
         <v>22</v>
       </c>
       <c r="D25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E25">
         <v>2011</v>
@@ -4540,7 +4540,7 @@
         <v>22</v>
       </c>
       <c r="D26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E26">
         <v>2011</v>
@@ -4593,7 +4593,7 @@
         <v>22</v>
       </c>
       <c r="D27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E27">
         <v>2020</v>
@@ -4646,7 +4646,7 @@
         <v>22</v>
       </c>
       <c r="D28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E28">
         <v>2020</v>
@@ -6401,19 +6401,19 @@
         <v>2022</v>
       </c>
       <c r="F61">
-        <v>2.6458760771440295E-2</v>
+        <v>0.16073697168649981</v>
       </c>
       <c r="G61">
         <v>1</v>
       </c>
       <c r="H61">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I61">
-        <v>65</v>
+        <v>55.000000000000014</v>
       </c>
       <c r="J61">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K61">
         <v>100</v>
@@ -6454,19 +6454,19 @@
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>8.9298317603610997E-2</v>
+        <v>1.7363561756257695E-2</v>
       </c>
       <c r="G62">
         <v>1</v>
       </c>
       <c r="H62">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I62">
-        <v>55.000000000000014</v>
+        <v>65</v>
       </c>
       <c r="J62">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K62">
         <v>100</v>
@@ -6507,19 +6507,19 @@
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>5.291752154288059E-2</v>
+        <v>2.6458760771440295E-2</v>
       </c>
       <c r="G63">
         <v>1</v>
       </c>
       <c r="H63">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I63">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="J63">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K63">
         <v>100</v>
@@ -6554,25 +6554,25 @@
         <v>78</v>
       </c>
       <c r="D64" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="E64">
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>1.7363561756257695E-2</v>
+        <v>5.8209273697168655E-2</v>
       </c>
       <c r="G64">
         <v>1</v>
       </c>
       <c r="H64">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I64">
-        <v>65</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J64">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K64">
         <v>100</v>
@@ -6607,13 +6607,13 @@
         <v>78</v>
       </c>
       <c r="D65" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E65">
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>3.9688141157160448E-2</v>
+        <v>1.2237176856791137E-2</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -6660,25 +6660,25 @@
         <v>78</v>
       </c>
       <c r="D66" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E66">
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>3.6380796060730414E-2</v>
+        <v>7.1438654082888797E-2</v>
       </c>
       <c r="G66">
         <v>1</v>
       </c>
       <c r="H66">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I66">
-        <v>65</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J66">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K66">
         <v>100</v>
@@ -6713,13 +6713,13 @@
         <v>78</v>
       </c>
       <c r="D67" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E67">
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>3.5057858022158397E-2</v>
+        <v>4.365695527287649E-2</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -6766,13 +6766,13 @@
         <v>78</v>
       </c>
       <c r="D68" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E68">
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>1.7528929011079199E-2</v>
+        <v>1.3229380385720147E-2</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -6819,19 +6819,19 @@
         <v>78</v>
       </c>
       <c r="D69" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E69">
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>2.1001641362330736E-2</v>
+        <v>1.2898645876077145E-2</v>
       </c>
       <c r="G69">
         <v>1</v>
       </c>
       <c r="H69">
-        <v>3375</v>
+        <v>3375.0000000000005</v>
       </c>
       <c r="I69">
         <v>65</v>
@@ -6872,13 +6872,13 @@
         <v>78</v>
       </c>
       <c r="D70" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E70">
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>2.7120229790726307E-2</v>
+        <v>3.6380796060730414E-2</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -6890,7 +6890,7 @@
         <v>65</v>
       </c>
       <c r="J70">
-        <v>2.3999999999999995</v>
+        <v>2.4</v>
       </c>
       <c r="K70">
         <v>100</v>
@@ -6925,25 +6925,25 @@
         <v>78</v>
       </c>
       <c r="D71" t="s">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="E71">
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>5.8209273697168655E-2</v>
+        <v>3.5057858022158397E-2</v>
       </c>
       <c r="G71">
         <v>1</v>
       </c>
       <c r="H71">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I71">
-        <v>55.000000000000007</v>
+        <v>65</v>
       </c>
       <c r="J71">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K71">
         <v>100</v>
@@ -6984,19 +6984,19 @@
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>0.16073697168649981</v>
+        <v>1.7528929011079199E-2</v>
       </c>
       <c r="G72">
         <v>1</v>
       </c>
       <c r="H72">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I72">
-        <v>55.000000000000014</v>
+        <v>65</v>
       </c>
       <c r="J72">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K72">
         <v>100</v>
@@ -7037,19 +7037,19 @@
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>7.1438654082888797E-2</v>
+        <v>2.1001641362330736E-2</v>
       </c>
       <c r="G73">
         <v>1</v>
       </c>
       <c r="H73">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I73">
-        <v>55.000000000000007</v>
+        <v>65</v>
       </c>
       <c r="J73">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K73">
         <v>100</v>
@@ -7090,7 +7090,7 @@
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>3.5057858022158397E-2</v>
+        <v>2.7120229790726307E-2</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -7102,7 +7102,7 @@
         <v>65</v>
       </c>
       <c r="J74">
-        <v>2.4</v>
+        <v>2.3999999999999995</v>
       </c>
       <c r="K74">
         <v>100</v>
@@ -7143,7 +7143,7 @@
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>1.5875256462864178E-2</v>
+        <v>3.5057858022158397E-2</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -7196,7 +7196,7 @@
         <v>2022</v>
       </c>
       <c r="F76">
-        <v>4.365695527287649E-2</v>
+        <v>1.5875256462864178E-2</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -7249,19 +7249,19 @@
         <v>2022</v>
       </c>
       <c r="F77">
-        <v>1.3229380385720147E-2</v>
+        <v>8.9298317603610997E-2</v>
       </c>
       <c r="G77">
         <v>1</v>
       </c>
       <c r="H77">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I77">
-        <v>65</v>
+        <v>55.000000000000014</v>
       </c>
       <c r="J77">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K77">
         <v>100</v>
@@ -7302,19 +7302,19 @@
         <v>2022</v>
       </c>
       <c r="F78">
-        <v>1.2898645876077145E-2</v>
+        <v>5.291752154288059E-2</v>
       </c>
       <c r="G78">
         <v>1</v>
       </c>
       <c r="H78">
-        <v>3375.0000000000005</v>
+        <v>2875</v>
       </c>
       <c r="I78">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J78">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K78">
         <v>100</v>
@@ -7355,7 +7355,7 @@
         <v>2022</v>
       </c>
       <c r="F79">
-        <v>1.2237176856791137E-2</v>
+        <v>3.9688141157160448E-2</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -7455,7 +7455,7 @@
         <v>78</v>
       </c>
       <c r="D81" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E81">
         <v>1929</v>
@@ -7508,7 +7508,7 @@
         <v>78</v>
       </c>
       <c r="D82" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E82">
         <v>1968</v>
@@ -7561,7 +7561,7 @@
         <v>78</v>
       </c>
       <c r="D83" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="E83">
         <v>1965</v>
@@ -7614,7 +7614,7 @@
         <v>78</v>
       </c>
       <c r="D84" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E84">
         <v>1992</v>
@@ -7667,7 +7667,7 @@
         <v>78</v>
       </c>
       <c r="D85" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E85">
         <v>1948</v>
@@ -7720,7 +7720,7 @@
         <v>78</v>
       </c>
       <c r="D86" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="E86">
         <v>1972</v>
@@ -7879,7 +7879,7 @@
         <v>78</v>
       </c>
       <c r="D89" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E89">
         <v>1961</v>
@@ -7932,7 +7932,7 @@
         <v>78</v>
       </c>
       <c r="D90" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E90">
         <v>1979</v>
@@ -7985,7 +7985,7 @@
         <v>78</v>
       </c>
       <c r="D91" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E91">
         <v>1984</v>
@@ -8038,7 +8038,7 @@
         <v>78</v>
       </c>
       <c r="D92" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E92">
         <v>1985</v>
@@ -8144,7 +8144,7 @@
         <v>78</v>
       </c>
       <c r="D94" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="E94">
         <v>1956</v>
@@ -8197,7 +8197,7 @@
         <v>78</v>
       </c>
       <c r="D95" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E95">
         <v>1977</v>
@@ -8250,7 +8250,7 @@
         <v>78</v>
       </c>
       <c r="D96" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="E96">
         <v>1973</v>
@@ -8303,7 +8303,7 @@
         <v>78</v>
       </c>
       <c r="D97" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E97">
         <v>1935</v>
@@ -8356,7 +8356,7 @@
         <v>78</v>
       </c>
       <c r="D98" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E98">
         <v>1956</v>
@@ -8409,7 +8409,7 @@
         <v>78</v>
       </c>
       <c r="D99" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="E99">
         <v>1967</v>
@@ -8462,7 +8462,7 @@
         <v>78</v>
       </c>
       <c r="D100" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="E100">
         <v>1958</v>
@@ -8621,7 +8621,7 @@
         <v>78</v>
       </c>
       <c r="D103" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E103">
         <v>1964</v>
@@ -8727,7 +8727,7 @@
         <v>126</v>
       </c>
       <c r="D105" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E105">
         <v>1998</v>
@@ -8780,7 +8780,7 @@
         <v>126</v>
       </c>
       <c r="D106" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E106">
         <v>1996</v>
@@ -8886,7 +8886,7 @@
         <v>126</v>
       </c>
       <c r="D108" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E108">
         <v>1987</v>
@@ -8939,7 +8939,7 @@
         <v>126</v>
       </c>
       <c r="D109" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E109">
         <v>2013</v>
@@ -8992,7 +8992,7 @@
         <v>126</v>
       </c>
       <c r="D110" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E110">
         <v>2013</v>
@@ -9045,7 +9045,7 @@
         <v>126</v>
       </c>
       <c r="D111" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E111">
         <v>2011</v>
@@ -9098,7 +9098,7 @@
         <v>126</v>
       </c>
       <c r="D112" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E112">
         <v>2011</v>
@@ -9151,7 +9151,7 @@
         <v>126</v>
       </c>
       <c r="D113" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E113">
         <v>2020</v>
@@ -9204,7 +9204,7 @@
         <v>126</v>
       </c>
       <c r="D114" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E114">
         <v>2020</v>
@@ -9316,7 +9316,7 @@
         <v>2022</v>
       </c>
       <c r="F116">
-        <v>1.5885190741534269E-3</v>
+        <v>1.5594957372591779E-3</v>
       </c>
       <c r="G116">
         <v>1</v>
@@ -9369,7 +9369,7 @@
         <v>2022</v>
       </c>
       <c r="F117">
-        <v>1.4842334709048478E-3</v>
+        <v>1.5957719531620534E-3</v>
       </c>
       <c r="G117">
         <v>1</v>
@@ -9422,7 +9422,7 @@
         <v>2022</v>
       </c>
       <c r="F118">
-        <v>1.3716498094399824E-3</v>
+        <v>1.681394643094816E-3</v>
       </c>
       <c r="G118">
         <v>1</v>
@@ -9431,7 +9431,7 @@
         <v>1215</v>
       </c>
       <c r="I118">
-        <v>19.5</v>
+        <v>19.499999999999996</v>
       </c>
       <c r="J118">
         <v>0</v>
@@ -9475,7 +9475,7 @@
         <v>2022</v>
       </c>
       <c r="F119">
-        <v>1.5512837432562687E-3</v>
+        <v>1.7514545590869789E-3</v>
       </c>
       <c r="G119">
         <v>1</v>
@@ -9528,7 +9528,7 @@
         <v>2022</v>
       </c>
       <c r="F120">
-        <v>2.2693848377204743E-3</v>
+        <v>2.0310594497185081E-3</v>
       </c>
       <c r="G120">
         <v>1</v>
@@ -9581,7 +9581,7 @@
         <v>2022</v>
       </c>
       <c r="F121">
-        <v>2.2544648114030861E-3</v>
+        <v>1.9041908874837391E-3</v>
       </c>
       <c r="G121">
         <v>1</v>
@@ -9634,7 +9634,7 @@
         <v>2022</v>
       </c>
       <c r="F122">
-        <v>2.0236833970682811E-3</v>
+        <v>1.7398893564716364E-3</v>
       </c>
       <c r="G122">
         <v>1</v>
@@ -9687,7 +9687,7 @@
         <v>2022</v>
       </c>
       <c r="F123">
-        <v>1.5123889334649886E-3</v>
+        <v>1.7328765534627693E-3</v>
       </c>
       <c r="G123">
         <v>1</v>
@@ -9740,7 +9740,7 @@
         <v>2022</v>
       </c>
       <c r="F124">
-        <v>2.1818796086266641E-3</v>
+        <v>2.0677662800078901E-3</v>
       </c>
       <c r="G124">
         <v>1</v>
@@ -9793,7 +9793,7 @@
         <v>2022</v>
       </c>
       <c r="F125">
-        <v>2.7044131701924336E-3</v>
+        <v>2.5552613877918469E-3</v>
       </c>
       <c r="G125">
         <v>1</v>
@@ -9846,7 +9846,7 @@
         <v>2022</v>
       </c>
       <c r="F126">
-        <v>2.4852305690178998E-3</v>
+        <v>2.2765004535102332E-3</v>
       </c>
       <c r="G126">
         <v>1</v>
@@ -9899,7 +9899,7 @@
         <v>2022</v>
       </c>
       <c r="F127">
-        <v>2.0249235860943641E-3</v>
+        <v>1.8303053054035986E-3</v>
       </c>
       <c r="G127">
         <v>1</v>
@@ -9952,7 +9952,7 @@
         <v>2022</v>
       </c>
       <c r="F128">
-        <v>2.0600443575713172E-3</v>
+        <v>1.8540947890351312E-3</v>
       </c>
       <c r="G128">
         <v>1</v>
@@ -10005,7 +10005,7 @@
         <v>2022</v>
       </c>
       <c r="F129">
-        <v>1.774216949104055E-3</v>
+        <v>1.8798253248958501E-3</v>
       </c>
       <c r="G129">
         <v>1</v>
@@ -10058,7 +10058,7 @@
         <v>2022</v>
       </c>
       <c r="F130">
-        <v>1.9925610351992154E-3</v>
+        <v>1.9827927176308963E-3</v>
       </c>
       <c r="G130">
         <v>1</v>
@@ -10111,7 +10111,7 @@
         <v>2022</v>
       </c>
       <c r="F131">
-        <v>2.7278809318591209E-3</v>
+        <v>2.5664336225679463E-3</v>
       </c>
       <c r="G131">
         <v>1</v>
@@ -10164,7 +10164,7 @@
         <v>2022</v>
       </c>
       <c r="F132">
-        <v>2.4659340609589232E-3</v>
+        <v>2.3348433987815352E-3</v>
       </c>
       <c r="G132">
         <v>1</v>
@@ -10217,7 +10217,7 @@
         <v>2022</v>
       </c>
       <c r="F133">
-        <v>2.530985098026719E-3</v>
+        <v>2.2454422346914107E-3</v>
       </c>
       <c r="G133">
         <v>1</v>
@@ -10270,7 +10270,7 @@
         <v>2022</v>
       </c>
       <c r="F134">
-        <v>2.4554668052086852E-3</v>
+        <v>2.0552498945176603E-3</v>
       </c>
       <c r="G134">
         <v>1</v>
@@ -10323,7 +10323,7 @@
         <v>2022</v>
       </c>
       <c r="F135">
-        <v>1.9947657005585169E-3</v>
+        <v>1.8603396453688319E-3</v>
       </c>
       <c r="G135">
         <v>1</v>
@@ -10332,7 +10332,7 @@
         <v>1215</v>
       </c>
       <c r="I135">
-        <v>19.5</v>
+        <v>19.499999999999996</v>
       </c>
       <c r="J135">
         <v>0</v>
@@ -10376,7 +10376,7 @@
         <v>2022</v>
       </c>
       <c r="F136">
-        <v>1.8945456656385502E-3</v>
+        <v>1.860200282062236E-3</v>
       </c>
       <c r="G136">
         <v>1</v>
@@ -10429,7 +10429,7 @@
         <v>2022</v>
       </c>
       <c r="F137">
-        <v>2.4281447788871676E-3</v>
+        <v>2.3005250177346812E-3</v>
       </c>
       <c r="G137">
         <v>1</v>
@@ -10482,7 +10482,7 @@
         <v>2022</v>
       </c>
       <c r="F138">
-        <v>2.8524504854579393E-3</v>
+        <v>2.6863869603865236E-3</v>
       </c>
       <c r="G138">
         <v>1</v>
@@ -10535,7 +10535,7 @@
         <v>2022</v>
       </c>
       <c r="F139">
-        <v>3.1667569677538165E-3</v>
+        <v>2.9281151205194007E-3</v>
       </c>
       <c r="G139">
         <v>1</v>
@@ -10588,7 +10588,7 @@
         <v>2022</v>
       </c>
       <c r="F140">
-        <v>2.44262578369991E-3</v>
+        <v>2.220106924052642E-3</v>
       </c>
       <c r="G140">
         <v>1</v>
@@ -10641,7 +10641,7 @@
         <v>2022</v>
       </c>
       <c r="F141">
-        <v>2.4718217885910843E-3</v>
+        <v>2.1665947207049354E-3</v>
       </c>
       <c r="G141">
         <v>1</v>
@@ -10694,7 +10694,7 @@
         <v>2022</v>
       </c>
       <c r="F142">
-        <v>2.2637556041579725E-3</v>
+        <v>2.0226566696839757E-3</v>
       </c>
       <c r="G142">
         <v>1</v>
@@ -10747,7 +10747,7 @@
         <v>2022</v>
       </c>
       <c r="F143">
-        <v>1.9145745887652981E-3</v>
+        <v>1.9903131596404476E-3</v>
       </c>
       <c r="G143">
         <v>1</v>
@@ -10800,7 +10800,7 @@
         <v>2022</v>
       </c>
       <c r="F144">
-        <v>2.2074846441425852E-3</v>
+        <v>2.1061221957065193E-3</v>
       </c>
       <c r="G144">
         <v>1</v>
@@ -10853,7 +10853,7 @@
         <v>2022</v>
       </c>
       <c r="F145">
-        <v>2.4711207994807987E-3</v>
+        <v>2.3612580294868238E-3</v>
       </c>
       <c r="G145">
         <v>1</v>
@@ -10906,7 +10906,7 @@
         <v>2022</v>
       </c>
       <c r="F146">
-        <v>2.6046387839200758E-3</v>
+        <v>2.4787803522933944E-3</v>
       </c>
       <c r="G146">
         <v>1</v>
@@ -10959,7 +10959,7 @@
         <v>2022</v>
       </c>
       <c r="F147">
-        <v>2.5936926745881075E-3</v>
+        <v>2.4912957908206218E-3</v>
       </c>
       <c r="G147">
         <v>1</v>
@@ -11012,7 +11012,7 @@
         <v>2022</v>
       </c>
       <c r="F148">
-        <v>2.4838993681452234E-3</v>
+        <v>2.2698195162290232E-3</v>
       </c>
       <c r="G148">
         <v>1</v>
@@ -11065,7 +11065,7 @@
         <v>2022</v>
       </c>
       <c r="F149">
-        <v>2.0707549533727169E-3</v>
+        <v>2.0385740261075016E-3</v>
       </c>
       <c r="G149">
         <v>1</v>
@@ -11118,7 +11118,7 @@
         <v>2022</v>
       </c>
       <c r="F150">
-        <v>1.9859125049299427E-3</v>
+        <v>1.9090109152240446E-3</v>
       </c>
       <c r="G150">
         <v>1</v>
@@ -11171,7 +11171,7 @@
         <v>2022</v>
       </c>
       <c r="F151">
-        <v>2.5793338701155105E-3</v>
+        <v>2.5564551287844913E-3</v>
       </c>
       <c r="G151">
         <v>1</v>
@@ -11224,7 +11224,7 @@
         <v>2022</v>
       </c>
       <c r="F152">
-        <v>2.8718802542940887E-3</v>
+        <v>2.7893582707224666E-3</v>
       </c>
       <c r="G152">
         <v>1</v>
@@ -11277,7 +11277,7 @@
         <v>2022</v>
       </c>
       <c r="F153">
-        <v>2.3707396053639857E-3</v>
+        <v>2.1416653388888801E-3</v>
       </c>
       <c r="G153">
         <v>1</v>
@@ -11330,7 +11330,7 @@
         <v>2022</v>
       </c>
       <c r="F154">
-        <v>1.9153089982184553E-3</v>
+        <v>1.8758586598916292E-3</v>
       </c>
       <c r="G154">
         <v>1</v>
@@ -11383,7 +11383,7 @@
         <v>2022</v>
       </c>
       <c r="F155">
-        <v>2.0141511467131994E-3</v>
+        <v>1.9357360092067981E-3</v>
       </c>
       <c r="G155">
         <v>1</v>
@@ -11436,7 +11436,7 @@
         <v>2022</v>
       </c>
       <c r="F156">
-        <v>1.8708577635393607E-3</v>
+        <v>1.8758614406213397E-3</v>
       </c>
       <c r="G156">
         <v>1</v>
@@ -11489,7 +11489,7 @@
         <v>2022</v>
       </c>
       <c r="F157">
-        <v>2.5480959434889005E-3</v>
+        <v>2.4650060954418121E-3</v>
       </c>
       <c r="G157">
         <v>1</v>
@@ -11542,7 +11542,7 @@
         <v>2022</v>
       </c>
       <c r="F158">
-        <v>2.7772869736992674E-3</v>
+        <v>2.7226678357276613E-3</v>
       </c>
       <c r="G158">
         <v>1</v>
@@ -11595,7 +11595,7 @@
         <v>2022</v>
       </c>
       <c r="F159">
-        <v>2.2202945624507004E-3</v>
+        <v>2.0984107007753325E-3</v>
       </c>
       <c r="G159">
         <v>1</v>
@@ -11648,7 +11648,7 @@
         <v>2022</v>
       </c>
       <c r="F160">
-        <v>1.7903892989050074E-3</v>
+        <v>1.8341281889645992E-3</v>
       </c>
       <c r="G160">
         <v>1</v>
@@ -11701,7 +11701,7 @@
         <v>2022</v>
       </c>
       <c r="F161">
-        <v>1.9116566825634086E-3</v>
+        <v>1.8309459757071037E-3</v>
       </c>
       <c r="G161">
         <v>1</v>
@@ -11754,7 +11754,7 @@
         <v>2022</v>
       </c>
       <c r="F162">
-        <v>1.8780035624633422E-3</v>
+        <v>1.8376199578929925E-3</v>
       </c>
       <c r="G162">
         <v>1</v>
@@ -11807,7 +11807,7 @@
         <v>2022</v>
       </c>
       <c r="F163">
-        <v>1.9291600424171859E-3</v>
+        <v>1.9160625059826042E-3</v>
       </c>
       <c r="G163">
         <v>1</v>
@@ -11860,7 +11860,7 @@
         <v>2022</v>
       </c>
       <c r="F164">
-        <v>1.9694145195123212E-3</v>
+        <v>2.0536257105033145E-3</v>
       </c>
       <c r="G164">
         <v>1</v>
@@ -11913,7 +11913,7 @@
         <v>2022</v>
       </c>
       <c r="F165">
-        <v>2.093947909342842E-3</v>
+        <v>2.1385819143723457E-3</v>
       </c>
       <c r="G165">
         <v>1</v>
@@ -11966,7 +11966,7 @@
         <v>2022</v>
       </c>
       <c r="F166">
-        <v>2.5753853784428356E-3</v>
+        <v>2.5203766497826222E-3</v>
       </c>
       <c r="G166">
         <v>1</v>
@@ -12019,7 +12019,7 @@
         <v>2022</v>
       </c>
       <c r="F167">
-        <v>2.3293560675847987E-3</v>
+        <v>2.2320440636524322E-3</v>
       </c>
       <c r="G167">
         <v>1</v>
@@ -12072,7 +12072,7 @@
         <v>2022</v>
       </c>
       <c r="F168">
-        <v>2.2638871102582713E-3</v>
+        <v>2.072327572310558E-3</v>
       </c>
       <c r="G168">
         <v>1</v>
@@ -12125,7 +12125,7 @@
         <v>2022</v>
       </c>
       <c r="F169">
-        <v>2.2507953758564765E-3</v>
+        <v>2.0620424242298219E-3</v>
       </c>
       <c r="G169">
         <v>1</v>
@@ -12178,7 +12178,7 @@
         <v>2022</v>
       </c>
       <c r="F170">
-        <v>2.3043531514675896E-3</v>
+        <v>2.1104229139695613E-3</v>
       </c>
       <c r="G170">
         <v>1</v>
@@ -12231,7 +12231,7 @@
         <v>2022</v>
       </c>
       <c r="F171">
-        <v>2.2182894846053684E-3</v>
+        <v>2.2323451014424579E-3</v>
       </c>
       <c r="G171">
         <v>1</v>
@@ -12284,7 +12284,7 @@
         <v>2022</v>
       </c>
       <c r="F172">
-        <v>2.2705967195447659E-3</v>
+        <v>2.4035308511924525E-3</v>
       </c>
       <c r="G172">
         <v>1</v>
@@ -12337,7 +12337,7 @@
         <v>2022</v>
       </c>
       <c r="F173">
-        <v>2.2045009693460837E-3</v>
+        <v>2.4464438802649113E-3</v>
       </c>
       <c r="G173">
         <v>1</v>
@@ -12390,7 +12390,7 @@
         <v>2022</v>
       </c>
       <c r="F174">
-        <v>2.1055951040819818E-3</v>
+        <v>2.2156157991273726E-3</v>
       </c>
       <c r="G174">
         <v>1</v>
@@ -12443,7 +12443,7 @@
         <v>2022</v>
       </c>
       <c r="F175">
-        <v>2.235771362566372E-3</v>
+        <v>2.2301830787298752E-3</v>
       </c>
       <c r="G175">
         <v>1</v>
@@ -12496,7 +12496,7 @@
         <v>2022</v>
       </c>
       <c r="F176">
-        <v>2.3312943418224586E-3</v>
+        <v>2.2718138956868915E-3</v>
       </c>
       <c r="G176">
         <v>1</v>
@@ -12549,7 +12549,7 @@
         <v>2022</v>
       </c>
       <c r="F177">
-        <v>2.0823661195547055E-3</v>
+        <v>2.2557413889438918E-3</v>
       </c>
       <c r="G177">
         <v>1</v>
@@ -12602,7 +12602,7 @@
         <v>2022</v>
       </c>
       <c r="F178">
-        <v>2.2589617039782571E-3</v>
+        <v>2.4842060120240047E-3</v>
       </c>
       <c r="G178">
         <v>1</v>
@@ -12655,7 +12655,7 @@
         <v>2022</v>
       </c>
       <c r="F179">
-        <v>2.2250463262194773E-3</v>
+        <v>2.4040711687966115E-3</v>
       </c>
       <c r="G179">
         <v>1</v>
@@ -12708,7 +12708,7 @@
         <v>2022</v>
       </c>
       <c r="F180">
-        <v>2.3184547550243952E-3</v>
+        <v>2.525861288212979E-3</v>
       </c>
       <c r="G180">
         <v>1</v>
@@ -12761,7 +12761,7 @@
         <v>2022</v>
       </c>
       <c r="F181">
-        <v>2.1756232821675448E-3</v>
+        <v>2.3746765147195652E-3</v>
       </c>
       <c r="G181">
         <v>1</v>
@@ -12814,7 +12814,7 @@
         <v>2022</v>
       </c>
       <c r="F182">
-        <v>2.0252130946660884E-3</v>
+        <v>2.2415721103215295E-3</v>
       </c>
       <c r="G182">
         <v>1</v>
@@ -12867,7 +12867,7 @@
         <v>2022</v>
       </c>
       <c r="F183">
-        <v>2.219564513480851E-3</v>
+        <v>2.3780804078557781E-3</v>
       </c>
       <c r="G183">
         <v>1</v>
@@ -12920,7 +12920,7 @@
         <v>2022</v>
       </c>
       <c r="F184">
-        <v>2.6122834732360111E-3</v>
+        <v>2.813188037338034E-3</v>
       </c>
       <c r="G184">
         <v>1</v>
@@ -12973,7 +12973,7 @@
         <v>2022</v>
       </c>
       <c r="F185">
-        <v>2.1965993127470692E-3</v>
+        <v>2.3413356884818158E-3</v>
       </c>
       <c r="G185">
         <v>1</v>
@@ -13026,7 +13026,7 @@
         <v>2022</v>
       </c>
       <c r="F186">
-        <v>2.1733796208281641E-3</v>
+        <v>2.3359311024407033E-3</v>
       </c>
       <c r="G186">
         <v>1</v>
@@ -13079,7 +13079,7 @@
         <v>2022</v>
       </c>
       <c r="F187">
-        <v>2.2679742005729054E-3</v>
+        <v>2.4584555724253263E-3</v>
       </c>
       <c r="G187">
         <v>1</v>
@@ -13132,7 +13132,7 @@
         <v>2022</v>
       </c>
       <c r="F188">
-        <v>2.4382997630506991E-3</v>
+        <v>2.6253315584249333E-3</v>
       </c>
       <c r="G188">
         <v>1</v>
@@ -13185,7 +13185,7 @@
         <v>2022</v>
       </c>
       <c r="F189">
-        <v>2.3301066105100121E-3</v>
+        <v>2.5436915873137738E-3</v>
       </c>
       <c r="G189">
         <v>1</v>
@@ -13238,7 +13238,7 @@
         <v>2022</v>
       </c>
       <c r="F190">
-        <v>2.0637572433266174E-3</v>
+        <v>2.2940718436913581E-3</v>
       </c>
       <c r="G190">
         <v>1</v>
@@ -13291,7 +13291,7 @@
         <v>2022</v>
       </c>
       <c r="F191">
-        <v>1.9943370854654846E-3</v>
+        <v>2.2509040186737168E-3</v>
       </c>
       <c r="G191">
         <v>1</v>
@@ -13344,7 +13344,7 @@
         <v>2022</v>
       </c>
       <c r="F192">
-        <v>2.2909044110739456E-3</v>
+        <v>2.431479327541414E-3</v>
       </c>
       <c r="G192">
         <v>1</v>
@@ -13397,7 +13397,7 @@
         <v>2022</v>
       </c>
       <c r="F193">
-        <v>2.2117680361611949E-3</v>
+        <v>2.3657873773726087E-3</v>
       </c>
       <c r="G193">
         <v>1</v>
@@ -13450,7 +13450,7 @@
         <v>2022</v>
       </c>
       <c r="F194">
-        <v>2.4830218370322683E-3</v>
+        <v>2.5199206482932244E-3</v>
       </c>
       <c r="G194">
         <v>1</v>
@@ -13503,7 +13503,7 @@
         <v>2022</v>
       </c>
       <c r="F195">
-        <v>2.4140397308667081E-3</v>
+        <v>2.4995093008198534E-3</v>
       </c>
       <c r="G195">
         <v>1</v>
@@ -13556,7 +13556,7 @@
         <v>2022</v>
       </c>
       <c r="F196">
-        <v>2.1662000711733078E-3</v>
+        <v>2.2344210301252164E-3</v>
       </c>
       <c r="G196">
         <v>1</v>
@@ -13609,7 +13609,7 @@
         <v>2022</v>
       </c>
       <c r="F197">
-        <v>2.3975464891235697E-3</v>
+        <v>2.4870539536296166E-3</v>
       </c>
       <c r="G197">
         <v>1</v>
@@ -13662,7 +13662,7 @@
         <v>2022</v>
       </c>
       <c r="F198">
-        <v>2.6170468434313812E-3</v>
+        <v>2.7062981548627023E-3</v>
       </c>
       <c r="G198">
         <v>1</v>
@@ -13715,7 +13715,7 @@
         <v>2022</v>
       </c>
       <c r="F199">
-        <v>2.8351849790278051E-3</v>
+        <v>2.8905436975062314E-3</v>
       </c>
       <c r="G199">
         <v>1</v>
@@ -13768,7 +13768,7 @@
         <v>2022</v>
       </c>
       <c r="F200">
-        <v>2.879761649882664E-3</v>
+        <v>2.9887523839473885E-3</v>
       </c>
       <c r="G200">
         <v>1</v>
@@ -13821,7 +13821,7 @@
         <v>2022</v>
       </c>
       <c r="F201">
-        <v>2.4807056939965305E-3</v>
+        <v>2.6533934435110994E-3</v>
       </c>
       <c r="G201">
         <v>1</v>
@@ -13874,7 +13874,7 @@
         <v>2022</v>
       </c>
       <c r="F202">
-        <v>2.0756164981612663E-3</v>
+        <v>2.2407479819659447E-3</v>
       </c>
       <c r="G202">
         <v>1</v>
@@ -13927,7 +13927,7 @@
         <v>2022</v>
       </c>
       <c r="F203">
-        <v>2.0810201550655427E-3</v>
+        <v>2.3009472260699612E-3</v>
       </c>
       <c r="G203">
         <v>1</v>
@@ -13980,7 +13980,7 @@
         <v>2022</v>
       </c>
       <c r="F204">
-        <v>2.4474591713329243E-3</v>
+        <v>2.5637833040290316E-3</v>
       </c>
       <c r="G204">
         <v>1</v>
@@ -14033,7 +14033,7 @@
         <v>2022</v>
       </c>
       <c r="F205">
-        <v>2.5051966390715343E-3</v>
+        <v>2.6875058862397263E-3</v>
       </c>
       <c r="G205">
         <v>1</v>
@@ -14086,7 +14086,7 @@
         <v>2022</v>
       </c>
       <c r="F206">
-        <v>2.6354570484113317E-3</v>
+        <v>2.8027760986865731E-3</v>
       </c>
       <c r="G206">
         <v>1</v>
@@ -14139,7 +14139,7 @@
         <v>2022</v>
       </c>
       <c r="F207">
-        <v>2.5977107686666191E-3</v>
+        <v>2.7170134953954941E-3</v>
       </c>
       <c r="G207">
         <v>1</v>
@@ -14192,7 +14192,7 @@
         <v>2022</v>
       </c>
       <c r="F208">
-        <v>2.3109610555220443E-3</v>
+        <v>2.3405057595990114E-3</v>
       </c>
       <c r="G208">
         <v>1</v>
@@ -14245,7 +14245,7 @@
         <v>2022</v>
       </c>
       <c r="F209">
-        <v>2.247812038324473E-3</v>
+        <v>2.221655342354076E-3</v>
       </c>
       <c r="G209">
         <v>1</v>
@@ -14298,7 +14298,7 @@
         <v>2022</v>
       </c>
       <c r="F210">
-        <v>2.5782273564128179E-3</v>
+        <v>2.6140637340113619E-3</v>
       </c>
       <c r="G210">
         <v>1</v>
@@ -14351,7 +14351,7 @@
         <v>2022</v>
       </c>
       <c r="F211">
-        <v>2.6440803038705715E-3</v>
+        <v>2.7643217486408721E-3</v>
       </c>
       <c r="G211">
         <v>1</v>
@@ -14404,7 +14404,7 @@
         <v>2022</v>
       </c>
       <c r="F212">
-        <v>2.4809773488945193E-3</v>
+        <v>2.660981388862334E-3</v>
       </c>
       <c r="G212">
         <v>1</v>
@@ -14457,7 +14457,7 @@
         <v>2022</v>
       </c>
       <c r="F213">
-        <v>2.0820564025004419E-3</v>
+        <v>2.3400547095720776E-3</v>
       </c>
       <c r="G213">
         <v>1</v>
@@ -14510,7 +14510,7 @@
         <v>2022</v>
       </c>
       <c r="F214">
-        <v>2.0477876365972668E-3</v>
+        <v>2.3084130794320712E-3</v>
       </c>
       <c r="G214">
         <v>1</v>
@@ -14563,7 +14563,7 @@
         <v>2022</v>
       </c>
       <c r="F215">
-        <v>2.5854316255178576E-3</v>
+        <v>2.7285052414141838E-3</v>
       </c>
       <c r="G215">
         <v>1</v>
@@ -14616,7 +14616,7 @@
         <v>2022</v>
       </c>
       <c r="F216">
-        <v>2.8920624725364634E-3</v>
+        <v>2.9730689862630783E-3</v>
       </c>
       <c r="G216">
         <v>1</v>
@@ -14669,7 +14669,7 @@
         <v>2022</v>
       </c>
       <c r="F217">
-        <v>2.4599832522575237E-3</v>
+        <v>2.4611957808079502E-3</v>
       </c>
       <c r="G217">
         <v>1</v>
@@ -14722,7 +14722,7 @@
         <v>2022</v>
       </c>
       <c r="F218">
-        <v>2.1657634774691708E-3</v>
+        <v>2.1862941780759204E-3</v>
       </c>
       <c r="G218">
         <v>1</v>
@@ -14775,7 +14775,7 @@
         <v>2022</v>
       </c>
       <c r="F219">
-        <v>2.383012156961723E-3</v>
+        <v>2.4267926458767467E-3</v>
       </c>
       <c r="G219">
         <v>1</v>
@@ -14828,7 +14828,7 @@
         <v>2022</v>
       </c>
       <c r="F220">
-        <v>2.5259420565437434E-3</v>
+        <v>2.593308961064827E-3</v>
       </c>
       <c r="G220">
         <v>1</v>
@@ -14881,7 +14881,7 @@
         <v>2022</v>
       </c>
       <c r="F221">
-        <v>2.3621420929912031E-3</v>
+        <v>2.3868129825653653E-3</v>
       </c>
       <c r="G221">
         <v>1</v>
@@ -14934,7 +14934,7 @@
         <v>2022</v>
       </c>
       <c r="F222">
-        <v>2.1901120002067215E-3</v>
+        <v>2.2420664820873635E-3</v>
       </c>
       <c r="G222">
         <v>1</v>
@@ -14987,7 +14987,7 @@
         <v>2022</v>
       </c>
       <c r="F223">
-        <v>2.1792172047164111E-3</v>
+        <v>2.2453686620587951E-3</v>
       </c>
       <c r="G223">
         <v>1</v>
@@ -15040,7 +15040,7 @@
         <v>2022</v>
       </c>
       <c r="F224">
-        <v>2.3441398907029388E-3</v>
+        <v>2.3815550419278401E-3</v>
       </c>
       <c r="G224">
         <v>1</v>
@@ -15093,7 +15093,7 @@
         <v>2022</v>
       </c>
       <c r="F225">
-        <v>2.1197508814250247E-3</v>
+        <v>2.2595551090248155E-3</v>
       </c>
       <c r="G225">
         <v>1</v>
@@ -15146,7 +15146,7 @@
         <v>2022</v>
       </c>
       <c r="F226">
-        <v>2.0645211220740429E-3</v>
+        <v>2.3768047278865216E-3</v>
       </c>
       <c r="G226">
         <v>1</v>
@@ -15199,7 +15199,7 @@
         <v>2022</v>
       </c>
       <c r="F227">
-        <v>1.898976957143093E-3</v>
+        <v>6.7745990347051514E-5</v>
       </c>
       <c r="G227">
         <v>1</v>
@@ -15352,7 +15352,7 @@
         <v>138</v>
       </c>
       <c r="D230" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E230">
         <v>2021</v>
@@ -15405,13 +15405,13 @@
         <v>138</v>
       </c>
       <c r="D231" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="E231">
         <v>2023</v>
       </c>
       <c r="F231">
-        <v>3.0999999999999999E-3</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G231">
         <v>1</v>
@@ -15458,13 +15458,13 @@
         <v>138</v>
       </c>
       <c r="D232" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="E232">
         <v>2023</v>
       </c>
       <c r="F232">
-        <v>3.9E-2</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="G232">
         <v>1</v>
@@ -15617,13 +15617,13 @@
         <v>138</v>
       </c>
       <c r="D235" t="s">
-        <v>367</v>
+        <v>46</v>
       </c>
       <c r="E235">
         <v>2025</v>
       </c>
       <c r="F235">
-        <v>3.6999999999999998E-2</v>
+        <v>2.0799999999999999E-2</v>
       </c>
       <c r="G235">
         <v>1</v>
@@ -15670,13 +15670,13 @@
         <v>138</v>
       </c>
       <c r="D236" t="s">
-        <v>46</v>
+        <v>367</v>
       </c>
       <c r="E236">
         <v>2025</v>
       </c>
       <c r="F236">
-        <v>2.0799999999999999E-2</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="G236">
         <v>1</v>

--- a/VerveStacks_NZL_grids/vt_vervestacks_NZL_v1.xlsx
+++ b/VerveStacks_NZL_grids/vt_vervestacks_NZL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FDE875F3-8EA3-4F5A-BA5A-F88BA3761DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DDF29DA-4C50-4438-BFDB-C070C0305A27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8C80F1A2-CCE3-4879-AB5E-9D87F6C2EFC7}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E9CB6262-7AA3-4BDD-987B-2F5A263B854D}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -108,12 +108,12 @@
     <t>gas</t>
   </si>
   <si>
+    <t>e_r17609399-220</t>
+  </si>
+  <si>
     <t>e_w188180344-220</t>
   </si>
   <si>
-    <t>e_r17609399-220</t>
-  </si>
-  <si>
     <t>ep_gas_combined_cycle_G100000407351</t>
   </si>
   <si>
@@ -276,63 +276,63 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_NZ40-220</t>
+  </si>
+  <si>
+    <t>e_NZ13-220</t>
+  </si>
+  <si>
+    <t>e_NZ22-220</t>
+  </si>
+  <si>
     <t>e_w412589726-220</t>
   </si>
   <si>
+    <t>e_w89664063-220</t>
+  </si>
+  <si>
+    <t>e_w180514007-220</t>
+  </si>
+  <si>
+    <t>e_w93556808-220</t>
+  </si>
+  <si>
+    <t>e_w89637174-220</t>
+  </si>
+  <si>
+    <t>e_w89636266-220</t>
+  </si>
+  <si>
+    <t>e_w272522517-220</t>
+  </si>
+  <si>
+    <t>e_NZ14-220</t>
+  </si>
+  <si>
+    <t>e_NZ12-220</t>
+  </si>
+  <si>
     <t>e_w89637173-220</t>
   </si>
   <si>
     <t>e_NZ30-220</t>
   </si>
   <si>
-    <t>e_w93556808-220</t>
-  </si>
-  <si>
-    <t>e_NZ40-220</t>
+    <t>e_NZ35-220</t>
+  </si>
+  <si>
+    <t>e_w270018358-220</t>
+  </si>
+  <si>
+    <t>e_w89411122-220</t>
+  </si>
+  <si>
+    <t>e_NZ11-220</t>
   </si>
   <si>
     <t>e_NZ33-220</t>
   </si>
   <si>
-    <t>e_NZ13-220</t>
-  </si>
-  <si>
-    <t>e_w270018358-220</t>
-  </si>
-  <si>
-    <t>e_w89637174-220</t>
-  </si>
-  <si>
-    <t>e_w89636266-220</t>
-  </si>
-  <si>
-    <t>e_w272522517-220</t>
-  </si>
-  <si>
-    <t>e_NZ14-220</t>
-  </si>
-  <si>
-    <t>e_NZ12-220</t>
-  </si>
-  <si>
-    <t>e_NZ35-220</t>
-  </si>
-  <si>
-    <t>e_NZ11-220</t>
-  </si>
-  <si>
-    <t>e_w89664063-220</t>
-  </si>
-  <si>
-    <t>e_w180514007-220</t>
-  </si>
-  <si>
-    <t>e_w89411122-220</t>
-  </si>
-  <si>
-    <t>e_NZ22-220</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000602849</t>
   </si>
   <si>
@@ -1263,12 +1263,12 @@
     <t>Aggregated Plant - EMBER Gap - way/188180344-220_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/167293888-220_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - relation/17609399-220_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/167293888-220_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Stratford power station_CC1</t>
   </si>
   <si>
@@ -1386,66 +1386,66 @@
     <t>Wairakei geothermal power plant_A</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/89637174-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/180514007-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/270018358-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ35-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ14-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ40-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/93556808-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ11-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89411122-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89664063-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/412589726-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ12-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/87928925-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/93556808-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - NZ30-220_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/89636266-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/272522517-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ33-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/89637173-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/272522517-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ33-220_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - NZ13-220_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - NZ22-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/89636266-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/180514007-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ35-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ14-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/270018358-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ40-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89637174-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ13-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ11-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89411122-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89664063-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/412589726-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ12-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Arapuni hydroelectric plant_</t>
   </si>
   <si>
@@ -1632,10 +1632,10 @@
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/188180344-220_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - relation/17609399-220_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/167293888-220_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - relation/17609399-220_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- McKee power station_2</t>
@@ -2027,7 +2027,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CF9CCC1-E9AA-47AD-A464-AD88D77FFF47}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97CDEAEC-4B21-4513-BEE1-8C605B9747FC}">
   <dimension ref="B9:T38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2271,7 +2271,7 @@
         <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E14">
         <v>0.45937499999999998</v>
@@ -2327,7 +2327,7 @@
         <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E15">
         <v>0.4375</v>
@@ -2439,7 +2439,7 @@
         <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E17">
         <v>0.37624999999999997</v>
@@ -2495,7 +2495,7 @@
         <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E18">
         <v>0.50749999999999995</v>
@@ -2607,7 +2607,7 @@
         <v>22</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E20">
         <v>0.50749999999999995</v>
@@ -2663,7 +2663,7 @@
         <v>22</v>
       </c>
       <c r="D21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E21">
         <v>0.26250000000000001</v>
@@ -2719,7 +2719,7 @@
         <v>22</v>
       </c>
       <c r="D22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E22">
         <v>0.26250000000000001</v>
@@ -2775,7 +2775,7 @@
         <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E23">
         <v>0.27124999999999999</v>
@@ -2831,7 +2831,7 @@
         <v>22</v>
       </c>
       <c r="D24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E24">
         <v>0.27124999999999999</v>
@@ -2887,7 +2887,7 @@
         <v>22</v>
       </c>
       <c r="D25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E25">
         <v>0.26250000000000001</v>
@@ -2943,7 +2943,7 @@
         <v>22</v>
       </c>
       <c r="D26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E26">
         <v>0.26250000000000001</v>
@@ -3055,7 +3055,7 @@
         <v>126</v>
       </c>
       <c r="D28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E28">
         <v>0.4375</v>
@@ -3111,7 +3111,7 @@
         <v>126</v>
       </c>
       <c r="D29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E29">
         <v>0.42</v>
@@ -3223,7 +3223,7 @@
         <v>126</v>
       </c>
       <c r="D31" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E31">
         <v>0.35875000000000001</v>
@@ -3279,7 +3279,7 @@
         <v>126</v>
       </c>
       <c r="D32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E32">
         <v>0.25374999999999998</v>
@@ -3335,7 +3335,7 @@
         <v>126</v>
       </c>
       <c r="D33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E33">
         <v>0.25374999999999998</v>
@@ -3391,7 +3391,7 @@
         <v>126</v>
       </c>
       <c r="D34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E34">
         <v>0.26250000000000001</v>
@@ -3447,7 +3447,7 @@
         <v>126</v>
       </c>
       <c r="D35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E35">
         <v>0.26250000000000001</v>
@@ -3503,7 +3503,7 @@
         <v>126</v>
       </c>
       <c r="D36" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E36">
         <v>0.25374999999999998</v>
@@ -3559,7 +3559,7 @@
         <v>126</v>
       </c>
       <c r="D37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E37">
         <v>0.25374999999999998</v>
@@ -3669,7 +3669,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01616D9F-B003-4136-9A23-7A954210F967}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92C4591A-74FF-4545-9707-48EA5E0F2909}">
   <dimension ref="B9:T260"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4016,19 +4016,19 @@
         <v>2022</v>
       </c>
       <c r="F16">
-        <v>3.9117357695010534E-2</v>
+        <v>0.29931763879128592</v>
       </c>
       <c r="G16">
-        <v>0.56000000000000005</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H16">
-        <v>1350</v>
+        <v>1150</v>
       </c>
       <c r="I16">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="J16">
-        <v>3.5999999999999996</v>
+        <v>3.3000000000000003</v>
       </c>
       <c r="K16">
         <v>50</v>
@@ -4063,13 +4063,13 @@
         <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E17">
         <v>2022</v>
       </c>
       <c r="F17">
-        <v>0.29931763879128592</v>
+        <v>0.1585650035137034</v>
       </c>
       <c r="G17">
         <v>0.57999999999999996</v>
@@ -4116,25 +4116,25 @@
         <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E18">
         <v>2022</v>
       </c>
       <c r="F18">
-        <v>0.1585650035137034</v>
+        <v>3.9117357695010534E-2</v>
       </c>
       <c r="G18">
-        <v>0.57999999999999996</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H18">
-        <v>1150</v>
+        <v>1350</v>
       </c>
       <c r="I18">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J18">
-        <v>3.3000000000000003</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="K18">
         <v>50</v>
@@ -4169,7 +4169,7 @@
         <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E19">
         <v>1998</v>
@@ -4222,7 +4222,7 @@
         <v>22</v>
       </c>
       <c r="D20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E20">
         <v>1996</v>
@@ -4328,7 +4328,7 @@
         <v>22</v>
       </c>
       <c r="D22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E22">
         <v>1987</v>
@@ -4381,7 +4381,7 @@
         <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E23">
         <v>2013</v>
@@ -4434,7 +4434,7 @@
         <v>22</v>
       </c>
       <c r="D24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E24">
         <v>2013</v>
@@ -4487,7 +4487,7 @@
         <v>22</v>
       </c>
       <c r="D25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E25">
         <v>2011</v>
@@ -4540,7 +4540,7 @@
         <v>22</v>
       </c>
       <c r="D26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E26">
         <v>2011</v>
@@ -4593,7 +4593,7 @@
         <v>22</v>
       </c>
       <c r="D27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E27">
         <v>2020</v>
@@ -4646,7 +4646,7 @@
         <v>22</v>
       </c>
       <c r="D28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E28">
         <v>2020</v>
@@ -6401,7 +6401,7 @@
         <v>2022</v>
       </c>
       <c r="F61">
-        <v>0.16073697168649981</v>
+        <v>7.1438654082888797E-2</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -6410,7 +6410,7 @@
         <v>2875</v>
       </c>
       <c r="I61">
-        <v>55.000000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J61">
         <v>2.2000000000000002</v>
@@ -6454,7 +6454,7 @@
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>1.7363561756257695E-2</v>
+        <v>1.3229380385720147E-2</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -6507,7 +6507,7 @@
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>2.6458760771440295E-2</v>
+        <v>1.9844070578580224E-2</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -6554,13 +6554,13 @@
         <v>78</v>
       </c>
       <c r="D64" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="E64">
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>5.8209273697168655E-2</v>
+        <v>0.16073697168649981</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -6569,7 +6569,7 @@
         <v>2875</v>
       </c>
       <c r="I64">
-        <v>55.000000000000007</v>
+        <v>55.000000000000014</v>
       </c>
       <c r="J64">
         <v>2.2000000000000002</v>
@@ -6607,25 +6607,25 @@
         <v>78</v>
       </c>
       <c r="D65" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="E65">
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>1.2237176856791137E-2</v>
+        <v>5.8209273697168655E-2</v>
       </c>
       <c r="G65">
         <v>1</v>
       </c>
       <c r="H65">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I65">
-        <v>65</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J65">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K65">
         <v>100</v>
@@ -6666,7 +6666,7 @@
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>7.1438654082888797E-2</v>
+        <v>8.9298317603610997E-2</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -6675,7 +6675,7 @@
         <v>2875</v>
       </c>
       <c r="I66">
-        <v>55.000000000000007</v>
+        <v>55.000000000000014</v>
       </c>
       <c r="J66">
         <v>2.2000000000000002</v>
@@ -6719,19 +6719,19 @@
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>4.365695527287649E-2</v>
+        <v>5.291752154288059E-2</v>
       </c>
       <c r="G67">
         <v>1</v>
       </c>
       <c r="H67">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I67">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J67">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K67">
         <v>100</v>
@@ -6772,7 +6772,7 @@
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>1.3229380385720147E-2</v>
+        <v>1.2237176856791137E-2</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -6825,13 +6825,13 @@
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>1.2898645876077145E-2</v>
+        <v>3.6380796060730414E-2</v>
       </c>
       <c r="G69">
         <v>1</v>
       </c>
       <c r="H69">
-        <v>3375.0000000000005</v>
+        <v>3375</v>
       </c>
       <c r="I69">
         <v>65</v>
@@ -6878,7 +6878,7 @@
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>3.6380796060730414E-2</v>
+        <v>3.5057858022158397E-2</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -6931,7 +6931,7 @@
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>3.5057858022158397E-2</v>
+        <v>1.7528929011079199E-2</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -6984,7 +6984,7 @@
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>1.7528929011079199E-2</v>
+        <v>2.1001641362330736E-2</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -7037,7 +7037,7 @@
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>2.1001641362330736E-2</v>
+        <v>2.7120229790726307E-2</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -7049,7 +7049,7 @@
         <v>65</v>
       </c>
       <c r="J73">
-        <v>2.4</v>
+        <v>2.3999999999999995</v>
       </c>
       <c r="K73">
         <v>100</v>
@@ -7090,7 +7090,7 @@
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>2.7120229790726307E-2</v>
+        <v>1.7363561756257695E-2</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -7102,7 +7102,7 @@
         <v>65</v>
       </c>
       <c r="J74">
-        <v>2.3999999999999995</v>
+        <v>2.4</v>
       </c>
       <c r="K74">
         <v>100</v>
@@ -7143,7 +7143,7 @@
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>3.5057858022158397E-2</v>
+        <v>2.6458760771440295E-2</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -7196,7 +7196,7 @@
         <v>2022</v>
       </c>
       <c r="F76">
-        <v>1.5875256462864178E-2</v>
+        <v>3.5057858022158397E-2</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -7249,19 +7249,19 @@
         <v>2022</v>
       </c>
       <c r="F77">
-        <v>8.9298317603610997E-2</v>
+        <v>1.2898645876077145E-2</v>
       </c>
       <c r="G77">
         <v>1</v>
       </c>
       <c r="H77">
-        <v>2875</v>
+        <v>3375.0000000000005</v>
       </c>
       <c r="I77">
-        <v>55.000000000000014</v>
+        <v>65</v>
       </c>
       <c r="J77">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K77">
         <v>100</v>
@@ -7302,19 +7302,19 @@
         <v>2022</v>
       </c>
       <c r="F78">
-        <v>5.291752154288059E-2</v>
+        <v>3.9688141157160448E-2</v>
       </c>
       <c r="G78">
         <v>1</v>
       </c>
       <c r="H78">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I78">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="J78">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K78">
         <v>100</v>
@@ -7355,7 +7355,7 @@
         <v>2022</v>
       </c>
       <c r="F79">
-        <v>3.9688141157160448E-2</v>
+        <v>1.5875256462864178E-2</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -7408,7 +7408,7 @@
         <v>2022</v>
       </c>
       <c r="F80">
-        <v>1.9844070578580224E-2</v>
+        <v>4.365695527287649E-2</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -7455,7 +7455,7 @@
         <v>78</v>
       </c>
       <c r="D81" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E81">
         <v>1929</v>
@@ -7508,7 +7508,7 @@
         <v>78</v>
       </c>
       <c r="D82" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E82">
         <v>1968</v>
@@ -7561,7 +7561,7 @@
         <v>78</v>
       </c>
       <c r="D83" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="E83">
         <v>1965</v>
@@ -7614,7 +7614,7 @@
         <v>78</v>
       </c>
       <c r="D84" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E84">
         <v>1992</v>
@@ -7667,7 +7667,7 @@
         <v>78</v>
       </c>
       <c r="D85" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E85">
         <v>1948</v>
@@ -7720,7 +7720,7 @@
         <v>78</v>
       </c>
       <c r="D86" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E86">
         <v>1972</v>
@@ -7879,7 +7879,7 @@
         <v>78</v>
       </c>
       <c r="D89" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E89">
         <v>1961</v>
@@ -7932,7 +7932,7 @@
         <v>78</v>
       </c>
       <c r="D90" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="E90">
         <v>1979</v>
@@ -7985,7 +7985,7 @@
         <v>78</v>
       </c>
       <c r="D91" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E91">
         <v>1984</v>
@@ -8038,7 +8038,7 @@
         <v>78</v>
       </c>
       <c r="D92" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E92">
         <v>1985</v>
@@ -8091,7 +8091,7 @@
         <v>78</v>
       </c>
       <c r="D93" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="E93">
         <v>1983</v>
@@ -8144,7 +8144,7 @@
         <v>78</v>
       </c>
       <c r="D94" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="E94">
         <v>1956</v>
@@ -8197,7 +8197,7 @@
         <v>78</v>
       </c>
       <c r="D95" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="E95">
         <v>1977</v>
@@ -8250,7 +8250,7 @@
         <v>78</v>
       </c>
       <c r="D96" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E96">
         <v>1973</v>
@@ -8303,7 +8303,7 @@
         <v>78</v>
       </c>
       <c r="D97" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="E97">
         <v>1935</v>
@@ -8356,7 +8356,7 @@
         <v>78</v>
       </c>
       <c r="D98" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E98">
         <v>1956</v>
@@ -8409,7 +8409,7 @@
         <v>78</v>
       </c>
       <c r="D99" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E99">
         <v>1967</v>
@@ -8462,7 +8462,7 @@
         <v>78</v>
       </c>
       <c r="D100" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E100">
         <v>1958</v>
@@ -8621,7 +8621,7 @@
         <v>78</v>
       </c>
       <c r="D103" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="E103">
         <v>1964</v>
@@ -8727,7 +8727,7 @@
         <v>126</v>
       </c>
       <c r="D105" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E105">
         <v>1998</v>
@@ -8780,7 +8780,7 @@
         <v>126</v>
       </c>
       <c r="D106" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E106">
         <v>1996</v>
@@ -8886,7 +8886,7 @@
         <v>126</v>
       </c>
       <c r="D108" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E108">
         <v>1987</v>
@@ -8939,7 +8939,7 @@
         <v>126</v>
       </c>
       <c r="D109" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E109">
         <v>2013</v>
@@ -8992,7 +8992,7 @@
         <v>126</v>
       </c>
       <c r="D110" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E110">
         <v>2013</v>
@@ -9045,7 +9045,7 @@
         <v>126</v>
       </c>
       <c r="D111" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E111">
         <v>2011</v>
@@ -9098,7 +9098,7 @@
         <v>126</v>
       </c>
       <c r="D112" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E112">
         <v>2011</v>
@@ -9151,7 +9151,7 @@
         <v>126</v>
       </c>
       <c r="D113" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E113">
         <v>2020</v>
@@ -9204,7 +9204,7 @@
         <v>126</v>
       </c>
       <c r="D114" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E114">
         <v>2020</v>
@@ -15352,7 +15352,7 @@
         <v>138</v>
       </c>
       <c r="D230" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E230">
         <v>2021</v>
@@ -15405,13 +15405,13 @@
         <v>138</v>
       </c>
       <c r="D231" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="E231">
         <v>2023</v>
       </c>
       <c r="F231">
-        <v>3.9E-2</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="G231">
         <v>1</v>
@@ -15458,13 +15458,13 @@
         <v>138</v>
       </c>
       <c r="D232" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="E232">
         <v>2023</v>
       </c>
       <c r="F232">
-        <v>3.0999999999999999E-3</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G232">
         <v>1</v>
@@ -15776,13 +15776,13 @@
         <v>138</v>
       </c>
       <c r="D238" t="s">
-        <v>46</v>
+        <v>369</v>
       </c>
       <c r="E238">
         <v>2028</v>
       </c>
       <c r="F238">
-        <v>2.4E-2</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="G238">
         <v>1</v>
@@ -15808,13 +15808,13 @@
         <v>138</v>
       </c>
       <c r="D239" t="s">
-        <v>369</v>
+        <v>46</v>
       </c>
       <c r="E239">
         <v>2028</v>
       </c>
       <c r="F239">
-        <v>4.9000000000000002E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="G239">
         <v>1</v>

--- a/VerveStacks_NZL_grids/vt_vervestacks_NZL_v1.xlsx
+++ b/VerveStacks_NZL_grids/vt_vervestacks_NZL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DDF29DA-4C50-4438-BFDB-C070C0305A27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C85B244A-1897-4EE9-A984-27048C31CDEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E9CB6262-7AA3-4BDD-987B-2F5A263B854D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9F071D61-2890-475F-866A-59CD1745E30B}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -276,63 +276,63 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_NZ35-220</t>
+  </si>
+  <si>
+    <t>e_w89664063-220</t>
+  </si>
+  <si>
+    <t>e_w180514007-220</t>
+  </si>
+  <si>
+    <t>e_NZ13-220</t>
+  </si>
+  <si>
+    <t>e_NZ33-220</t>
+  </si>
+  <si>
+    <t>e_w270018358-220</t>
+  </si>
+  <si>
+    <t>e_NZ11-220</t>
+  </si>
+  <si>
+    <t>e_w412589726-220</t>
+  </si>
+  <si>
     <t>e_NZ40-220</t>
   </si>
   <si>
-    <t>e_NZ13-220</t>
-  </si>
-  <si>
     <t>e_NZ22-220</t>
   </si>
   <si>
-    <t>e_w412589726-220</t>
-  </si>
-  <si>
-    <t>e_w89664063-220</t>
-  </si>
-  <si>
-    <t>e_w180514007-220</t>
+    <t>e_w89637174-220</t>
+  </si>
+  <si>
+    <t>e_w89636266-220</t>
+  </si>
+  <si>
+    <t>e_w272522517-220</t>
+  </si>
+  <si>
+    <t>e_NZ14-220</t>
+  </si>
+  <si>
+    <t>e_NZ12-220</t>
+  </si>
+  <si>
+    <t>e_w89637173-220</t>
+  </si>
+  <si>
+    <t>e_NZ30-220</t>
+  </si>
+  <si>
+    <t>e_w89411122-220</t>
   </si>
   <si>
     <t>e_w93556808-220</t>
   </si>
   <si>
-    <t>e_w89637174-220</t>
-  </si>
-  <si>
-    <t>e_w89636266-220</t>
-  </si>
-  <si>
-    <t>e_w272522517-220</t>
-  </si>
-  <si>
-    <t>e_NZ14-220</t>
-  </si>
-  <si>
-    <t>e_NZ12-220</t>
-  </si>
-  <si>
-    <t>e_w89637173-220</t>
-  </si>
-  <si>
-    <t>e_NZ30-220</t>
-  </si>
-  <si>
-    <t>e_NZ35-220</t>
-  </si>
-  <si>
-    <t>e_w270018358-220</t>
-  </si>
-  <si>
-    <t>e_w89411122-220</t>
-  </si>
-  <si>
-    <t>e_NZ11-220</t>
-  </si>
-  <si>
-    <t>e_NZ33-220</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000602849</t>
   </si>
   <si>
@@ -1260,15 +1260,15 @@
     <t>Huntly power station_4</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - relation/17609399-220_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/167293888-220_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/188180344-220_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/167293888-220_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - relation/17609399-220_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Stratford power station_CC1</t>
   </si>
   <si>
@@ -1386,10 +1386,49 @@
     <t>Wairakei geothermal power plant_A</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - NZ30-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89637173-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/272522517-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ33-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/93556808-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/180514007-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/89637174-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/180514007-220_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - way/89411122-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89636266-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89664063-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/412589726-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ12-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ13-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ14-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ40-220_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - way/270018358-220_Missing Hydro Capacity</t>
@@ -1398,54 +1437,15 @@
     <t>Aggregated Plant - IRENA Gap - NZ35-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - NZ14-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ40-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/93556808-220_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - NZ22-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/87928925-220_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - NZ11-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/89411122-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89664063-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/412589726-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ12-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/87928925-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ30-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89636266-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/272522517-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ33-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89637173-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ13-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ22-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Arapuni hydroelectric plant_</t>
   </si>
   <si>
@@ -1632,10 +1632,10 @@
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/188180344-220_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/167293888-220_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - relation/17609399-220_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/167293888-220_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- McKee power station_2</t>
@@ -2027,7 +2027,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97CDEAEC-4B21-4513-BEE1-8C605B9747FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F05FA867-B3BA-42C6-B18C-4C9EAF82FCC7}">
   <dimension ref="B9:T38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2495,7 +2495,7 @@
         <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E18">
         <v>0.50749999999999995</v>
@@ -2607,7 +2607,7 @@
         <v>22</v>
       </c>
       <c r="D20" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E20">
         <v>0.50749999999999995</v>
@@ -3669,7 +3669,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92C4591A-74FF-4545-9707-48EA5E0F2909}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{193D5457-8395-454B-B3C5-B4974C8C6476}">
   <dimension ref="B9:T260"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4063,25 +4063,25 @@
         <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E17">
         <v>2022</v>
       </c>
       <c r="F17">
-        <v>0.1585650035137034</v>
+        <v>3.9117357695010534E-2</v>
       </c>
       <c r="G17">
-        <v>0.57999999999999996</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H17">
-        <v>1150</v>
+        <v>1350</v>
       </c>
       <c r="I17">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J17">
-        <v>3.3000000000000003</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="K17">
         <v>50</v>
@@ -4116,25 +4116,25 @@
         <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E18">
         <v>2022</v>
       </c>
       <c r="F18">
-        <v>3.9117357695010534E-2</v>
+        <v>0.1585650035137034</v>
       </c>
       <c r="G18">
-        <v>0.56000000000000005</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H18">
-        <v>1350</v>
+        <v>1150</v>
       </c>
       <c r="I18">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="J18">
-        <v>3.5999999999999996</v>
+        <v>3.3000000000000003</v>
       </c>
       <c r="K18">
         <v>50</v>
@@ -6401,19 +6401,19 @@
         <v>2022</v>
       </c>
       <c r="F61">
-        <v>7.1438654082888797E-2</v>
+        <v>3.5057858022158397E-2</v>
       </c>
       <c r="G61">
         <v>1</v>
       </c>
       <c r="H61">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I61">
-        <v>55.000000000000007</v>
+        <v>65</v>
       </c>
       <c r="J61">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K61">
         <v>100</v>
@@ -6454,19 +6454,19 @@
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>1.3229380385720147E-2</v>
+        <v>8.9298317603610997E-2</v>
       </c>
       <c r="G62">
         <v>1</v>
       </c>
       <c r="H62">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I62">
-        <v>65</v>
+        <v>55.000000000000014</v>
       </c>
       <c r="J62">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K62">
         <v>100</v>
@@ -6507,19 +6507,19 @@
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>1.9844070578580224E-2</v>
+        <v>5.291752154288059E-2</v>
       </c>
       <c r="G63">
         <v>1</v>
       </c>
       <c r="H63">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I63">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J63">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K63">
         <v>100</v>
@@ -6560,19 +6560,19 @@
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>0.16073697168649981</v>
+        <v>1.3229380385720147E-2</v>
       </c>
       <c r="G64">
         <v>1</v>
       </c>
       <c r="H64">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I64">
-        <v>55.000000000000014</v>
+        <v>65</v>
       </c>
       <c r="J64">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K64">
         <v>100</v>
@@ -6607,25 +6607,25 @@
         <v>78</v>
       </c>
       <c r="D65" t="s">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="E65">
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>5.8209273697168655E-2</v>
+        <v>4.365695527287649E-2</v>
       </c>
       <c r="G65">
         <v>1</v>
       </c>
       <c r="H65">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I65">
-        <v>55.000000000000007</v>
+        <v>65</v>
       </c>
       <c r="J65">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K65">
         <v>100</v>
@@ -6660,25 +6660,25 @@
         <v>78</v>
       </c>
       <c r="D66" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E66">
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>8.9298317603610997E-2</v>
+        <v>1.2898645876077145E-2</v>
       </c>
       <c r="G66">
         <v>1</v>
       </c>
       <c r="H66">
-        <v>2875</v>
+        <v>3375.0000000000005</v>
       </c>
       <c r="I66">
-        <v>55.000000000000014</v>
+        <v>65</v>
       </c>
       <c r="J66">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K66">
         <v>100</v>
@@ -6713,25 +6713,25 @@
         <v>78</v>
       </c>
       <c r="D67" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E67">
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>5.291752154288059E-2</v>
+        <v>1.5875256462864178E-2</v>
       </c>
       <c r="G67">
         <v>1</v>
       </c>
       <c r="H67">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I67">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="J67">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K67">
         <v>100</v>
@@ -6766,25 +6766,25 @@
         <v>78</v>
       </c>
       <c r="D68" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="E68">
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>1.2237176856791137E-2</v>
+        <v>5.8209273697168655E-2</v>
       </c>
       <c r="G68">
         <v>1</v>
       </c>
       <c r="H68">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I68">
-        <v>65</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J68">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K68">
         <v>100</v>
@@ -6825,19 +6825,19 @@
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>3.6380796060730414E-2</v>
+        <v>0.16073697168649981</v>
       </c>
       <c r="G69">
         <v>1</v>
       </c>
       <c r="H69">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I69">
-        <v>65</v>
+        <v>55.000000000000014</v>
       </c>
       <c r="J69">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K69">
         <v>100</v>
@@ -6878,19 +6878,19 @@
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>3.5057858022158397E-2</v>
+        <v>7.1438654082888797E-2</v>
       </c>
       <c r="G70">
         <v>1</v>
       </c>
       <c r="H70">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I70">
-        <v>65</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J70">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K70">
         <v>100</v>
@@ -6931,7 +6931,7 @@
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>1.7528929011079199E-2</v>
+        <v>1.9844070578580224E-2</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -6984,7 +6984,7 @@
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>2.1001641362330736E-2</v>
+        <v>3.6380796060730414E-2</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -7037,7 +7037,7 @@
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>2.7120229790726307E-2</v>
+        <v>3.5057858022158397E-2</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -7049,7 +7049,7 @@
         <v>65</v>
       </c>
       <c r="J73">
-        <v>2.3999999999999995</v>
+        <v>2.4</v>
       </c>
       <c r="K73">
         <v>100</v>
@@ -7090,7 +7090,7 @@
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>1.7363561756257695E-2</v>
+        <v>1.7528929011079199E-2</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -7143,7 +7143,7 @@
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>2.6458760771440295E-2</v>
+        <v>2.1001641362330736E-2</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -7196,7 +7196,7 @@
         <v>2022</v>
       </c>
       <c r="F76">
-        <v>3.5057858022158397E-2</v>
+        <v>2.7120229790726307E-2</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -7208,7 +7208,7 @@
         <v>65</v>
       </c>
       <c r="J76">
-        <v>2.4</v>
+        <v>2.3999999999999995</v>
       </c>
       <c r="K76">
         <v>100</v>
@@ -7249,13 +7249,13 @@
         <v>2022</v>
       </c>
       <c r="F77">
-        <v>1.2898645876077145E-2</v>
+        <v>1.7363561756257695E-2</v>
       </c>
       <c r="G77">
         <v>1</v>
       </c>
       <c r="H77">
-        <v>3375.0000000000005</v>
+        <v>3375</v>
       </c>
       <c r="I77">
         <v>65</v>
@@ -7302,7 +7302,7 @@
         <v>2022</v>
       </c>
       <c r="F78">
-        <v>3.9688141157160448E-2</v>
+        <v>2.6458760771440295E-2</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -7355,7 +7355,7 @@
         <v>2022</v>
       </c>
       <c r="F79">
-        <v>1.5875256462864178E-2</v>
+        <v>3.9688141157160448E-2</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -7408,7 +7408,7 @@
         <v>2022</v>
       </c>
       <c r="F80">
-        <v>4.365695527287649E-2</v>
+        <v>1.2237176856791137E-2</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -7455,7 +7455,7 @@
         <v>78</v>
       </c>
       <c r="D81" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E81">
         <v>1929</v>
@@ -7508,7 +7508,7 @@
         <v>78</v>
       </c>
       <c r="D82" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E82">
         <v>1968</v>
@@ -7561,7 +7561,7 @@
         <v>78</v>
       </c>
       <c r="D83" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E83">
         <v>1965</v>
@@ -7614,7 +7614,7 @@
         <v>78</v>
       </c>
       <c r="D84" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E84">
         <v>1992</v>
@@ -7667,7 +7667,7 @@
         <v>78</v>
       </c>
       <c r="D85" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="E85">
         <v>1948</v>
@@ -7720,7 +7720,7 @@
         <v>78</v>
       </c>
       <c r="D86" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E86">
         <v>1972</v>
@@ -7879,7 +7879,7 @@
         <v>78</v>
       </c>
       <c r="D89" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E89">
         <v>1961</v>
@@ -7932,7 +7932,7 @@
         <v>78</v>
       </c>
       <c r="D90" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="E90">
         <v>1979</v>
@@ -7985,7 +7985,7 @@
         <v>78</v>
       </c>
       <c r="D91" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="E91">
         <v>1984</v>
@@ -8038,7 +8038,7 @@
         <v>78</v>
       </c>
       <c r="D92" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E92">
         <v>1985</v>
@@ -8091,7 +8091,7 @@
         <v>78</v>
       </c>
       <c r="D93" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E93">
         <v>1983</v>
@@ -8144,7 +8144,7 @@
         <v>78</v>
       </c>
       <c r="D94" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E94">
         <v>1956</v>
@@ -8197,7 +8197,7 @@
         <v>78</v>
       </c>
       <c r="D95" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E95">
         <v>1977</v>
@@ -8250,7 +8250,7 @@
         <v>78</v>
       </c>
       <c r="D96" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E96">
         <v>1973</v>
@@ -8303,7 +8303,7 @@
         <v>78</v>
       </c>
       <c r="D97" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E97">
         <v>1935</v>
@@ -8356,7 +8356,7 @@
         <v>78</v>
       </c>
       <c r="D98" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E98">
         <v>1956</v>
@@ -8409,7 +8409,7 @@
         <v>78</v>
       </c>
       <c r="D99" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E99">
         <v>1967</v>
@@ -8462,7 +8462,7 @@
         <v>78</v>
       </c>
       <c r="D100" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E100">
         <v>1958</v>
@@ -8621,7 +8621,7 @@
         <v>78</v>
       </c>
       <c r="D103" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E103">
         <v>1964</v>
@@ -15405,13 +15405,13 @@
         <v>138</v>
       </c>
       <c r="D231" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="E231">
         <v>2023</v>
       </c>
       <c r="F231">
-        <v>3.0999999999999999E-3</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G231">
         <v>1</v>
@@ -15458,13 +15458,13 @@
         <v>138</v>
       </c>
       <c r="D232" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="E232">
         <v>2023</v>
       </c>
       <c r="F232">
-        <v>3.9E-2</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="G232">
         <v>1</v>
@@ -15617,13 +15617,13 @@
         <v>138</v>
       </c>
       <c r="D235" t="s">
-        <v>46</v>
+        <v>367</v>
       </c>
       <c r="E235">
         <v>2025</v>
       </c>
       <c r="F235">
-        <v>2.0799999999999999E-2</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="G235">
         <v>1</v>
@@ -15670,13 +15670,13 @@
         <v>138</v>
       </c>
       <c r="D236" t="s">
-        <v>367</v>
+        <v>46</v>
       </c>
       <c r="E236">
         <v>2025</v>
       </c>
       <c r="F236">
-        <v>3.6999999999999998E-2</v>
+        <v>2.0799999999999999E-2</v>
       </c>
       <c r="G236">
         <v>1</v>
@@ -15776,13 +15776,13 @@
         <v>138</v>
       </c>
       <c r="D238" t="s">
-        <v>369</v>
+        <v>46</v>
       </c>
       <c r="E238">
         <v>2028</v>
       </c>
       <c r="F238">
-        <v>4.9000000000000002E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="G238">
         <v>1</v>
@@ -15808,13 +15808,13 @@
         <v>138</v>
       </c>
       <c r="D239" t="s">
-        <v>46</v>
+        <v>369</v>
       </c>
       <c r="E239">
         <v>2028</v>
       </c>
       <c r="F239">
-        <v>2.4E-2</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="G239">
         <v>1</v>

--- a/VerveStacks_NZL_grids/vt_vervestacks_NZL_v1.xlsx
+++ b/VerveStacks_NZL_grids/vt_vervestacks_NZL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C85B244A-1897-4EE9-A984-27048C31CDEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A257F4A0-D98A-4DBB-9084-080C7D9D0178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9F071D61-2890-475F-866A-59CD1745E30B}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5029C820-1D4F-4ABB-9870-CD1BFD393216}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -276,63 +276,63 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_w89637174-220</t>
+  </si>
+  <si>
+    <t>e_w89664063-220</t>
+  </si>
+  <si>
+    <t>e_w180514007-220</t>
+  </si>
+  <si>
+    <t>e_NZ13-220</t>
+  </si>
+  <si>
+    <t>e_NZ33-220</t>
+  </si>
+  <si>
+    <t>e_w89636266-220</t>
+  </si>
+  <si>
+    <t>e_w272522517-220</t>
+  </si>
+  <si>
+    <t>e_NZ14-220</t>
+  </si>
+  <si>
+    <t>e_NZ12-220</t>
+  </si>
+  <si>
+    <t>e_w270018358-220</t>
+  </si>
+  <si>
+    <t>e_w89411122-220</t>
+  </si>
+  <si>
+    <t>e_w412589726-220</t>
+  </si>
+  <si>
+    <t>e_NZ40-220</t>
+  </si>
+  <si>
+    <t>e_NZ11-220</t>
+  </si>
+  <si>
+    <t>e_NZ22-220</t>
+  </si>
+  <si>
+    <t>e_w93556808-220</t>
+  </si>
+  <si>
+    <t>e_w89637173-220</t>
+  </si>
+  <si>
+    <t>e_NZ30-220</t>
+  </si>
+  <si>
     <t>e_NZ35-220</t>
   </si>
   <si>
-    <t>e_w89664063-220</t>
-  </si>
-  <si>
-    <t>e_w180514007-220</t>
-  </si>
-  <si>
-    <t>e_NZ13-220</t>
-  </si>
-  <si>
-    <t>e_NZ33-220</t>
-  </si>
-  <si>
-    <t>e_w270018358-220</t>
-  </si>
-  <si>
-    <t>e_NZ11-220</t>
-  </si>
-  <si>
-    <t>e_w412589726-220</t>
-  </si>
-  <si>
-    <t>e_NZ40-220</t>
-  </si>
-  <si>
-    <t>e_NZ22-220</t>
-  </si>
-  <si>
-    <t>e_w89637174-220</t>
-  </si>
-  <si>
-    <t>e_w89636266-220</t>
-  </si>
-  <si>
-    <t>e_w272522517-220</t>
-  </si>
-  <si>
-    <t>e_NZ14-220</t>
-  </si>
-  <si>
-    <t>e_NZ12-220</t>
-  </si>
-  <si>
-    <t>e_w89637173-220</t>
-  </si>
-  <si>
-    <t>e_NZ30-220</t>
-  </si>
-  <si>
-    <t>e_w89411122-220</t>
-  </si>
-  <si>
-    <t>e_w93556808-220</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000602849</t>
   </si>
   <si>
@@ -1386,64 +1386,64 @@
     <t>Wairakei geothermal power plant_A</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/89636266-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/180514007-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89637174-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ35-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ40-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/270018358-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ14-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89664063-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/412589726-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89411122-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ13-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ12-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/87928925-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - NZ30-220_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - NZ22-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/272522517-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ33-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/89637173-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/272522517-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ33-220_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - NZ11-220_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - way/93556808-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/180514007-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89637174-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89411122-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89636266-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89664063-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/412589726-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ12-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ13-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ14-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ40-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/270018358-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ35-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ22-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/87928925-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ11-220_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Arapuni hydroelectric plant_</t>
@@ -2027,7 +2027,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F05FA867-B3BA-42C6-B18C-4C9EAF82FCC7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8520F056-D215-47A7-876E-FFAC7C9535E7}">
   <dimension ref="B9:T38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3669,7 +3669,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{193D5457-8395-454B-B3C5-B4974C8C6476}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{668697DC-05C7-410F-BB71-5C89FC8B9F13}">
   <dimension ref="B9:T260"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6401,7 +6401,7 @@
         <v>2022</v>
       </c>
       <c r="F61">
-        <v>3.5057858022158397E-2</v>
+        <v>3.6380796060730414E-2</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -6666,13 +6666,13 @@
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>1.2898645876077145E-2</v>
+        <v>3.5057858022158397E-2</v>
       </c>
       <c r="G66">
         <v>1</v>
       </c>
       <c r="H66">
-        <v>3375.0000000000005</v>
+        <v>3375</v>
       </c>
       <c r="I66">
         <v>65</v>
@@ -6719,7 +6719,7 @@
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>1.5875256462864178E-2</v>
+        <v>1.7528929011079199E-2</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -6766,25 +6766,25 @@
         <v>78</v>
       </c>
       <c r="D68" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="E68">
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>5.8209273697168655E-2</v>
+        <v>2.1001641362330736E-2</v>
       </c>
       <c r="G68">
         <v>1</v>
       </c>
       <c r="H68">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I68">
-        <v>55.000000000000007</v>
+        <v>65</v>
       </c>
       <c r="J68">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K68">
         <v>100</v>
@@ -6819,25 +6819,25 @@
         <v>78</v>
       </c>
       <c r="D69" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E69">
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>0.16073697168649981</v>
+        <v>2.7120229790726307E-2</v>
       </c>
       <c r="G69">
         <v>1</v>
       </c>
       <c r="H69">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I69">
-        <v>55.000000000000014</v>
+        <v>65</v>
       </c>
       <c r="J69">
-        <v>2.2000000000000002</v>
+        <v>2.3999999999999995</v>
       </c>
       <c r="K69">
         <v>100</v>
@@ -6872,25 +6872,25 @@
         <v>78</v>
       </c>
       <c r="D70" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E70">
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>7.1438654082888797E-2</v>
+        <v>1.2898645876077145E-2</v>
       </c>
       <c r="G70">
         <v>1</v>
       </c>
       <c r="H70">
-        <v>2875</v>
+        <v>3375.0000000000005</v>
       </c>
       <c r="I70">
-        <v>55.000000000000007</v>
+        <v>65</v>
       </c>
       <c r="J70">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K70">
         <v>100</v>
@@ -6925,13 +6925,13 @@
         <v>78</v>
       </c>
       <c r="D71" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E71">
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>1.9844070578580224E-2</v>
+        <v>3.9688141157160448E-2</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -6978,25 +6978,25 @@
         <v>78</v>
       </c>
       <c r="D72" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="E72">
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>3.6380796060730414E-2</v>
+        <v>5.8209273697168655E-2</v>
       </c>
       <c r="G72">
         <v>1</v>
       </c>
       <c r="H72">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I72">
-        <v>65</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J72">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K72">
         <v>100</v>
@@ -7037,19 +7037,19 @@
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>3.5057858022158397E-2</v>
+        <v>0.16073697168649981</v>
       </c>
       <c r="G73">
         <v>1</v>
       </c>
       <c r="H73">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I73">
-        <v>65</v>
+        <v>55.000000000000014</v>
       </c>
       <c r="J73">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K73">
         <v>100</v>
@@ -7090,19 +7090,19 @@
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>1.7528929011079199E-2</v>
+        <v>7.1438654082888797E-2</v>
       </c>
       <c r="G74">
         <v>1</v>
       </c>
       <c r="H74">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I74">
-        <v>65</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J74">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K74">
         <v>100</v>
@@ -7143,7 +7143,7 @@
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>2.1001641362330736E-2</v>
+        <v>1.5875256462864178E-2</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -7196,7 +7196,7 @@
         <v>2022</v>
       </c>
       <c r="F76">
-        <v>2.7120229790726307E-2</v>
+        <v>1.9844070578580224E-2</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -7208,7 +7208,7 @@
         <v>65</v>
       </c>
       <c r="J76">
-        <v>2.3999999999999995</v>
+        <v>2.4</v>
       </c>
       <c r="K76">
         <v>100</v>
@@ -7249,7 +7249,7 @@
         <v>2022</v>
       </c>
       <c r="F77">
-        <v>1.7363561756257695E-2</v>
+        <v>1.2237176856791137E-2</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -7302,7 +7302,7 @@
         <v>2022</v>
       </c>
       <c r="F78">
-        <v>2.6458760771440295E-2</v>
+        <v>1.7363561756257695E-2</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -7355,7 +7355,7 @@
         <v>2022</v>
       </c>
       <c r="F79">
-        <v>3.9688141157160448E-2</v>
+        <v>2.6458760771440295E-2</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -7408,7 +7408,7 @@
         <v>2022</v>
       </c>
       <c r="F80">
-        <v>1.2237176856791137E-2</v>
+        <v>3.5057858022158397E-2</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -7455,7 +7455,7 @@
         <v>78</v>
       </c>
       <c r="D81" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E81">
         <v>1929</v>
@@ -7508,7 +7508,7 @@
         <v>78</v>
       </c>
       <c r="D82" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="E82">
         <v>1968</v>
@@ -7614,7 +7614,7 @@
         <v>78</v>
       </c>
       <c r="D84" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E84">
         <v>1992</v>
@@ -7667,7 +7667,7 @@
         <v>78</v>
       </c>
       <c r="D85" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="E85">
         <v>1948</v>
@@ -7720,7 +7720,7 @@
         <v>78</v>
       </c>
       <c r="D86" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E86">
         <v>1972</v>
@@ -7879,7 +7879,7 @@
         <v>78</v>
       </c>
       <c r="D89" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E89">
         <v>1961</v>
@@ -7985,7 +7985,7 @@
         <v>78</v>
       </c>
       <c r="D91" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="E91">
         <v>1984</v>
@@ -8038,7 +8038,7 @@
         <v>78</v>
       </c>
       <c r="D92" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E92">
         <v>1985</v>
@@ -8091,7 +8091,7 @@
         <v>78</v>
       </c>
       <c r="D93" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E93">
         <v>1983</v>
@@ -8197,7 +8197,7 @@
         <v>78</v>
       </c>
       <c r="D95" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E95">
         <v>1977</v>
@@ -8250,7 +8250,7 @@
         <v>78</v>
       </c>
       <c r="D96" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="E96">
         <v>1973</v>
@@ -8303,7 +8303,7 @@
         <v>78</v>
       </c>
       <c r="D97" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E97">
         <v>1935</v>
@@ -8356,7 +8356,7 @@
         <v>78</v>
       </c>
       <c r="D98" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E98">
         <v>1956</v>
@@ -8462,7 +8462,7 @@
         <v>78</v>
       </c>
       <c r="D100" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E100">
         <v>1958</v>
@@ -8621,7 +8621,7 @@
         <v>78</v>
       </c>
       <c r="D103" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E103">
         <v>1964</v>
@@ -9369,7 +9369,7 @@
         <v>2022</v>
       </c>
       <c r="F117">
-        <v>1.5957719531620534E-3</v>
+        <v>1.5957719531620542E-3</v>
       </c>
       <c r="G117">
         <v>1</v>
@@ -9422,7 +9422,7 @@
         <v>2022</v>
       </c>
       <c r="F118">
-        <v>1.681394643094816E-3</v>
+        <v>1.6813946430948173E-3</v>
       </c>
       <c r="G118">
         <v>1</v>
@@ -9431,7 +9431,7 @@
         <v>1215</v>
       </c>
       <c r="I118">
-        <v>19.499999999999996</v>
+        <v>19.500000000000004</v>
       </c>
       <c r="J118">
         <v>0</v>
@@ -10482,7 +10482,7 @@
         <v>2022</v>
       </c>
       <c r="F138">
-        <v>2.6863869603865236E-3</v>
+        <v>2.6863869603865253E-3</v>
       </c>
       <c r="G138">
         <v>1</v>
@@ -11118,7 +11118,7 @@
         <v>2022</v>
       </c>
       <c r="F150">
-        <v>1.9090109152240446E-3</v>
+        <v>1.9090109152240457E-3</v>
       </c>
       <c r="G150">
         <v>1</v>
@@ -12019,7 +12019,7 @@
         <v>2022</v>
       </c>
       <c r="F167">
-        <v>2.2320440636524322E-3</v>
+        <v>2.2320440636524326E-3</v>
       </c>
       <c r="G167">
         <v>1</v>
@@ -12231,7 +12231,7 @@
         <v>2022</v>
       </c>
       <c r="F171">
-        <v>2.2323451014424579E-3</v>
+        <v>2.2323451014424588E-3</v>
       </c>
       <c r="G171">
         <v>1</v>
@@ -13397,7 +13397,7 @@
         <v>2022</v>
       </c>
       <c r="F193">
-        <v>2.3657873773726087E-3</v>
+        <v>2.36578737737261E-3</v>
       </c>
       <c r="G193">
         <v>1</v>
@@ -13662,7 +13662,7 @@
         <v>2022</v>
       </c>
       <c r="F198">
-        <v>2.7062981548627023E-3</v>
+        <v>2.706298154862704E-3</v>
       </c>
       <c r="G198">
         <v>1</v>
@@ -13874,7 +13874,7 @@
         <v>2022</v>
       </c>
       <c r="F202">
-        <v>2.2407479819659447E-3</v>
+        <v>2.240747981965946E-3</v>
       </c>
       <c r="G202">
         <v>1</v>
@@ -14298,7 +14298,7 @@
         <v>2022</v>
       </c>
       <c r="F210">
-        <v>2.6140637340113619E-3</v>
+        <v>2.6140637340113636E-3</v>
       </c>
       <c r="G210">
         <v>1</v>
@@ -14722,7 +14722,7 @@
         <v>2022</v>
       </c>
       <c r="F218">
-        <v>2.1862941780759204E-3</v>
+        <v>2.1862941780759217E-3</v>
       </c>
       <c r="G218">
         <v>1</v>
@@ -15093,7 +15093,7 @@
         <v>2022</v>
       </c>
       <c r="F225">
-        <v>2.2595551090248155E-3</v>
+        <v>2.2595551090248164E-3</v>
       </c>
       <c r="G225">
         <v>1</v>
@@ -15299,13 +15299,13 @@
         <v>138</v>
       </c>
       <c r="D229" t="s">
-        <v>364</v>
+        <v>23</v>
       </c>
       <c r="E229">
         <v>2021</v>
       </c>
       <c r="F229">
-        <v>2.5000000000000001E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="G229">
         <v>1</v>
@@ -15352,13 +15352,13 @@
         <v>138</v>
       </c>
       <c r="D230" t="s">
-        <v>23</v>
+        <v>364</v>
       </c>
       <c r="E230">
         <v>2021</v>
       </c>
       <c r="F230">
-        <v>1.9E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="G230">
         <v>1</v>

--- a/VerveStacks_NZL_grids/vt_vervestacks_NZL_v1.xlsx
+++ b/VerveStacks_NZL_grids/vt_vervestacks_NZL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A257F4A0-D98A-4DBB-9084-080C7D9D0178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{50012E06-1139-4613-8335-A082F8BC6623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5029C820-1D4F-4ABB-9870-CD1BFD393216}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{171C3F22-0E79-4AC4-B1BD-94BDDD2385EC}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -276,21 +276,48 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_w270018358-220</t>
+  </si>
+  <si>
+    <t>e_NZ11-220</t>
+  </si>
+  <si>
+    <t>e_NZ35-220</t>
+  </si>
+  <si>
+    <t>e_NZ13-220</t>
+  </si>
+  <si>
+    <t>e_NZ33-220</t>
+  </si>
+  <si>
+    <t>e_w89411122-220</t>
+  </si>
+  <si>
+    <t>e_w412589726-220</t>
+  </si>
+  <si>
+    <t>e_NZ40-220</t>
+  </si>
+  <si>
+    <t>e_w89664063-220</t>
+  </si>
+  <si>
+    <t>e_w180514007-220</t>
+  </si>
+  <si>
+    <t>e_w93556808-220</t>
+  </si>
+  <si>
+    <t>e_w89637173-220</t>
+  </si>
+  <si>
+    <t>e_NZ30-220</t>
+  </si>
+  <si>
     <t>e_w89637174-220</t>
   </si>
   <si>
-    <t>e_w89664063-220</t>
-  </si>
-  <si>
-    <t>e_w180514007-220</t>
-  </si>
-  <si>
-    <t>e_NZ13-220</t>
-  </si>
-  <si>
-    <t>e_NZ33-220</t>
-  </si>
-  <si>
     <t>e_w89636266-220</t>
   </si>
   <si>
@@ -303,36 +330,9 @@
     <t>e_NZ12-220</t>
   </si>
   <si>
-    <t>e_w270018358-220</t>
-  </si>
-  <si>
-    <t>e_w89411122-220</t>
-  </si>
-  <si>
-    <t>e_w412589726-220</t>
-  </si>
-  <si>
-    <t>e_NZ40-220</t>
-  </si>
-  <si>
-    <t>e_NZ11-220</t>
-  </si>
-  <si>
     <t>e_NZ22-220</t>
   </si>
   <si>
-    <t>e_w93556808-220</t>
-  </si>
-  <si>
-    <t>e_w89637173-220</t>
-  </si>
-  <si>
-    <t>e_NZ30-220</t>
-  </si>
-  <si>
-    <t>e_NZ35-220</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000602849</t>
   </si>
   <si>
@@ -1386,66 +1386,66 @@
     <t>Wairakei geothermal power plant_A</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - NZ22-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/89636266-220_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - NZ13-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/272522517-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ30-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89637173-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ33-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/87928925-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ35-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ14-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ40-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/270018358-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ12-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89664063-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/412589726-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89411122-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/93556808-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ11-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89637174-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/180514007-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/89637174-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ35-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ40-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/270018358-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ14-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89664063-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/412589726-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89411122-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ13-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ12-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/87928925-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ30-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ22-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/272522517-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ33-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89637173-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ11-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/93556808-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Arapuni hydroelectric plant_</t>
   </si>
   <si>
@@ -1629,13 +1629,13 @@
     <t>ccs retrofit of -- Glenbrook power station_1</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - relation/17609399-220_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/188180344-220_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/167293888-220_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - relation/17609399-220_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- McKee power station_2</t>
@@ -2027,7 +2027,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8520F056-D215-47A7-876E-FFAC7C9535E7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BD46AF1-40A4-4A17-ABA1-EAFFF2DF7114}">
   <dimension ref="B9:T38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3669,7 +3669,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{668697DC-05C7-410F-BB71-5C89FC8B9F13}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87C32617-3D75-4CD7-8D84-2C5AF131ED18}">
   <dimension ref="B9:T260"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6401,13 +6401,13 @@
         <v>2022</v>
       </c>
       <c r="F61">
-        <v>3.6380796060730414E-2</v>
+        <v>1.2898645876077145E-2</v>
       </c>
       <c r="G61">
         <v>1</v>
       </c>
       <c r="H61">
-        <v>3375</v>
+        <v>3375.0000000000005</v>
       </c>
       <c r="I61">
         <v>65</v>
@@ -6454,19 +6454,19 @@
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>8.9298317603610997E-2</v>
+        <v>1.5875256462864178E-2</v>
       </c>
       <c r="G62">
         <v>1</v>
       </c>
       <c r="H62">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I62">
-        <v>55.000000000000014</v>
+        <v>65</v>
       </c>
       <c r="J62">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K62">
         <v>100</v>
@@ -6507,19 +6507,19 @@
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>5.291752154288059E-2</v>
+        <v>3.5057858022158397E-2</v>
       </c>
       <c r="G63">
         <v>1</v>
       </c>
       <c r="H63">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I63">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="J63">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K63">
         <v>100</v>
@@ -6666,7 +6666,7 @@
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>3.5057858022158397E-2</v>
+        <v>3.9688141157160448E-2</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -6713,25 +6713,25 @@
         <v>78</v>
       </c>
       <c r="D67" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="E67">
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>1.7528929011079199E-2</v>
+        <v>5.8209273697168655E-2</v>
       </c>
       <c r="G67">
         <v>1</v>
       </c>
       <c r="H67">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I67">
-        <v>65</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J67">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K67">
         <v>100</v>
@@ -6766,25 +6766,25 @@
         <v>78</v>
       </c>
       <c r="D68" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E68">
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>2.1001641362330736E-2</v>
+        <v>0.16073697168649981</v>
       </c>
       <c r="G68">
         <v>1</v>
       </c>
       <c r="H68">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I68">
-        <v>65</v>
+        <v>55.000000000000014</v>
       </c>
       <c r="J68">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K68">
         <v>100</v>
@@ -6819,25 +6819,25 @@
         <v>78</v>
       </c>
       <c r="D69" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E69">
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>2.7120229790726307E-2</v>
+        <v>7.1438654082888797E-2</v>
       </c>
       <c r="G69">
         <v>1</v>
       </c>
       <c r="H69">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I69">
-        <v>65</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J69">
-        <v>2.3999999999999995</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K69">
         <v>100</v>
@@ -6872,25 +6872,25 @@
         <v>78</v>
       </c>
       <c r="D70" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E70">
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>1.2898645876077145E-2</v>
+        <v>8.9298317603610997E-2</v>
       </c>
       <c r="G70">
         <v>1</v>
       </c>
       <c r="H70">
-        <v>3375.0000000000005</v>
+        <v>2875</v>
       </c>
       <c r="I70">
-        <v>65</v>
+        <v>55.000000000000014</v>
       </c>
       <c r="J70">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K70">
         <v>100</v>
@@ -6925,25 +6925,25 @@
         <v>78</v>
       </c>
       <c r="D71" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E71">
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>3.9688141157160448E-2</v>
+        <v>5.291752154288059E-2</v>
       </c>
       <c r="G71">
         <v>1</v>
       </c>
       <c r="H71">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I71">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J71">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K71">
         <v>100</v>
@@ -6978,25 +6978,25 @@
         <v>78</v>
       </c>
       <c r="D72" t="s">
-        <v>14</v>
+        <v>89</v>
       </c>
       <c r="E72">
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>5.8209273697168655E-2</v>
+        <v>1.2237176856791137E-2</v>
       </c>
       <c r="G72">
         <v>1</v>
       </c>
       <c r="H72">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I72">
-        <v>55.000000000000007</v>
+        <v>65</v>
       </c>
       <c r="J72">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K72">
         <v>100</v>
@@ -7037,19 +7037,19 @@
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>0.16073697168649981</v>
+        <v>1.7363561756257695E-2</v>
       </c>
       <c r="G73">
         <v>1</v>
       </c>
       <c r="H73">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I73">
-        <v>55.000000000000014</v>
+        <v>65</v>
       </c>
       <c r="J73">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K73">
         <v>100</v>
@@ -7090,19 +7090,19 @@
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>7.1438654082888797E-2</v>
+        <v>2.6458760771440295E-2</v>
       </c>
       <c r="G74">
         <v>1</v>
       </c>
       <c r="H74">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I74">
-        <v>55.000000000000007</v>
+        <v>65</v>
       </c>
       <c r="J74">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K74">
         <v>100</v>
@@ -7143,7 +7143,7 @@
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>1.5875256462864178E-2</v>
+        <v>3.6380796060730414E-2</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -7196,7 +7196,7 @@
         <v>2022</v>
       </c>
       <c r="F76">
-        <v>1.9844070578580224E-2</v>
+        <v>3.5057858022158397E-2</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -7249,7 +7249,7 @@
         <v>2022</v>
       </c>
       <c r="F77">
-        <v>1.2237176856791137E-2</v>
+        <v>1.7528929011079199E-2</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -7302,7 +7302,7 @@
         <v>2022</v>
       </c>
       <c r="F78">
-        <v>1.7363561756257695E-2</v>
+        <v>2.1001641362330736E-2</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -7355,7 +7355,7 @@
         <v>2022</v>
       </c>
       <c r="F79">
-        <v>2.6458760771440295E-2</v>
+        <v>2.7120229790726307E-2</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -7367,7 +7367,7 @@
         <v>65</v>
       </c>
       <c r="J79">
-        <v>2.4</v>
+        <v>2.3999999999999995</v>
       </c>
       <c r="K79">
         <v>100</v>
@@ -7408,7 +7408,7 @@
         <v>2022</v>
       </c>
       <c r="F80">
-        <v>3.5057858022158397E-2</v>
+        <v>1.9844070578580224E-2</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -7455,7 +7455,7 @@
         <v>78</v>
       </c>
       <c r="D81" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="E81">
         <v>1929</v>
@@ -7508,7 +7508,7 @@
         <v>78</v>
       </c>
       <c r="D82" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="E82">
         <v>1968</v>
@@ -7561,7 +7561,7 @@
         <v>78</v>
       </c>
       <c r="D83" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="E83">
         <v>1965</v>
@@ -7614,7 +7614,7 @@
         <v>78</v>
       </c>
       <c r="D84" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E84">
         <v>1992</v>
@@ -7667,7 +7667,7 @@
         <v>78</v>
       </c>
       <c r="D85" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="E85">
         <v>1948</v>
@@ -7720,7 +7720,7 @@
         <v>78</v>
       </c>
       <c r="D86" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E86">
         <v>1972</v>
@@ -7879,7 +7879,7 @@
         <v>78</v>
       </c>
       <c r="D89" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="E89">
         <v>1961</v>
@@ -7985,7 +7985,7 @@
         <v>78</v>
       </c>
       <c r="D91" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="E91">
         <v>1984</v>
@@ -8038,7 +8038,7 @@
         <v>78</v>
       </c>
       <c r="D92" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="E92">
         <v>1985</v>
@@ -8091,7 +8091,7 @@
         <v>78</v>
       </c>
       <c r="D93" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E93">
         <v>1983</v>
@@ -8144,7 +8144,7 @@
         <v>78</v>
       </c>
       <c r="D94" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E94">
         <v>1956</v>
@@ -8197,7 +8197,7 @@
         <v>78</v>
       </c>
       <c r="D95" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E95">
         <v>1977</v>
@@ -8250,7 +8250,7 @@
         <v>78</v>
       </c>
       <c r="D96" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E96">
         <v>1973</v>
@@ -8303,7 +8303,7 @@
         <v>78</v>
       </c>
       <c r="D97" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E97">
         <v>1935</v>
@@ -8356,7 +8356,7 @@
         <v>78</v>
       </c>
       <c r="D98" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="E98">
         <v>1956</v>
@@ -8462,7 +8462,7 @@
         <v>78</v>
       </c>
       <c r="D100" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E100">
         <v>1958</v>
@@ -8621,7 +8621,7 @@
         <v>78</v>
       </c>
       <c r="D103" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E103">
         <v>1964</v>
@@ -15299,13 +15299,13 @@
         <v>138</v>
       </c>
       <c r="D229" t="s">
-        <v>23</v>
+        <v>364</v>
       </c>
       <c r="E229">
         <v>2021</v>
       </c>
       <c r="F229">
-        <v>1.9E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="G229">
         <v>1</v>
@@ -15352,13 +15352,13 @@
         <v>138</v>
       </c>
       <c r="D230" t="s">
-        <v>364</v>
+        <v>23</v>
       </c>
       <c r="E230">
         <v>2021</v>
       </c>
       <c r="F230">
-        <v>2.5000000000000001E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="G230">
         <v>1</v>
@@ -15617,13 +15617,13 @@
         <v>138</v>
       </c>
       <c r="D235" t="s">
-        <v>367</v>
+        <v>46</v>
       </c>
       <c r="E235">
         <v>2025</v>
       </c>
       <c r="F235">
-        <v>3.6999999999999998E-2</v>
+        <v>2.0799999999999999E-2</v>
       </c>
       <c r="G235">
         <v>1</v>
@@ -15670,13 +15670,13 @@
         <v>138</v>
       </c>
       <c r="D236" t="s">
-        <v>46</v>
+        <v>367</v>
       </c>
       <c r="E236">
         <v>2025</v>
       </c>
       <c r="F236">
-        <v>2.0799999999999999E-2</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="G236">
         <v>1</v>
@@ -15776,13 +15776,13 @@
         <v>138</v>
       </c>
       <c r="D238" t="s">
-        <v>46</v>
+        <v>369</v>
       </c>
       <c r="E238">
         <v>2028</v>
       </c>
       <c r="F238">
-        <v>2.4E-2</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="G238">
         <v>1</v>
@@ -15808,13 +15808,13 @@
         <v>138</v>
       </c>
       <c r="D239" t="s">
-        <v>369</v>
+        <v>46</v>
       </c>
       <c r="E239">
         <v>2028</v>
       </c>
       <c r="F239">
-        <v>4.9000000000000002E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="G239">
         <v>1</v>

--- a/VerveStacks_NZL_grids/vt_vervestacks_NZL_v1.xlsx
+++ b/VerveStacks_NZL_grids/vt_vervestacks_NZL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{50012E06-1139-4613-8335-A082F8BC6623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2F747D3-17F7-48A8-A352-1EC39D36989E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{171C3F22-0E79-4AC4-B1BD-94BDDD2385EC}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{61B3CB9E-DC8F-4627-AB98-8162314E0788}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -108,12 +108,12 @@
     <t>gas</t>
   </si>
   <si>
+    <t>e_w188180344-220</t>
+  </si>
+  <si>
     <t>e_r17609399-220</t>
   </si>
   <si>
-    <t>e_w188180344-220</t>
-  </si>
-  <si>
     <t>ep_gas_combined_cycle_G100000407351</t>
   </si>
   <si>
@@ -276,63 +276,63 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_NZ22-220</t>
+  </si>
+  <si>
+    <t>e_NZ40-220</t>
+  </si>
+  <si>
+    <t>e_NZ35-220</t>
+  </si>
+  <si>
+    <t>e_w180514007-220</t>
+  </si>
+  <si>
+    <t>e_w89664063-220</t>
+  </si>
+  <si>
+    <t>e_w89637173-220</t>
+  </si>
+  <si>
+    <t>e_NZ30-220</t>
+  </si>
+  <si>
+    <t>e_w89411122-220</t>
+  </si>
+  <si>
+    <t>e_w89637174-220</t>
+  </si>
+  <si>
+    <t>e_w89636266-220</t>
+  </si>
+  <si>
+    <t>e_w272522517-220</t>
+  </si>
+  <si>
+    <t>e_NZ14-220</t>
+  </si>
+  <si>
+    <t>e_NZ12-220</t>
+  </si>
+  <si>
     <t>e_w270018358-220</t>
   </si>
   <si>
     <t>e_NZ11-220</t>
   </si>
   <si>
-    <t>e_NZ35-220</t>
+    <t>e_NZ33-220</t>
   </si>
   <si>
     <t>e_NZ13-220</t>
   </si>
   <si>
-    <t>e_NZ33-220</t>
-  </si>
-  <si>
-    <t>e_w89411122-220</t>
+    <t>e_w93556808-220</t>
   </si>
   <si>
     <t>e_w412589726-220</t>
   </si>
   <si>
-    <t>e_NZ40-220</t>
-  </si>
-  <si>
-    <t>e_w89664063-220</t>
-  </si>
-  <si>
-    <t>e_w180514007-220</t>
-  </si>
-  <si>
-    <t>e_w93556808-220</t>
-  </si>
-  <si>
-    <t>e_w89637173-220</t>
-  </si>
-  <si>
-    <t>e_NZ30-220</t>
-  </si>
-  <si>
-    <t>e_w89637174-220</t>
-  </si>
-  <si>
-    <t>e_w89636266-220</t>
-  </si>
-  <si>
-    <t>e_w272522517-220</t>
-  </si>
-  <si>
-    <t>e_NZ14-220</t>
-  </si>
-  <si>
-    <t>e_NZ12-220</t>
-  </si>
-  <si>
-    <t>e_NZ22-220</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000602849</t>
   </si>
   <si>
@@ -1260,15 +1260,15 @@
     <t>Huntly power station_4</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/188180344-220_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/167293888-220_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - relation/17609399-220_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/167293888-220_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/188180344-220_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Stratford power station_CC1</t>
   </si>
   <si>
@@ -1386,66 +1386,66 @@
     <t>Wairakei geothermal power plant_A</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - NZ11-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/93556808-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89637174-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/180514007-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/412589726-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89411122-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89664063-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/87928925-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ35-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ40-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ13-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89636266-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/270018358-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ33-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/272522517-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ30-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89637173-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ12-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - NZ22-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/89636266-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ13-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/272522517-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ30-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89637173-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ33-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/87928925-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ35-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - NZ14-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - NZ40-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/270018358-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ12-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89664063-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/412589726-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89411122-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/93556808-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ11-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89637174-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/180514007-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Arapuni hydroelectric plant_</t>
   </si>
   <si>
@@ -1629,13 +1629,13 @@
     <t>ccs retrofit of -- Glenbrook power station_1</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/188180344-220_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/167293888-220_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - relation/17609399-220_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/188180344-220_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/167293888-220_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- McKee power station_2</t>
@@ -2027,7 +2027,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BD46AF1-40A4-4A17-ABA1-EAFFF2DF7114}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE096827-12C8-437A-A7F1-AA9D4E3DAF24}">
   <dimension ref="B9:T38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2271,7 +2271,7 @@
         <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E14">
         <v>0.45937499999999998</v>
@@ -2327,7 +2327,7 @@
         <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E15">
         <v>0.4375</v>
@@ -2439,7 +2439,7 @@
         <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E17">
         <v>0.37624999999999997</v>
@@ -2495,7 +2495,7 @@
         <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E18">
         <v>0.50749999999999995</v>
@@ -2607,7 +2607,7 @@
         <v>22</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E20">
         <v>0.50749999999999995</v>
@@ -2663,7 +2663,7 @@
         <v>22</v>
       </c>
       <c r="D21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E21">
         <v>0.26250000000000001</v>
@@ -2719,7 +2719,7 @@
         <v>22</v>
       </c>
       <c r="D22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E22">
         <v>0.26250000000000001</v>
@@ -2775,7 +2775,7 @@
         <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E23">
         <v>0.27124999999999999</v>
@@ -2831,7 +2831,7 @@
         <v>22</v>
       </c>
       <c r="D24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E24">
         <v>0.27124999999999999</v>
@@ -2887,7 +2887,7 @@
         <v>22</v>
       </c>
       <c r="D25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E25">
         <v>0.26250000000000001</v>
@@ -2943,7 +2943,7 @@
         <v>22</v>
       </c>
       <c r="D26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E26">
         <v>0.26250000000000001</v>
@@ -3055,7 +3055,7 @@
         <v>126</v>
       </c>
       <c r="D28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E28">
         <v>0.4375</v>
@@ -3111,7 +3111,7 @@
         <v>126</v>
       </c>
       <c r="D29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E29">
         <v>0.42</v>
@@ -3223,7 +3223,7 @@
         <v>126</v>
       </c>
       <c r="D31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E31">
         <v>0.35875000000000001</v>
@@ -3279,7 +3279,7 @@
         <v>126</v>
       </c>
       <c r="D32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E32">
         <v>0.25374999999999998</v>
@@ -3335,7 +3335,7 @@
         <v>126</v>
       </c>
       <c r="D33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E33">
         <v>0.25374999999999998</v>
@@ -3391,7 +3391,7 @@
         <v>126</v>
       </c>
       <c r="D34" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E34">
         <v>0.26250000000000001</v>
@@ -3447,7 +3447,7 @@
         <v>126</v>
       </c>
       <c r="D35" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E35">
         <v>0.26250000000000001</v>
@@ -3503,7 +3503,7 @@
         <v>126</v>
       </c>
       <c r="D36" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E36">
         <v>0.25374999999999998</v>
@@ -3559,7 +3559,7 @@
         <v>126</v>
       </c>
       <c r="D37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E37">
         <v>0.25374999999999998</v>
@@ -3669,7 +3669,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87C32617-3D75-4CD7-8D84-2C5AF131ED18}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E0B82F8-4E26-43F5-A2D5-8F6D804CB601}">
   <dimension ref="B9:T260"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4016,19 +4016,19 @@
         <v>2022</v>
       </c>
       <c r="F16">
-        <v>0.29931763879128592</v>
+        <v>3.9117357695010534E-2</v>
       </c>
       <c r="G16">
-        <v>0.57999999999999996</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H16">
-        <v>1150</v>
+        <v>1350</v>
       </c>
       <c r="I16">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J16">
-        <v>3.3000000000000003</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="K16">
         <v>50</v>
@@ -4063,25 +4063,25 @@
         <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E17">
         <v>2022</v>
       </c>
       <c r="F17">
-        <v>3.9117357695010534E-2</v>
+        <v>0.1585650035137034</v>
       </c>
       <c r="G17">
-        <v>0.56000000000000005</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H17">
-        <v>1350</v>
+        <v>1150</v>
       </c>
       <c r="I17">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="J17">
-        <v>3.5999999999999996</v>
+        <v>3.3000000000000003</v>
       </c>
       <c r="K17">
         <v>50</v>
@@ -4116,13 +4116,13 @@
         <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E18">
         <v>2022</v>
       </c>
       <c r="F18">
-        <v>0.1585650035137034</v>
+        <v>0.29931763879128592</v>
       </c>
       <c r="G18">
         <v>0.57999999999999996</v>
@@ -4169,7 +4169,7 @@
         <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E19">
         <v>1998</v>
@@ -4222,7 +4222,7 @@
         <v>22</v>
       </c>
       <c r="D20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E20">
         <v>1996</v>
@@ -4328,7 +4328,7 @@
         <v>22</v>
       </c>
       <c r="D22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E22">
         <v>1987</v>
@@ -4381,7 +4381,7 @@
         <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E23">
         <v>2013</v>
@@ -4434,7 +4434,7 @@
         <v>22</v>
       </c>
       <c r="D24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E24">
         <v>2013</v>
@@ -4487,7 +4487,7 @@
         <v>22</v>
       </c>
       <c r="D25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E25">
         <v>2011</v>
@@ -4540,7 +4540,7 @@
         <v>22</v>
       </c>
       <c r="D26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E26">
         <v>2011</v>
@@ -4593,7 +4593,7 @@
         <v>22</v>
       </c>
       <c r="D27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E27">
         <v>2020</v>
@@ -4646,7 +4646,7 @@
         <v>22</v>
       </c>
       <c r="D28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E28">
         <v>2020</v>
@@ -6401,13 +6401,13 @@
         <v>2022</v>
       </c>
       <c r="F61">
-        <v>1.2898645876077145E-2</v>
+        <v>1.9844070578580224E-2</v>
       </c>
       <c r="G61">
         <v>1</v>
       </c>
       <c r="H61">
-        <v>3375.0000000000005</v>
+        <v>3375</v>
       </c>
       <c r="I61">
         <v>65</v>
@@ -6454,19 +6454,19 @@
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>1.5875256462864178E-2</v>
+        <v>7.1438654082888797E-2</v>
       </c>
       <c r="G62">
         <v>1</v>
       </c>
       <c r="H62">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I62">
-        <v>65</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J62">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K62">
         <v>100</v>
@@ -6560,19 +6560,19 @@
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>1.3229380385720147E-2</v>
+        <v>5.291752154288059E-2</v>
       </c>
       <c r="G64">
         <v>1</v>
       </c>
       <c r="H64">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I64">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J64">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K64">
         <v>100</v>
@@ -6613,19 +6613,19 @@
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>4.365695527287649E-2</v>
+        <v>8.9298317603610997E-2</v>
       </c>
       <c r="G65">
         <v>1</v>
       </c>
       <c r="H65">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I65">
-        <v>65</v>
+        <v>55.000000000000014</v>
       </c>
       <c r="J65">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K65">
         <v>100</v>
@@ -6666,7 +6666,7 @@
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>3.9688141157160448E-2</v>
+        <v>1.7363561756257695E-2</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -6713,25 +6713,25 @@
         <v>78</v>
       </c>
       <c r="D67" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="E67">
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>5.8209273697168655E-2</v>
+        <v>2.6458760771440295E-2</v>
       </c>
       <c r="G67">
         <v>1</v>
       </c>
       <c r="H67">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I67">
-        <v>55.000000000000007</v>
+        <v>65</v>
       </c>
       <c r="J67">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K67">
         <v>100</v>
@@ -6766,25 +6766,25 @@
         <v>78</v>
       </c>
       <c r="D68" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E68">
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>0.16073697168649981</v>
+        <v>3.9688141157160448E-2</v>
       </c>
       <c r="G68">
         <v>1</v>
       </c>
       <c r="H68">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I68">
-        <v>55.000000000000014</v>
+        <v>65</v>
       </c>
       <c r="J68">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K68">
         <v>100</v>
@@ -6819,25 +6819,25 @@
         <v>78</v>
       </c>
       <c r="D69" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E69">
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>7.1438654082888797E-2</v>
+        <v>3.6380796060730414E-2</v>
       </c>
       <c r="G69">
         <v>1</v>
       </c>
       <c r="H69">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I69">
-        <v>55.000000000000007</v>
+        <v>65</v>
       </c>
       <c r="J69">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K69">
         <v>100</v>
@@ -6872,25 +6872,25 @@
         <v>78</v>
       </c>
       <c r="D70" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E70">
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>8.9298317603610997E-2</v>
+        <v>3.5057858022158397E-2</v>
       </c>
       <c r="G70">
         <v>1</v>
       </c>
       <c r="H70">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I70">
-        <v>55.000000000000014</v>
+        <v>65</v>
       </c>
       <c r="J70">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K70">
         <v>100</v>
@@ -6925,25 +6925,25 @@
         <v>78</v>
       </c>
       <c r="D71" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E71">
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>5.291752154288059E-2</v>
+        <v>1.7528929011079199E-2</v>
       </c>
       <c r="G71">
         <v>1</v>
       </c>
       <c r="H71">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I71">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="J71">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K71">
         <v>100</v>
@@ -6978,13 +6978,13 @@
         <v>78</v>
       </c>
       <c r="D72" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E72">
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>1.2237176856791137E-2</v>
+        <v>2.1001641362330736E-2</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -7031,13 +7031,13 @@
         <v>78</v>
       </c>
       <c r="D73" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E73">
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>1.7363561756257695E-2</v>
+        <v>2.7120229790726307E-2</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -7049,7 +7049,7 @@
         <v>65</v>
       </c>
       <c r="J73">
-        <v>2.4</v>
+        <v>2.3999999999999995</v>
       </c>
       <c r="K73">
         <v>100</v>
@@ -7084,19 +7084,19 @@
         <v>78</v>
       </c>
       <c r="D74" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E74">
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>2.6458760771440295E-2</v>
+        <v>1.2898645876077145E-2</v>
       </c>
       <c r="G74">
         <v>1</v>
       </c>
       <c r="H74">
-        <v>3375</v>
+        <v>3375.0000000000005</v>
       </c>
       <c r="I74">
         <v>65</v>
@@ -7137,13 +7137,13 @@
         <v>78</v>
       </c>
       <c r="D75" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E75">
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>3.6380796060730414E-2</v>
+        <v>1.5875256462864178E-2</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -7190,13 +7190,13 @@
         <v>78</v>
       </c>
       <c r="D76" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E76">
         <v>2022</v>
       </c>
       <c r="F76">
-        <v>3.5057858022158397E-2</v>
+        <v>4.365695527287649E-2</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -7243,13 +7243,13 @@
         <v>78</v>
       </c>
       <c r="D77" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E77">
         <v>2022</v>
       </c>
       <c r="F77">
-        <v>1.7528929011079199E-2</v>
+        <v>1.3229380385720147E-2</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -7296,13 +7296,13 @@
         <v>78</v>
       </c>
       <c r="D78" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E78">
         <v>2022</v>
       </c>
       <c r="F78">
-        <v>2.1001641362330736E-2</v>
+        <v>1.2237176856791137E-2</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -7349,25 +7349,25 @@
         <v>78</v>
       </c>
       <c r="D79" t="s">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="E79">
         <v>2022</v>
       </c>
       <c r="F79">
-        <v>2.7120229790726307E-2</v>
+        <v>5.8209273697168655E-2</v>
       </c>
       <c r="G79">
         <v>1</v>
       </c>
       <c r="H79">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I79">
-        <v>65</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J79">
-        <v>2.3999999999999995</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K79">
         <v>100</v>
@@ -7408,19 +7408,19 @@
         <v>2022</v>
       </c>
       <c r="F80">
-        <v>1.9844070578580224E-2</v>
+        <v>0.16073697168649981</v>
       </c>
       <c r="G80">
         <v>1</v>
       </c>
       <c r="H80">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I80">
-        <v>65</v>
+        <v>55.000000000000014</v>
       </c>
       <c r="J80">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K80">
         <v>100</v>
@@ -7455,7 +7455,7 @@
         <v>78</v>
       </c>
       <c r="D81" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E81">
         <v>1929</v>
@@ -7508,7 +7508,7 @@
         <v>78</v>
       </c>
       <c r="D82" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E82">
         <v>1968</v>
@@ -7561,7 +7561,7 @@
         <v>78</v>
       </c>
       <c r="D83" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E83">
         <v>1965</v>
@@ -7614,7 +7614,7 @@
         <v>78</v>
       </c>
       <c r="D84" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E84">
         <v>1992</v>
@@ -7667,7 +7667,7 @@
         <v>78</v>
       </c>
       <c r="D85" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E85">
         <v>1948</v>
@@ -7720,7 +7720,7 @@
         <v>78</v>
       </c>
       <c r="D86" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E86">
         <v>1972</v>
@@ -7879,7 +7879,7 @@
         <v>78</v>
       </c>
       <c r="D89" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E89">
         <v>1961</v>
@@ -7932,7 +7932,7 @@
         <v>78</v>
       </c>
       <c r="D90" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="E90">
         <v>1979</v>
@@ -8038,7 +8038,7 @@
         <v>78</v>
       </c>
       <c r="D92" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E92">
         <v>1985</v>
@@ -8091,7 +8091,7 @@
         <v>78</v>
       </c>
       <c r="D93" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="E93">
         <v>1983</v>
@@ -8144,7 +8144,7 @@
         <v>78</v>
       </c>
       <c r="D94" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E94">
         <v>1956</v>
@@ -8197,7 +8197,7 @@
         <v>78</v>
       </c>
       <c r="D95" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E95">
         <v>1977</v>
@@ -8250,7 +8250,7 @@
         <v>78</v>
       </c>
       <c r="D96" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E96">
         <v>1973</v>
@@ -8303,7 +8303,7 @@
         <v>78</v>
       </c>
       <c r="D97" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E97">
         <v>1935</v>
@@ -8356,7 +8356,7 @@
         <v>78</v>
       </c>
       <c r="D98" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E98">
         <v>1956</v>
@@ -8409,7 +8409,7 @@
         <v>78</v>
       </c>
       <c r="D99" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="E99">
         <v>1967</v>
@@ -8462,7 +8462,7 @@
         <v>78</v>
       </c>
       <c r="D100" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E100">
         <v>1958</v>
@@ -8621,7 +8621,7 @@
         <v>78</v>
       </c>
       <c r="D103" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="E103">
         <v>1964</v>
@@ -8727,7 +8727,7 @@
         <v>126</v>
       </c>
       <c r="D105" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E105">
         <v>1998</v>
@@ -8780,7 +8780,7 @@
         <v>126</v>
       </c>
       <c r="D106" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E106">
         <v>1996</v>
@@ -8886,7 +8886,7 @@
         <v>126</v>
       </c>
       <c r="D108" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E108">
         <v>1987</v>
@@ -8939,7 +8939,7 @@
         <v>126</v>
       </c>
       <c r="D109" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E109">
         <v>2013</v>
@@ -8992,7 +8992,7 @@
         <v>126</v>
       </c>
       <c r="D110" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E110">
         <v>2013</v>
@@ -9045,7 +9045,7 @@
         <v>126</v>
       </c>
       <c r="D111" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E111">
         <v>2011</v>
@@ -9098,7 +9098,7 @@
         <v>126</v>
       </c>
       <c r="D112" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E112">
         <v>2011</v>
@@ -9151,7 +9151,7 @@
         <v>126</v>
       </c>
       <c r="D113" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E113">
         <v>2020</v>
@@ -9204,7 +9204,7 @@
         <v>126</v>
       </c>
       <c r="D114" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E114">
         <v>2020</v>
@@ -15299,13 +15299,13 @@
         <v>138</v>
       </c>
       <c r="D229" t="s">
-        <v>364</v>
+        <v>24</v>
       </c>
       <c r="E229">
         <v>2021</v>
       </c>
       <c r="F229">
-        <v>2.5000000000000001E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="G229">
         <v>1</v>
@@ -15352,13 +15352,13 @@
         <v>138</v>
       </c>
       <c r="D230" t="s">
-        <v>23</v>
+        <v>364</v>
       </c>
       <c r="E230">
         <v>2021</v>
       </c>
       <c r="F230">
-        <v>1.9E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="G230">
         <v>1</v>
@@ -15405,13 +15405,13 @@
         <v>138</v>
       </c>
       <c r="D231" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="E231">
         <v>2023</v>
       </c>
       <c r="F231">
-        <v>3.9E-2</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="G231">
         <v>1</v>
@@ -15458,13 +15458,13 @@
         <v>138</v>
       </c>
       <c r="D232" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="E232">
         <v>2023</v>
       </c>
       <c r="F232">
-        <v>3.0999999999999999E-3</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G232">
         <v>1</v>
@@ -15617,13 +15617,13 @@
         <v>138</v>
       </c>
       <c r="D235" t="s">
-        <v>46</v>
+        <v>367</v>
       </c>
       <c r="E235">
         <v>2025</v>
       </c>
       <c r="F235">
-        <v>2.0799999999999999E-2</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="G235">
         <v>1</v>
@@ -15670,13 +15670,13 @@
         <v>138</v>
       </c>
       <c r="D236" t="s">
-        <v>367</v>
+        <v>46</v>
       </c>
       <c r="E236">
         <v>2025</v>
       </c>
       <c r="F236">
-        <v>3.6999999999999998E-2</v>
+        <v>2.0799999999999999E-2</v>
       </c>
       <c r="G236">
         <v>1</v>

--- a/VerveStacks_NZL_grids/vt_vervestacks_NZL_v1.xlsx
+++ b/VerveStacks_NZL_grids/vt_vervestacks_NZL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2F747D3-17F7-48A8-A352-1EC39D36989E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EF475C5-8E8B-4C99-B700-3CA892AB5E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{61B3CB9E-DC8F-4627-AB98-8162314E0788}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2C983A29-9CB4-4DC4-89DF-741AECAC25C5}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -276,63 +276,63 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_NZ40-220</t>
+  </si>
+  <si>
+    <t>e_NZ30-220</t>
+  </si>
+  <si>
     <t>e_NZ22-220</t>
   </si>
   <si>
-    <t>e_NZ40-220</t>
+    <t>e_w412589726-220</t>
+  </si>
+  <si>
+    <t>e_w89664063-220</t>
+  </si>
+  <si>
+    <t>e_w180514007-220</t>
+  </si>
+  <si>
+    <t>e_w89637174-220</t>
+  </si>
+  <si>
+    <t>e_w89636266-220</t>
+  </si>
+  <si>
+    <t>e_w272522517-220</t>
+  </si>
+  <si>
+    <t>e_NZ14-220</t>
+  </si>
+  <si>
+    <t>e_NZ12-220</t>
+  </si>
+  <si>
+    <t>e_NZ33-220</t>
+  </si>
+  <si>
+    <t>e_NZ13-220</t>
   </si>
   <si>
     <t>e_NZ35-220</t>
   </si>
   <si>
-    <t>e_w180514007-220</t>
-  </si>
-  <si>
-    <t>e_w89664063-220</t>
+    <t>e_NZ11-220</t>
+  </si>
+  <si>
+    <t>e_w89411122-220</t>
+  </si>
+  <si>
+    <t>e_w93556808-220</t>
+  </si>
+  <si>
+    <t>e_w270018358-220</t>
   </si>
   <si>
     <t>e_w89637173-220</t>
   </si>
   <si>
-    <t>e_NZ30-220</t>
-  </si>
-  <si>
-    <t>e_w89411122-220</t>
-  </si>
-  <si>
-    <t>e_w89637174-220</t>
-  </si>
-  <si>
-    <t>e_w89636266-220</t>
-  </si>
-  <si>
-    <t>e_w272522517-220</t>
-  </si>
-  <si>
-    <t>e_NZ14-220</t>
-  </si>
-  <si>
-    <t>e_NZ12-220</t>
-  </si>
-  <si>
-    <t>e_w270018358-220</t>
-  </si>
-  <si>
-    <t>e_NZ11-220</t>
-  </si>
-  <si>
-    <t>e_NZ33-220</t>
-  </si>
-  <si>
-    <t>e_NZ13-220</t>
-  </si>
-  <si>
-    <t>e_w93556808-220</t>
-  </si>
-  <si>
-    <t>e_w412589726-220</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000602849</t>
   </si>
   <si>
@@ -1260,15 +1260,15 @@
     <t>Huntly power station_4</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - relation/17609399-220_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/167293888-220_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/188180344-220_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/167293888-220_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - relation/17609399-220_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Stratford power station_CC1</t>
   </si>
   <si>
@@ -1386,66 +1386,66 @@
     <t>Wairakei geothermal power plant_A</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/89637174-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/180514007-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/272522517-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89637173-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ33-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ30-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/87928925-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89411122-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89664063-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/412589726-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89636266-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - NZ11-220_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - way/93556808-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/89637174-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/180514007-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/412589726-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89411122-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89664063-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/87928925-220_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - NZ22-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ13-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/270018358-220_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - NZ35-220_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - NZ14-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - NZ40-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - NZ13-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89636266-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/270018358-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ33-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/272522517-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ30-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89637173-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - NZ12-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - NZ22-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ14-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Arapuni hydroelectric plant_</t>
   </si>
   <si>
@@ -1632,10 +1632,10 @@
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/188180344-220_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - relation/17609399-220_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/167293888-220_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - relation/17609399-220_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- McKee power station_2</t>
@@ -2027,7 +2027,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE096827-12C8-437A-A7F1-AA9D4E3DAF24}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{594B762B-28C1-4845-8927-498DF5F977E1}">
   <dimension ref="B9:T38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2495,7 +2495,7 @@
         <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E18">
         <v>0.50749999999999995</v>
@@ -2607,7 +2607,7 @@
         <v>22</v>
       </c>
       <c r="D20" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E20">
         <v>0.50749999999999995</v>
@@ -3669,7 +3669,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E0B82F8-4E26-43F5-A2D5-8F6D804CB601}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1871AB3-C914-4EB6-A58B-91560C9DE3F2}">
   <dimension ref="B9:T260"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4063,13 +4063,13 @@
         <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E17">
         <v>2022</v>
       </c>
       <c r="F17">
-        <v>0.1585650035137034</v>
+        <v>0.29931763879128592</v>
       </c>
       <c r="G17">
         <v>0.57999999999999996</v>
@@ -4116,13 +4116,13 @@
         <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E18">
         <v>2022</v>
       </c>
       <c r="F18">
-        <v>0.29931763879128592</v>
+        <v>0.1585650035137034</v>
       </c>
       <c r="G18">
         <v>0.57999999999999996</v>
@@ -6401,19 +6401,19 @@
         <v>2022</v>
       </c>
       <c r="F61">
-        <v>1.9844070578580224E-2</v>
+        <v>7.1438654082888797E-2</v>
       </c>
       <c r="G61">
         <v>1</v>
       </c>
       <c r="H61">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I61">
-        <v>65</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J61">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K61">
         <v>100</v>
@@ -6454,19 +6454,19 @@
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>7.1438654082888797E-2</v>
+        <v>2.6458760771440295E-2</v>
       </c>
       <c r="G62">
         <v>1</v>
       </c>
       <c r="H62">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I62">
-        <v>55.000000000000007</v>
+        <v>65</v>
       </c>
       <c r="J62">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K62">
         <v>100</v>
@@ -6507,7 +6507,7 @@
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>3.5057858022158397E-2</v>
+        <v>1.9844070578580224E-2</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -6560,7 +6560,7 @@
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>5.291752154288059E-2</v>
+        <v>0.16073697168649981</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -6569,7 +6569,7 @@
         <v>2875</v>
       </c>
       <c r="I64">
-        <v>55</v>
+        <v>55.000000000000014</v>
       </c>
       <c r="J64">
         <v>2.2000000000000002</v>
@@ -6607,13 +6607,13 @@
         <v>78</v>
       </c>
       <c r="D65" t="s">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="E65">
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>8.9298317603610997E-2</v>
+        <v>5.8209273697168655E-2</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -6622,7 +6622,7 @@
         <v>2875</v>
       </c>
       <c r="I65">
-        <v>55.000000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J65">
         <v>2.2000000000000002</v>
@@ -6660,25 +6660,25 @@
         <v>78</v>
       </c>
       <c r="D66" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E66">
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>1.7363561756257695E-2</v>
+        <v>8.9298317603610997E-2</v>
       </c>
       <c r="G66">
         <v>1</v>
       </c>
       <c r="H66">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I66">
-        <v>65</v>
+        <v>55.000000000000014</v>
       </c>
       <c r="J66">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K66">
         <v>100</v>
@@ -6713,25 +6713,25 @@
         <v>78</v>
       </c>
       <c r="D67" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E67">
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>2.6458760771440295E-2</v>
+        <v>5.291752154288059E-2</v>
       </c>
       <c r="G67">
         <v>1</v>
       </c>
       <c r="H67">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I67">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J67">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K67">
         <v>100</v>
@@ -6766,13 +6766,13 @@
         <v>78</v>
       </c>
       <c r="D68" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E68">
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>3.9688141157160448E-2</v>
+        <v>3.6380796060730414E-2</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -6819,13 +6819,13 @@
         <v>78</v>
       </c>
       <c r="D69" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E69">
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>3.6380796060730414E-2</v>
+        <v>3.5057858022158397E-2</v>
       </c>
       <c r="G69">
         <v>1</v>
@@ -6872,13 +6872,13 @@
         <v>78</v>
       </c>
       <c r="D70" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E70">
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>3.5057858022158397E-2</v>
+        <v>1.7528929011079199E-2</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -6925,13 +6925,13 @@
         <v>78</v>
       </c>
       <c r="D71" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E71">
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>1.7528929011079199E-2</v>
+        <v>2.1001641362330736E-2</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -6978,13 +6978,13 @@
         <v>78</v>
       </c>
       <c r="D72" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E72">
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>2.1001641362330736E-2</v>
+        <v>2.7120229790726307E-2</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -6996,7 +6996,7 @@
         <v>65</v>
       </c>
       <c r="J72">
-        <v>2.4</v>
+        <v>2.3999999999999995</v>
       </c>
       <c r="K72">
         <v>100</v>
@@ -7031,13 +7031,13 @@
         <v>78</v>
       </c>
       <c r="D73" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E73">
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>2.7120229790726307E-2</v>
+        <v>4.365695527287649E-2</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -7049,7 +7049,7 @@
         <v>65</v>
       </c>
       <c r="J73">
-        <v>2.3999999999999995</v>
+        <v>2.4</v>
       </c>
       <c r="K73">
         <v>100</v>
@@ -7084,19 +7084,19 @@
         <v>78</v>
       </c>
       <c r="D74" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E74">
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>1.2898645876077145E-2</v>
+        <v>1.3229380385720147E-2</v>
       </c>
       <c r="G74">
         <v>1</v>
       </c>
       <c r="H74">
-        <v>3375.0000000000005</v>
+        <v>3375</v>
       </c>
       <c r="I74">
         <v>65</v>
@@ -7137,13 +7137,13 @@
         <v>78</v>
       </c>
       <c r="D75" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E75">
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>1.5875256462864178E-2</v>
+        <v>3.5057858022158397E-2</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -7190,13 +7190,13 @@
         <v>78</v>
       </c>
       <c r="D76" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E76">
         <v>2022</v>
       </c>
       <c r="F76">
-        <v>4.365695527287649E-2</v>
+        <v>1.5875256462864178E-2</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -7243,13 +7243,13 @@
         <v>78</v>
       </c>
       <c r="D77" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E77">
         <v>2022</v>
       </c>
       <c r="F77">
-        <v>1.3229380385720147E-2</v>
+        <v>3.9688141157160448E-2</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -7296,7 +7296,7 @@
         <v>78</v>
       </c>
       <c r="D78" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E78">
         <v>2022</v>
@@ -7349,25 +7349,25 @@
         <v>78</v>
       </c>
       <c r="D79" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="E79">
         <v>2022</v>
       </c>
       <c r="F79">
-        <v>5.8209273697168655E-2</v>
+        <v>1.2898645876077145E-2</v>
       </c>
       <c r="G79">
         <v>1</v>
       </c>
       <c r="H79">
-        <v>2875</v>
+        <v>3375.0000000000005</v>
       </c>
       <c r="I79">
-        <v>55.000000000000007</v>
+        <v>65</v>
       </c>
       <c r="J79">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K79">
         <v>100</v>
@@ -7408,19 +7408,19 @@
         <v>2022</v>
       </c>
       <c r="F80">
-        <v>0.16073697168649981</v>
+        <v>1.7363561756257695E-2</v>
       </c>
       <c r="G80">
         <v>1</v>
       </c>
       <c r="H80">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I80">
-        <v>55.000000000000014</v>
+        <v>65</v>
       </c>
       <c r="J80">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K80">
         <v>100</v>
@@ -7455,7 +7455,7 @@
         <v>78</v>
       </c>
       <c r="D81" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E81">
         <v>1929</v>
@@ -7508,7 +7508,7 @@
         <v>78</v>
       </c>
       <c r="D82" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E82">
         <v>1968</v>
@@ -7614,7 +7614,7 @@
         <v>78</v>
       </c>
       <c r="D84" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E84">
         <v>1992</v>
@@ -7720,7 +7720,7 @@
         <v>78</v>
       </c>
       <c r="D86" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="E86">
         <v>1972</v>
@@ -7879,7 +7879,7 @@
         <v>78</v>
       </c>
       <c r="D89" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E89">
         <v>1961</v>
@@ -7932,7 +7932,7 @@
         <v>78</v>
       </c>
       <c r="D90" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E90">
         <v>1979</v>
@@ -7985,7 +7985,7 @@
         <v>78</v>
       </c>
       <c r="D91" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="E91">
         <v>1984</v>
@@ -8038,7 +8038,7 @@
         <v>78</v>
       </c>
       <c r="D92" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E92">
         <v>1985</v>
@@ -8091,7 +8091,7 @@
         <v>78</v>
       </c>
       <c r="D93" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E93">
         <v>1983</v>
@@ -8144,7 +8144,7 @@
         <v>78</v>
       </c>
       <c r="D94" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E94">
         <v>1956</v>
@@ -8197,7 +8197,7 @@
         <v>78</v>
       </c>
       <c r="D95" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E95">
         <v>1977</v>
@@ -8250,7 +8250,7 @@
         <v>78</v>
       </c>
       <c r="D96" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="E96">
         <v>1973</v>
@@ -8303,7 +8303,7 @@
         <v>78</v>
       </c>
       <c r="D97" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="E97">
         <v>1935</v>
@@ -8356,7 +8356,7 @@
         <v>78</v>
       </c>
       <c r="D98" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E98">
         <v>1956</v>
@@ -8409,7 +8409,7 @@
         <v>78</v>
       </c>
       <c r="D99" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E99">
         <v>1967</v>
@@ -8462,7 +8462,7 @@
         <v>78</v>
       </c>
       <c r="D100" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E100">
         <v>1958</v>
@@ -8621,7 +8621,7 @@
         <v>78</v>
       </c>
       <c r="D103" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E103">
         <v>1964</v>
@@ -15299,13 +15299,13 @@
         <v>138</v>
       </c>
       <c r="D229" t="s">
-        <v>24</v>
+        <v>364</v>
       </c>
       <c r="E229">
         <v>2021</v>
       </c>
       <c r="F229">
-        <v>1.9E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="G229">
         <v>1</v>
@@ -15352,13 +15352,13 @@
         <v>138</v>
       </c>
       <c r="D230" t="s">
-        <v>364</v>
+        <v>24</v>
       </c>
       <c r="E230">
         <v>2021</v>
       </c>
       <c r="F230">
-        <v>2.5000000000000001E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="G230">
         <v>1</v>
@@ -15405,13 +15405,13 @@
         <v>138</v>
       </c>
       <c r="D231" t="s">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="E231">
         <v>2023</v>
       </c>
       <c r="F231">
-        <v>3.0999999999999999E-3</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G231">
         <v>1</v>
@@ -15458,13 +15458,13 @@
         <v>138</v>
       </c>
       <c r="D232" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="E232">
         <v>2023</v>
       </c>
       <c r="F232">
-        <v>3.9E-2</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="G232">
         <v>1</v>
@@ -15776,13 +15776,13 @@
         <v>138</v>
       </c>
       <c r="D238" t="s">
-        <v>369</v>
+        <v>46</v>
       </c>
       <c r="E238">
         <v>2028</v>
       </c>
       <c r="F238">
-        <v>4.9000000000000002E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="G238">
         <v>1</v>
@@ -15808,13 +15808,13 @@
         <v>138</v>
       </c>
       <c r="D239" t="s">
-        <v>46</v>
+        <v>369</v>
       </c>
       <c r="E239">
         <v>2028</v>
       </c>
       <c r="F239">
-        <v>2.4E-2</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="G239">
         <v>1</v>

--- a/VerveStacks_NZL_grids/vt_vervestacks_NZL_v1.xlsx
+++ b/VerveStacks_NZL_grids/vt_vervestacks_NZL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDA66730-8100-46B0-9F22-5CD2D74C3CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E973508C-2EEB-4E4E-81EE-B64A0E3E6398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CFC6087D-2BC6-4080-87CC-A26A1556E902}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{49DC5754-B12E-44D3-AAA9-719646BFC123}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -108,12 +108,12 @@
     <t>gas</t>
   </si>
   <si>
+    <t>e_w188180344-220</t>
+  </si>
+  <si>
     <t>e_r17609399-220</t>
   </si>
   <si>
-    <t>e_w188180344-220</t>
-  </si>
-  <si>
     <t>ep_gas_combined_cycle_G100000407351</t>
   </si>
   <si>
@@ -276,63 +276,63 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_w89637173-220</t>
+  </si>
+  <si>
+    <t>e_NZ11-220</t>
+  </si>
+  <si>
+    <t>e_w270018358-220</t>
+  </si>
+  <si>
+    <t>e_NZ35-220</t>
+  </si>
+  <si>
+    <t>e_NZ30-220</t>
+  </si>
+  <si>
+    <t>e_w89411122-220</t>
+  </si>
+  <si>
+    <t>e_w89637174-220</t>
+  </si>
+  <si>
+    <t>e_w89636266-220</t>
+  </si>
+  <si>
+    <t>e_NZ40-220</t>
+  </si>
+  <si>
+    <t>e_w412589726-220</t>
+  </si>
+  <si>
+    <t>e_w93556808-220</t>
+  </si>
+  <si>
+    <t>e_NZ13-220</t>
+  </si>
+  <si>
     <t>e_NZ33-220</t>
   </si>
   <si>
-    <t>e_w93556808-220</t>
-  </si>
-  <si>
-    <t>e_w89636266-220</t>
-  </si>
-  <si>
-    <t>e_w89637174-220</t>
-  </si>
-  <si>
-    <t>e_NZ13-220</t>
-  </si>
-  <si>
-    <t>e_w270018358-220</t>
+    <t>e_w272522517-220</t>
+  </si>
+  <si>
+    <t>e_NZ14-220</t>
+  </si>
+  <si>
+    <t>e_NZ12-220</t>
   </si>
   <si>
     <t>e_w180514007-220</t>
   </si>
   <si>
-    <t>e_w89637173-220</t>
-  </si>
-  <si>
-    <t>e_NZ35-220</t>
-  </si>
-  <si>
-    <t>e_NZ40-220</t>
-  </si>
-  <si>
-    <t>e_w412589726-220</t>
-  </si>
-  <si>
-    <t>e_NZ12-220</t>
-  </si>
-  <si>
-    <t>e_NZ14-220</t>
-  </si>
-  <si>
-    <t>e_NZ30-220</t>
+    <t>e_w89664063-220</t>
   </si>
   <si>
     <t>e_NZ22-220</t>
   </si>
   <si>
-    <t>e_w89411122-220</t>
-  </si>
-  <si>
-    <t>e_w89664063-220</t>
-  </si>
-  <si>
-    <t>e_NZ11-220</t>
-  </si>
-  <si>
-    <t>e_w272522517-220</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000602849</t>
   </si>
   <si>
@@ -654,12 +654,12 @@
     <t>Huntly power station_4</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/167293888-220_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - relation/17609399-220_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/167293888-220_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/188180344-220_Missing Gas Capacity</t>
   </si>
   <si>
@@ -780,66 +780,66 @@
     <t>Wairakei geothermal power plant_A</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/89636266-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ22-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ11-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/87928925-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/272522517-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ33-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ30-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89637173-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ14-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ40-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/270018358-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89664063-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89411122-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/412589726-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89637174-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/180514007-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ12-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/93556808-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/89636266-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/412589726-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89664063-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89411122-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ22-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ30-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/87928925-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89637173-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/272522517-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ33-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/270018358-220_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - NZ13-220_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - NZ35-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - NZ40-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ14-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/180514007-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89637174-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ13-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ12-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ11-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Arapuni hydroelectric plant_</t>
   </si>
   <si>
@@ -1023,10 +1023,10 @@
     <t>ccs retrofit of -- Glenbrook power station_1</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/188180344-220_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/167293888-220_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/188180344-220_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - relation/17609399-220_Missing Gas Capacity</t>
@@ -1421,7 +1421,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C54EEE82-1536-4E6B-8324-515B51384916}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E314553E-860B-4090-B39F-0DAB7A95C1BB}">
   <dimension ref="B9:T38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1665,7 +1665,7 @@
         <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E14">
         <v>0.45937499999999998</v>
@@ -1721,7 +1721,7 @@
         <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E15">
         <v>0.4375</v>
@@ -1833,7 +1833,7 @@
         <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E17">
         <v>0.37624999999999997</v>
@@ -1945,7 +1945,7 @@
         <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E19">
         <v>0.50749999999999995</v>
@@ -2001,7 +2001,7 @@
         <v>22</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E20">
         <v>0.50749999999999995</v>
@@ -2057,7 +2057,7 @@
         <v>22</v>
       </c>
       <c r="D21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E21">
         <v>0.26250000000000001</v>
@@ -2113,7 +2113,7 @@
         <v>22</v>
       </c>
       <c r="D22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E22">
         <v>0.26250000000000001</v>
@@ -2169,7 +2169,7 @@
         <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E23">
         <v>0.27124999999999999</v>
@@ -2225,7 +2225,7 @@
         <v>22</v>
       </c>
       <c r="D24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E24">
         <v>0.27124999999999999</v>
@@ -2281,7 +2281,7 @@
         <v>22</v>
       </c>
       <c r="D25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E25">
         <v>0.26250000000000001</v>
@@ -2337,7 +2337,7 @@
         <v>22</v>
       </c>
       <c r="D26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E26">
         <v>0.26250000000000001</v>
@@ -2449,7 +2449,7 @@
         <v>126</v>
       </c>
       <c r="D28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E28">
         <v>0.4375</v>
@@ -2505,7 +2505,7 @@
         <v>126</v>
       </c>
       <c r="D29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E29">
         <v>0.42</v>
@@ -2617,7 +2617,7 @@
         <v>126</v>
       </c>
       <c r="D31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E31">
         <v>0.35875000000000001</v>
@@ -2673,7 +2673,7 @@
         <v>126</v>
       </c>
       <c r="D32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E32">
         <v>0.25374999999999998</v>
@@ -2729,7 +2729,7 @@
         <v>126</v>
       </c>
       <c r="D33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E33">
         <v>0.25374999999999998</v>
@@ -2785,7 +2785,7 @@
         <v>126</v>
       </c>
       <c r="D34" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E34">
         <v>0.26250000000000001</v>
@@ -2841,7 +2841,7 @@
         <v>126</v>
       </c>
       <c r="D35" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E35">
         <v>0.26250000000000001</v>
@@ -2897,7 +2897,7 @@
         <v>126</v>
       </c>
       <c r="D36" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E36">
         <v>0.25374999999999998</v>
@@ -2953,7 +2953,7 @@
         <v>126</v>
       </c>
       <c r="D37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E37">
         <v>0.25374999999999998</v>
@@ -3063,7 +3063,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{180DFD4C-EE46-4317-883B-711148613E7B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6FAE010-BE81-4C51-A04C-2706FEDCA28E}">
   <dimension ref="B9:T149"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3410,19 +3410,19 @@
         <v>2022</v>
       </c>
       <c r="F16">
-        <v>0.29931763879128592</v>
+        <v>3.9117357695010534E-2</v>
       </c>
       <c r="G16">
-        <v>0.57999999999999996</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H16">
-        <v>1150</v>
+        <v>1350</v>
       </c>
       <c r="I16">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J16">
-        <v>3.3000000000000003</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="K16">
         <v>50</v>
@@ -3457,25 +3457,25 @@
         <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E17">
         <v>2022</v>
       </c>
       <c r="F17">
-        <v>3.9117357695010534E-2</v>
+        <v>0.1585650035137034</v>
       </c>
       <c r="G17">
-        <v>0.56000000000000005</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H17">
-        <v>1350</v>
+        <v>1150</v>
       </c>
       <c r="I17">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="J17">
-        <v>3.5999999999999996</v>
+        <v>3.3000000000000003</v>
       </c>
       <c r="K17">
         <v>50</v>
@@ -3510,13 +3510,13 @@
         <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E18">
         <v>2022</v>
       </c>
       <c r="F18">
-        <v>0.1585650035137034</v>
+        <v>0.29931763879128592</v>
       </c>
       <c r="G18">
         <v>0.57999999999999996</v>
@@ -3563,7 +3563,7 @@
         <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E19">
         <v>1998</v>
@@ -3616,7 +3616,7 @@
         <v>22</v>
       </c>
       <c r="D20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E20">
         <v>1996</v>
@@ -3722,7 +3722,7 @@
         <v>22</v>
       </c>
       <c r="D22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E22">
         <v>1987</v>
@@ -3775,7 +3775,7 @@
         <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E23">
         <v>2013</v>
@@ -3828,7 +3828,7 @@
         <v>22</v>
       </c>
       <c r="D24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E24">
         <v>2013</v>
@@ -3881,7 +3881,7 @@
         <v>22</v>
       </c>
       <c r="D25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E25">
         <v>2011</v>
@@ -3934,7 +3934,7 @@
         <v>22</v>
       </c>
       <c r="D26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E26">
         <v>2011</v>
@@ -3987,7 +3987,7 @@
         <v>22</v>
       </c>
       <c r="D27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E27">
         <v>2020</v>
@@ -4040,7 +4040,7 @@
         <v>22</v>
       </c>
       <c r="D28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E28">
         <v>2020</v>
@@ -5795,7 +5795,7 @@
         <v>2022</v>
       </c>
       <c r="F61">
-        <v>4.365695527287649E-2</v>
+        <v>1.7363561756257695E-2</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -5848,7 +5848,7 @@
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>1.2237176856791137E-2</v>
+        <v>1.5875256462864178E-2</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -5901,13 +5901,13 @@
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>3.5057858022158397E-2</v>
+        <v>1.2898645876077145E-2</v>
       </c>
       <c r="G63">
         <v>1</v>
       </c>
       <c r="H63">
-        <v>3375</v>
+        <v>3375.0000000000005</v>
       </c>
       <c r="I63">
         <v>65</v>
@@ -5954,7 +5954,7 @@
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>3.6380796060730414E-2</v>
+        <v>3.5057858022158397E-2</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -6007,7 +6007,7 @@
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>1.3229380385720147E-2</v>
+        <v>2.6458760771440295E-2</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -6060,13 +6060,13 @@
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>1.2898645876077145E-2</v>
+        <v>3.9688141157160448E-2</v>
       </c>
       <c r="G66">
         <v>1</v>
       </c>
       <c r="H66">
-        <v>3375.0000000000005</v>
+        <v>3375</v>
       </c>
       <c r="I66">
         <v>65</v>
@@ -6113,19 +6113,19 @@
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>5.291752154288059E-2</v>
+        <v>3.6380796060730414E-2</v>
       </c>
       <c r="G67">
         <v>1</v>
       </c>
       <c r="H67">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I67">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="J67">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K67">
         <v>100</v>
@@ -6166,7 +6166,7 @@
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>1.7363561756257695E-2</v>
+        <v>3.5057858022158397E-2</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -6219,19 +6219,19 @@
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>3.5057858022158397E-2</v>
+        <v>7.1438654082888797E-2</v>
       </c>
       <c r="G69">
         <v>1</v>
       </c>
       <c r="H69">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I69">
-        <v>65</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J69">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K69">
         <v>100</v>
@@ -6272,7 +6272,7 @@
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>7.1438654082888797E-2</v>
+        <v>0.16073697168649981</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -6281,7 +6281,7 @@
         <v>2875</v>
       </c>
       <c r="I70">
-        <v>55.000000000000007</v>
+        <v>55.000000000000014</v>
       </c>
       <c r="J70">
         <v>2.2000000000000002</v>
@@ -6319,13 +6319,13 @@
         <v>78</v>
       </c>
       <c r="D71" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="E71">
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>0.16073697168649981</v>
+        <v>5.8209273697168655E-2</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -6334,7 +6334,7 @@
         <v>2875</v>
       </c>
       <c r="I71">
-        <v>55.000000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J71">
         <v>2.2000000000000002</v>
@@ -6372,25 +6372,25 @@
         <v>78</v>
       </c>
       <c r="D72" t="s">
-        <v>14</v>
+        <v>89</v>
       </c>
       <c r="E72">
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>5.8209273697168655E-2</v>
+        <v>1.2237176856791137E-2</v>
       </c>
       <c r="G72">
         <v>1</v>
       </c>
       <c r="H72">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I72">
-        <v>55.000000000000007</v>
+        <v>65</v>
       </c>
       <c r="J72">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K72">
         <v>100</v>
@@ -6431,7 +6431,7 @@
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>2.7120229790726307E-2</v>
+        <v>1.3229380385720147E-2</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -6443,7 +6443,7 @@
         <v>65</v>
       </c>
       <c r="J73">
-        <v>2.3999999999999995</v>
+        <v>2.4</v>
       </c>
       <c r="K73">
         <v>100</v>
@@ -6484,7 +6484,7 @@
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>2.1001641362330736E-2</v>
+        <v>4.365695527287649E-2</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -6537,7 +6537,7 @@
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>2.6458760771440295E-2</v>
+        <v>1.7528929011079199E-2</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -6590,7 +6590,7 @@
         <v>2022</v>
       </c>
       <c r="F76">
-        <v>1.9844070578580224E-2</v>
+        <v>2.1001641362330736E-2</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -6643,7 +6643,7 @@
         <v>2022</v>
       </c>
       <c r="F77">
-        <v>3.9688141157160448E-2</v>
+        <v>2.7120229790726307E-2</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -6655,7 +6655,7 @@
         <v>65</v>
       </c>
       <c r="J77">
-        <v>2.4</v>
+        <v>2.3999999999999995</v>
       </c>
       <c r="K77">
         <v>100</v>
@@ -6696,7 +6696,7 @@
         <v>2022</v>
       </c>
       <c r="F78">
-        <v>8.9298317603610997E-2</v>
+        <v>5.291752154288059E-2</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -6705,7 +6705,7 @@
         <v>2875</v>
       </c>
       <c r="I78">
-        <v>55.000000000000014</v>
+        <v>55</v>
       </c>
       <c r="J78">
         <v>2.2000000000000002</v>
@@ -6749,19 +6749,19 @@
         <v>2022</v>
       </c>
       <c r="F79">
-        <v>1.5875256462864178E-2</v>
+        <v>8.9298317603610997E-2</v>
       </c>
       <c r="G79">
         <v>1</v>
       </c>
       <c r="H79">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I79">
-        <v>65</v>
+        <v>55.000000000000014</v>
       </c>
       <c r="J79">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K79">
         <v>100</v>
@@ -6802,7 +6802,7 @@
         <v>2022</v>
       </c>
       <c r="F80">
-        <v>1.7528929011079199E-2</v>
+        <v>1.9844070578580224E-2</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -6849,7 +6849,7 @@
         <v>78</v>
       </c>
       <c r="D81" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E81">
         <v>1929</v>
@@ -6902,7 +6902,7 @@
         <v>78</v>
       </c>
       <c r="D82" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E82">
         <v>1968</v>
@@ -6955,7 +6955,7 @@
         <v>78</v>
       </c>
       <c r="D83" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E83">
         <v>1965</v>
@@ -7008,7 +7008,7 @@
         <v>78</v>
       </c>
       <c r="D84" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E84">
         <v>1992</v>
@@ -7061,7 +7061,7 @@
         <v>78</v>
       </c>
       <c r="D85" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="E85">
         <v>1948</v>
@@ -7114,7 +7114,7 @@
         <v>78</v>
       </c>
       <c r="D86" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E86">
         <v>1972</v>
@@ -7273,7 +7273,7 @@
         <v>78</v>
       </c>
       <c r="D89" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E89">
         <v>1961</v>
@@ -7326,7 +7326,7 @@
         <v>78</v>
       </c>
       <c r="D90" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="E90">
         <v>1979</v>
@@ -7379,7 +7379,7 @@
         <v>78</v>
       </c>
       <c r="D91" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E91">
         <v>1984</v>
@@ -7432,7 +7432,7 @@
         <v>78</v>
       </c>
       <c r="D92" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E92">
         <v>1985</v>
@@ -7485,7 +7485,7 @@
         <v>78</v>
       </c>
       <c r="D93" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E93">
         <v>1983</v>
@@ -7538,7 +7538,7 @@
         <v>78</v>
       </c>
       <c r="D94" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E94">
         <v>1956</v>
@@ -7591,7 +7591,7 @@
         <v>78</v>
       </c>
       <c r="D95" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="E95">
         <v>1977</v>
@@ -7644,7 +7644,7 @@
         <v>78</v>
       </c>
       <c r="D96" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E96">
         <v>1973</v>
@@ -7697,7 +7697,7 @@
         <v>78</v>
       </c>
       <c r="D97" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E97">
         <v>1935</v>
@@ -7750,7 +7750,7 @@
         <v>78</v>
       </c>
       <c r="D98" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E98">
         <v>1956</v>
@@ -7803,7 +7803,7 @@
         <v>78</v>
       </c>
       <c r="D99" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E99">
         <v>1967</v>
@@ -7856,7 +7856,7 @@
         <v>78</v>
       </c>
       <c r="D100" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="E100">
         <v>1958</v>
@@ -8015,7 +8015,7 @@
         <v>78</v>
       </c>
       <c r="D103" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E103">
         <v>1964</v>
@@ -8121,7 +8121,7 @@
         <v>126</v>
       </c>
       <c r="D105" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E105">
         <v>1998</v>
@@ -8174,7 +8174,7 @@
         <v>126</v>
       </c>
       <c r="D106" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E106">
         <v>1996</v>
@@ -8280,7 +8280,7 @@
         <v>126</v>
       </c>
       <c r="D108" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E108">
         <v>1987</v>
@@ -8333,7 +8333,7 @@
         <v>126</v>
       </c>
       <c r="D109" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E109">
         <v>2013</v>
@@ -8386,7 +8386,7 @@
         <v>126</v>
       </c>
       <c r="D110" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E110">
         <v>2013</v>
@@ -8439,7 +8439,7 @@
         <v>126</v>
       </c>
       <c r="D111" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E111">
         <v>2011</v>
@@ -8492,7 +8492,7 @@
         <v>126</v>
       </c>
       <c r="D112" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E112">
         <v>2011</v>
@@ -8545,7 +8545,7 @@
         <v>126</v>
       </c>
       <c r="D113" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E113">
         <v>2020</v>
@@ -8598,7 +8598,7 @@
         <v>126</v>
       </c>
       <c r="D114" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E114">
         <v>2020</v>
@@ -8728,7 +8728,7 @@
         <v>33</v>
       </c>
       <c r="L116">
-        <v>0.1910967417235313</v>
+        <v>0.19109674172353133</v>
       </c>
       <c r="N116" t="s">
         <v>194</v>
@@ -9232,7 +9232,7 @@
         <v>33</v>
       </c>
       <c r="L125">
-        <v>0.1910967417235313</v>
+        <v>0.19109674172353133</v>
       </c>
       <c r="N125" t="s">
         <v>194</v>
@@ -9400,7 +9400,7 @@
         <v>33</v>
       </c>
       <c r="L128">
-        <v>0.1910967417235313</v>
+        <v>0.19109674172353133</v>
       </c>
       <c r="N128" t="s">
         <v>194</v>

--- a/VerveStacks_NZL_grids/vt_vervestacks_NZL_v1.xlsx
+++ b/VerveStacks_NZL_grids/vt_vervestacks_NZL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E973508C-2EEB-4E4E-81EE-B64A0E3E6398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{618646BF-9561-48D1-9AFD-6E74B6DEF9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{49DC5754-B12E-44D3-AAA9-719646BFC123}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1FB2EE62-C25B-4F4B-9480-7362BD69667A}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1661" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="315">
   <si>
     <t>~fi_t</t>
   </si>
@@ -276,63 +276,63 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_w412589726-220</t>
+  </si>
+  <si>
+    <t>e_NZ12-220</t>
+  </si>
+  <si>
+    <t>e_NZ30-220</t>
+  </si>
+  <si>
     <t>e_w89637173-220</t>
   </si>
   <si>
+    <t>e_NZ40-220</t>
+  </si>
+  <si>
+    <t>e_w93556808-220</t>
+  </si>
+  <si>
+    <t>e_w272522517-220</t>
+  </si>
+  <si>
+    <t>e_w89636266-220</t>
+  </si>
+  <si>
+    <t>e_w89637174-220</t>
+  </si>
+  <si>
+    <t>e_w89411122-220</t>
+  </si>
+  <si>
+    <t>e_NZ35-220</t>
+  </si>
+  <si>
+    <t>e_NZ22-220</t>
+  </si>
+  <si>
+    <t>e_NZ13-220</t>
+  </si>
+  <si>
+    <t>e_NZ33-220</t>
+  </si>
+  <si>
+    <t>e_w180514007-220</t>
+  </si>
+  <si>
+    <t>e_w89664063-220</t>
+  </si>
+  <si>
     <t>e_NZ11-220</t>
   </si>
   <si>
+    <t>e_NZ14-220</t>
+  </si>
+  <si>
     <t>e_w270018358-220</t>
   </si>
   <si>
-    <t>e_NZ35-220</t>
-  </si>
-  <si>
-    <t>e_NZ30-220</t>
-  </si>
-  <si>
-    <t>e_w89411122-220</t>
-  </si>
-  <si>
-    <t>e_w89637174-220</t>
-  </si>
-  <si>
-    <t>e_w89636266-220</t>
-  </si>
-  <si>
-    <t>e_NZ40-220</t>
-  </si>
-  <si>
-    <t>e_w412589726-220</t>
-  </si>
-  <si>
-    <t>e_w93556808-220</t>
-  </si>
-  <si>
-    <t>e_NZ13-220</t>
-  </si>
-  <si>
-    <t>e_NZ33-220</t>
-  </si>
-  <si>
-    <t>e_w272522517-220</t>
-  </si>
-  <si>
-    <t>e_NZ14-220</t>
-  </si>
-  <si>
-    <t>e_NZ12-220</t>
-  </si>
-  <si>
-    <t>e_w180514007-220</t>
-  </si>
-  <si>
-    <t>e_w89664063-220</t>
-  </si>
-  <si>
-    <t>e_NZ22-220</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000602849</t>
   </si>
   <si>
@@ -414,42 +414,6 @@
     <t>e_w169512273-220</t>
   </si>
   <si>
-    <t>ep_oil_combined_cycle_G100000407351</t>
-  </si>
-  <si>
-    <t>oil</t>
-  </si>
-  <si>
-    <t>ep_oil_combined_cycle_G100000407366</t>
-  </si>
-  <si>
-    <t>ep_oil_combined_cycle_G100000410345</t>
-  </si>
-  <si>
-    <t>ep_oil_combined_cycle_G100000411125</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100000407347</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100000407348</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100000407349</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100000407350</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100000407364</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100000407365</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100000407367</t>
-  </si>
-  <si>
     <t>ep_solar_pv_025</t>
   </si>
   <si>
@@ -780,66 +744,66 @@
     <t>Wairakei geothermal power plant_A</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/89664063-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/89636266-220_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/89411122-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/412589726-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/272522517-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ33-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ30-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89637173-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ12-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - NZ22-220_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - NZ11-220_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/180514007-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89637174-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ14-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ13-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ35-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/270018358-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ40-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/93556808-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/87928925-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/272522517-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ33-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ30-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89637173-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ14-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ40-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/270018358-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89664063-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89411122-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/412589726-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89637174-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/180514007-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ12-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/93556808-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ13-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ35-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Arapuni hydroelectric plant_</t>
   </si>
   <si>
@@ -969,39 +933,6 @@
     <t>ep_gas_gas_turbine_G100000407367_ccs-rf</t>
   </si>
   <si>
-    <t>ep_oil_combined_cycle_G100000407351_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_oil_combined_cycle_G100000407366_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_oil_combined_cycle_G100000410345_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_oil_combined_cycle_G100000411125_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100000407347_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100000407348_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100000407349_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100000407350_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100000407364_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100000407365_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100000407367_ccs-rf</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Huntly power station_1</t>
   </si>
   <si>
@@ -1023,10 +954,10 @@
     <t>ccs retrofit of -- Glenbrook power station_1</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/167293888-220_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/188180344-220_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/167293888-220_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - relation/17609399-220_Missing Gas Capacity</t>
@@ -1421,8 +1352,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E314553E-860B-4090-B39F-0DAB7A95C1BB}">
-  <dimension ref="B9:T38"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E8770C3-F466-4319-97C6-DE174508C341}">
+  <dimension ref="B9:T27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="9" spans="2:20" x14ac:dyDescent="0.45">
@@ -1430,7 +1361,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.45">
@@ -1456,42 +1387,42 @@
         <v>9</v>
       </c>
       <c r="I10" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="J10" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="K10" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="L10" t="s">
         <v>10</v>
       </c>
       <c r="N10" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="O10" t="s">
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="Q10" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="R10" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="S10" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="T10" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
@@ -1524,30 +1455,30 @@
         <v>20</v>
       </c>
       <c r="N11" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O11" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="P11" t="s">
-        <v>321</v>
+        <v>298</v>
       </c>
       <c r="Q11" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R11" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S11" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T11" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -1580,30 +1511,30 @@
         <v>20</v>
       </c>
       <c r="N12" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O12" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="P12" t="s">
-        <v>322</v>
+        <v>299</v>
       </c>
       <c r="Q12" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R12" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S12" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T12" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="C13" t="s">
         <v>17</v>
@@ -1636,30 +1567,30 @@
         <v>20</v>
       </c>
       <c r="N13" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O13" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="P13" t="s">
-        <v>323</v>
+        <v>300</v>
       </c>
       <c r="Q13" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R13" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S13" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T13" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="C14" t="s">
         <v>22</v>
@@ -1692,30 +1623,30 @@
         <v>20</v>
       </c>
       <c r="N14" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O14" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="P14" t="s">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="Q14" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R14" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S14" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T14" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="C15" t="s">
         <v>22</v>
@@ -1748,30 +1679,30 @@
         <v>20</v>
       </c>
       <c r="N15" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O15" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="P15" t="s">
-        <v>325</v>
+        <v>302</v>
       </c>
       <c r="Q15" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R15" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S15" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T15" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="C16" t="s">
         <v>22</v>
@@ -1804,30 +1735,30 @@
         <v>20</v>
       </c>
       <c r="N16" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O16" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="P16" t="s">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="Q16" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R16" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S16" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T16" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="C17" t="s">
         <v>22</v>
@@ -1860,30 +1791,30 @@
         <v>20</v>
       </c>
       <c r="N17" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O17" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="P17" t="s">
-        <v>327</v>
+        <v>304</v>
       </c>
       <c r="Q17" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R17" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S17" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T17" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="C18" t="s">
         <v>22</v>
@@ -1916,30 +1847,30 @@
         <v>20</v>
       </c>
       <c r="N18" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O18" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="P18" t="s">
-        <v>328</v>
+        <v>305</v>
       </c>
       <c r="Q18" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R18" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S18" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T18" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="C19" t="s">
         <v>22</v>
@@ -1972,30 +1903,30 @@
         <v>20</v>
       </c>
       <c r="N19" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O19" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="P19" t="s">
-        <v>329</v>
+        <v>306</v>
       </c>
       <c r="Q19" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R19" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S19" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T19" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="C20" t="s">
         <v>22</v>
@@ -2028,30 +1959,30 @@
         <v>20</v>
       </c>
       <c r="N20" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O20" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="P20" t="s">
-        <v>330</v>
+        <v>307</v>
       </c>
       <c r="Q20" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R20" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S20" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T20" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="C21" t="s">
         <v>22</v>
@@ -2084,30 +2015,30 @@
         <v>20</v>
       </c>
       <c r="N21" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O21" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="P21" t="s">
-        <v>331</v>
+        <v>308</v>
       </c>
       <c r="Q21" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R21" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S21" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T21" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="C22" t="s">
         <v>22</v>
@@ -2140,30 +2071,30 @@
         <v>20</v>
       </c>
       <c r="N22" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O22" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="P22" t="s">
-        <v>332</v>
+        <v>309</v>
       </c>
       <c r="Q22" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R22" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S22" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T22" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="C23" t="s">
         <v>22</v>
@@ -2196,30 +2127,30 @@
         <v>20</v>
       </c>
       <c r="N23" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O23" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="P23" t="s">
-        <v>333</v>
+        <v>310</v>
       </c>
       <c r="Q23" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R23" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S23" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T23" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="C24" t="s">
         <v>22</v>
@@ -2252,30 +2183,30 @@
         <v>20</v>
       </c>
       <c r="N24" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O24" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="P24" t="s">
-        <v>334</v>
+        <v>311</v>
       </c>
       <c r="Q24" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R24" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S24" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T24" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="C25" t="s">
         <v>22</v>
@@ -2308,30 +2239,30 @@
         <v>20</v>
       </c>
       <c r="N25" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O25" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="P25" t="s">
-        <v>335</v>
+        <v>312</v>
       </c>
       <c r="Q25" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R25" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S25" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T25" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="C26" t="s">
         <v>22</v>
@@ -2364,30 +2295,30 @@
         <v>20</v>
       </c>
       <c r="N26" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O26" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="P26" t="s">
-        <v>336</v>
+        <v>313</v>
       </c>
       <c r="Q26" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R26" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S26" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T26" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="C27" t="s">
         <v>22</v>
@@ -2420,641 +2351,25 @@
         <v>20</v>
       </c>
       <c r="N27" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O27" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="P27" t="s">
-        <v>337</v>
+        <v>314</v>
       </c>
       <c r="Q27" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R27" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S27" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T27" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B28" t="s">
-        <v>310</v>
-      </c>
-      <c r="C28" t="s">
-        <v>126</v>
-      </c>
-      <c r="D28" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28">
-        <v>0.4375</v>
-      </c>
-      <c r="F28">
-        <v>1365</v>
-      </c>
-      <c r="G28">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="H28">
-        <v>3.75</v>
-      </c>
-      <c r="I28">
-        <v>0.84455000000000002</v>
-      </c>
-      <c r="J28" t="s">
-        <v>125</v>
-      </c>
-      <c r="K28">
-        <v>1</v>
-      </c>
-      <c r="L28">
-        <v>20</v>
-      </c>
-      <c r="N28" t="s">
-        <v>194</v>
-      </c>
-      <c r="O28" t="s">
-        <v>310</v>
-      </c>
-      <c r="P28" t="s">
-        <v>324</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>196</v>
-      </c>
-      <c r="R28" t="s">
-        <v>197</v>
-      </c>
-      <c r="S28" t="s">
-        <v>198</v>
-      </c>
-      <c r="T28" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B29" t="s">
-        <v>311</v>
-      </c>
-      <c r="C29" t="s">
-        <v>126</v>
-      </c>
-      <c r="D29" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29">
-        <v>0.42</v>
-      </c>
-      <c r="F29">
-        <v>1365</v>
-      </c>
-      <c r="G29">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="H29">
-        <v>3.75</v>
-      </c>
-      <c r="I29">
-        <v>0.84455000000000002</v>
-      </c>
-      <c r="J29" t="s">
-        <v>127</v>
-      </c>
-      <c r="K29">
-        <v>1</v>
-      </c>
-      <c r="L29">
-        <v>20</v>
-      </c>
-      <c r="N29" t="s">
-        <v>194</v>
-      </c>
-      <c r="O29" t="s">
-        <v>311</v>
-      </c>
-      <c r="P29" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>196</v>
-      </c>
-      <c r="R29" t="s">
-        <v>197</v>
-      </c>
-      <c r="S29" t="s">
-        <v>198</v>
-      </c>
-      <c r="T29" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B30" t="s">
-        <v>312</v>
-      </c>
-      <c r="C30" t="s">
-        <v>126</v>
-      </c>
-      <c r="D30" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30">
-        <v>0.45500000000000002</v>
-      </c>
-      <c r="F30">
-        <v>1365</v>
-      </c>
-      <c r="G30">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="H30">
-        <v>3.75</v>
-      </c>
-      <c r="I30">
-        <v>0.84455000000000002</v>
-      </c>
-      <c r="J30" t="s">
-        <v>128</v>
-      </c>
-      <c r="K30">
-        <v>1</v>
-      </c>
-      <c r="L30">
-        <v>20</v>
-      </c>
-      <c r="N30" t="s">
-        <v>194</v>
-      </c>
-      <c r="O30" t="s">
-        <v>312</v>
-      </c>
-      <c r="P30" t="s">
-        <v>326</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>196</v>
-      </c>
-      <c r="R30" t="s">
-        <v>197</v>
-      </c>
-      <c r="S30" t="s">
-        <v>198</v>
-      </c>
-      <c r="T30" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B31" t="s">
-        <v>313</v>
-      </c>
-      <c r="C31" t="s">
-        <v>126</v>
-      </c>
-      <c r="D31" t="s">
-        <v>23</v>
-      </c>
-      <c r="E31">
-        <v>0.35875000000000001</v>
-      </c>
-      <c r="F31">
-        <v>1365</v>
-      </c>
-      <c r="G31">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="H31">
-        <v>3.75</v>
-      </c>
-      <c r="I31">
-        <v>0.84455000000000002</v>
-      </c>
-      <c r="J31" t="s">
-        <v>129</v>
-      </c>
-      <c r="K31">
-        <v>1</v>
-      </c>
-      <c r="L31">
-        <v>20</v>
-      </c>
-      <c r="N31" t="s">
-        <v>194</v>
-      </c>
-      <c r="O31" t="s">
-        <v>313</v>
-      </c>
-      <c r="P31" t="s">
-        <v>327</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>196</v>
-      </c>
-      <c r="R31" t="s">
-        <v>197</v>
-      </c>
-      <c r="S31" t="s">
-        <v>198</v>
-      </c>
-      <c r="T31" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B32" t="s">
-        <v>314</v>
-      </c>
-      <c r="C32" t="s">
-        <v>126</v>
-      </c>
-      <c r="D32" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32">
-        <v>0.25374999999999998</v>
-      </c>
-      <c r="F32">
-        <v>1365</v>
-      </c>
-      <c r="G32">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="H32">
-        <v>3.75</v>
-      </c>
-      <c r="I32">
-        <v>0.84455000000000002</v>
-      </c>
-      <c r="J32" t="s">
-        <v>130</v>
-      </c>
-      <c r="K32">
-        <v>1</v>
-      </c>
-      <c r="L32">
-        <v>20</v>
-      </c>
-      <c r="N32" t="s">
-        <v>194</v>
-      </c>
-      <c r="O32" t="s">
-        <v>314</v>
-      </c>
-      <c r="P32" t="s">
-        <v>331</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>196</v>
-      </c>
-      <c r="R32" t="s">
-        <v>197</v>
-      </c>
-      <c r="S32" t="s">
-        <v>198</v>
-      </c>
-      <c r="T32" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B33" t="s">
-        <v>315</v>
-      </c>
-      <c r="C33" t="s">
-        <v>126</v>
-      </c>
-      <c r="D33" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33">
-        <v>0.25374999999999998</v>
-      </c>
-      <c r="F33">
-        <v>1365</v>
-      </c>
-      <c r="G33">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="H33">
-        <v>3.75</v>
-      </c>
-      <c r="I33">
-        <v>0.84455000000000002</v>
-      </c>
-      <c r="J33" t="s">
-        <v>131</v>
-      </c>
-      <c r="K33">
-        <v>1</v>
-      </c>
-      <c r="L33">
-        <v>20</v>
-      </c>
-      <c r="N33" t="s">
-        <v>194</v>
-      </c>
-      <c r="O33" t="s">
-        <v>315</v>
-      </c>
-      <c r="P33" t="s">
-        <v>332</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>196</v>
-      </c>
-      <c r="R33" t="s">
-        <v>197</v>
-      </c>
-      <c r="S33" t="s">
-        <v>198</v>
-      </c>
-      <c r="T33" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B34" t="s">
-        <v>316</v>
-      </c>
-      <c r="C34" t="s">
-        <v>126</v>
-      </c>
-      <c r="D34" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34">
-        <v>0.26250000000000001</v>
-      </c>
-      <c r="F34">
-        <v>1365</v>
-      </c>
-      <c r="G34">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="H34">
-        <v>3.75</v>
-      </c>
-      <c r="I34">
-        <v>0.84455000000000002</v>
-      </c>
-      <c r="J34" t="s">
-        <v>132</v>
-      </c>
-      <c r="K34">
-        <v>1</v>
-      </c>
-      <c r="L34">
-        <v>20</v>
-      </c>
-      <c r="N34" t="s">
-        <v>194</v>
-      </c>
-      <c r="O34" t="s">
-        <v>316</v>
-      </c>
-      <c r="P34" t="s">
-        <v>333</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>196</v>
-      </c>
-      <c r="R34" t="s">
-        <v>197</v>
-      </c>
-      <c r="S34" t="s">
-        <v>198</v>
-      </c>
-      <c r="T34" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B35" t="s">
-        <v>317</v>
-      </c>
-      <c r="C35" t="s">
-        <v>126</v>
-      </c>
-      <c r="D35" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35">
-        <v>0.26250000000000001</v>
-      </c>
-      <c r="F35">
-        <v>1365</v>
-      </c>
-      <c r="G35">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="H35">
-        <v>3.75</v>
-      </c>
-      <c r="I35">
-        <v>0.84455000000000002</v>
-      </c>
-      <c r="J35" t="s">
-        <v>133</v>
-      </c>
-      <c r="K35">
-        <v>1</v>
-      </c>
-      <c r="L35">
-        <v>20</v>
-      </c>
-      <c r="N35" t="s">
-        <v>194</v>
-      </c>
-      <c r="O35" t="s">
-        <v>317</v>
-      </c>
-      <c r="P35" t="s">
-        <v>334</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>196</v>
-      </c>
-      <c r="R35" t="s">
-        <v>197</v>
-      </c>
-      <c r="S35" t="s">
-        <v>198</v>
-      </c>
-      <c r="T35" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="36" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B36" t="s">
-        <v>318</v>
-      </c>
-      <c r="C36" t="s">
-        <v>126</v>
-      </c>
-      <c r="D36" t="s">
-        <v>24</v>
-      </c>
-      <c r="E36">
-        <v>0.25374999999999998</v>
-      </c>
-      <c r="F36">
-        <v>1365</v>
-      </c>
-      <c r="G36">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="H36">
-        <v>3.75</v>
-      </c>
-      <c r="I36">
-        <v>0.84455000000000002</v>
-      </c>
-      <c r="J36" t="s">
-        <v>134</v>
-      </c>
-      <c r="K36">
-        <v>1</v>
-      </c>
-      <c r="L36">
-        <v>20</v>
-      </c>
-      <c r="N36" t="s">
-        <v>194</v>
-      </c>
-      <c r="O36" t="s">
-        <v>318</v>
-      </c>
-      <c r="P36" t="s">
-        <v>335</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>196</v>
-      </c>
-      <c r="R36" t="s">
-        <v>197</v>
-      </c>
-      <c r="S36" t="s">
-        <v>198</v>
-      </c>
-      <c r="T36" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B37" t="s">
-        <v>319</v>
-      </c>
-      <c r="C37" t="s">
-        <v>126</v>
-      </c>
-      <c r="D37" t="s">
-        <v>24</v>
-      </c>
-      <c r="E37">
-        <v>0.25374999999999998</v>
-      </c>
-      <c r="F37">
-        <v>1365</v>
-      </c>
-      <c r="G37">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="H37">
-        <v>3.75</v>
-      </c>
-      <c r="I37">
-        <v>0.84455000000000002</v>
-      </c>
-      <c r="J37" t="s">
-        <v>135</v>
-      </c>
-      <c r="K37">
-        <v>1</v>
-      </c>
-      <c r="L37">
-        <v>20</v>
-      </c>
-      <c r="N37" t="s">
-        <v>194</v>
-      </c>
-      <c r="O37" t="s">
-        <v>319</v>
-      </c>
-      <c r="P37" t="s">
-        <v>336</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>196</v>
-      </c>
-      <c r="R37" t="s">
-        <v>197</v>
-      </c>
-      <c r="S37" t="s">
-        <v>198</v>
-      </c>
-      <c r="T37" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B38" t="s">
-        <v>320</v>
-      </c>
-      <c r="C38" t="s">
-        <v>126</v>
-      </c>
-      <c r="D38" t="s">
-        <v>18</v>
-      </c>
-      <c r="E38">
-        <v>0.24500000000000002</v>
-      </c>
-      <c r="F38">
-        <v>1365</v>
-      </c>
-      <c r="G38">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="H38">
-        <v>3.75</v>
-      </c>
-      <c r="I38">
-        <v>0.84455000000000002</v>
-      </c>
-      <c r="J38" t="s">
-        <v>136</v>
-      </c>
-      <c r="K38">
-        <v>1</v>
-      </c>
-      <c r="L38">
-        <v>20</v>
-      </c>
-      <c r="N38" t="s">
-        <v>194</v>
-      </c>
-      <c r="O38" t="s">
-        <v>320</v>
-      </c>
-      <c r="P38" t="s">
-        <v>337</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>196</v>
-      </c>
-      <c r="R38" t="s">
-        <v>197</v>
-      </c>
-      <c r="S38" t="s">
-        <v>198</v>
-      </c>
-      <c r="T38" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -3063,8 +2378,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6FAE010-BE81-4C51-A04C-2706FEDCA28E}">
-  <dimension ref="B9:T149"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73EBEADB-A272-436E-AC28-143A06BF3090}">
+  <dimension ref="B9:T138"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="9" spans="2:20" x14ac:dyDescent="0.45">
@@ -3072,7 +2387,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.45">
@@ -3110,25 +2425,25 @@
         <v>11</v>
       </c>
       <c r="N10" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="O10" t="s">
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="Q10" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="R10" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="S10" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="T10" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.45">
@@ -3163,25 +2478,25 @@
         <v>50</v>
       </c>
       <c r="N11" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O11" t="s">
         <v>12</v>
       </c>
       <c r="P11" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="Q11" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R11" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S11" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T11" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.45">
@@ -3216,25 +2531,25 @@
         <v>58</v>
       </c>
       <c r="N12" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O12" t="s">
         <v>15</v>
       </c>
       <c r="P12" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="Q12" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R12" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S12" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T12" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.45">
@@ -3269,25 +2584,25 @@
         <v>52</v>
       </c>
       <c r="N13" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O13" t="s">
         <v>16</v>
       </c>
       <c r="P13" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="Q13" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R13" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S13" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T13" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.45">
@@ -3322,25 +2637,25 @@
         <v>52</v>
       </c>
       <c r="N14" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O14" t="s">
         <v>19</v>
       </c>
       <c r="P14" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="Q14" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R14" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S14" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T14" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.45">
@@ -3375,25 +2690,25 @@
         <v>52</v>
       </c>
       <c r="N15" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O15" t="s">
         <v>20</v>
       </c>
       <c r="P15" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="Q15" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R15" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S15" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T15" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.45">
@@ -3428,25 +2743,25 @@
         <v>50</v>
       </c>
       <c r="N16" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O16" t="s">
         <v>21</v>
       </c>
       <c r="P16" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="Q16" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R16" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S16" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T16" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.45">
@@ -3481,25 +2796,25 @@
         <v>50</v>
       </c>
       <c r="N17" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O17" t="s">
         <v>21</v>
       </c>
       <c r="P17" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="Q17" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R17" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S17" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T17" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.45">
@@ -3534,25 +2849,25 @@
         <v>50</v>
       </c>
       <c r="N18" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O18" t="s">
         <v>21</v>
       </c>
       <c r="P18" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="Q18" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R18" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S18" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T18" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.45">
@@ -3587,25 +2902,25 @@
         <v>50</v>
       </c>
       <c r="N19" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O19" t="s">
         <v>25</v>
       </c>
       <c r="P19" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="Q19" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R19" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S19" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T19" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.45">
@@ -3640,25 +2955,25 @@
         <v>59</v>
       </c>
       <c r="N20" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O20" t="s">
         <v>26</v>
       </c>
       <c r="P20" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="Q20" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R20" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S20" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T20" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.45">
@@ -3693,25 +3008,25 @@
         <v>50</v>
       </c>
       <c r="N21" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O21" t="s">
         <v>27</v>
       </c>
       <c r="P21" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="Q21" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R21" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S21" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T21" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.45">
@@ -3746,25 +3061,25 @@
         <v>68</v>
       </c>
       <c r="N22" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O22" t="s">
         <v>28</v>
       </c>
       <c r="P22" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="Q22" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R22" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S22" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T22" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.45">
@@ -3799,25 +3114,25 @@
         <v>40</v>
       </c>
       <c r="N23" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O23" t="s">
         <v>29</v>
       </c>
       <c r="P23" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="Q23" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R23" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S23" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T23" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.45">
@@ -3852,25 +3167,25 @@
         <v>40</v>
       </c>
       <c r="N24" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O24" t="s">
         <v>30</v>
       </c>
       <c r="P24" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="Q24" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R24" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S24" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T24" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.45">
@@ -3905,25 +3220,25 @@
         <v>40</v>
       </c>
       <c r="N25" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O25" t="s">
         <v>31</v>
       </c>
       <c r="P25" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="Q25" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R25" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S25" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T25" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.45">
@@ -3958,25 +3273,25 @@
         <v>40</v>
       </c>
       <c r="N26" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O26" t="s">
         <v>32</v>
       </c>
       <c r="P26" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="Q26" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R26" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S26" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T26" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.45">
@@ -4011,25 +3326,25 @@
         <v>40</v>
       </c>
       <c r="N27" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O27" t="s">
         <v>33</v>
       </c>
       <c r="P27" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="Q27" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R27" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S27" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T27" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.45">
@@ -4064,25 +3379,25 @@
         <v>40</v>
       </c>
       <c r="N28" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O28" t="s">
         <v>34</v>
       </c>
       <c r="P28" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="Q28" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R28" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S28" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T28" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.45">
@@ -4117,25 +3432,25 @@
         <v>40</v>
       </c>
       <c r="N29" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O29" t="s">
         <v>35</v>
       </c>
       <c r="P29" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="Q29" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R29" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S29" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T29" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.45">
@@ -4170,25 +3485,25 @@
         <v>50</v>
       </c>
       <c r="N30" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O30" t="s">
         <v>36</v>
       </c>
       <c r="P30" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="Q30" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R30" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S30" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T30" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.45">
@@ -4223,25 +3538,25 @@
         <v>55</v>
       </c>
       <c r="N31" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O31" t="s">
         <v>39</v>
       </c>
       <c r="P31" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="Q31" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R31" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S31" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T31" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="32" spans="2:20" x14ac:dyDescent="0.45">
@@ -4276,25 +3591,25 @@
         <v>50</v>
       </c>
       <c r="N32" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O32" t="s">
         <v>41</v>
       </c>
       <c r="P32" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="Q32" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R32" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S32" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T32" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="33" spans="2:20" x14ac:dyDescent="0.45">
@@ -4329,25 +3644,25 @@
         <v>50</v>
       </c>
       <c r="N33" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O33" t="s">
         <v>43</v>
       </c>
       <c r="P33" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="Q33" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R33" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S33" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T33" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34" spans="2:20" x14ac:dyDescent="0.45">
@@ -4382,25 +3697,25 @@
         <v>50</v>
       </c>
       <c r="N34" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O34" t="s">
         <v>45</v>
       </c>
       <c r="P34" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="Q34" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R34" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S34" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T34" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.45">
@@ -4435,25 +3750,25 @@
         <v>66</v>
       </c>
       <c r="N35" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O35" t="s">
         <v>47</v>
       </c>
       <c r="P35" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="Q35" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R35" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S35" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T35" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="36" spans="2:20" x14ac:dyDescent="0.45">
@@ -4488,25 +3803,25 @@
         <v>58</v>
       </c>
       <c r="N36" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O36" t="s">
         <v>49</v>
       </c>
       <c r="P36" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="Q36" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R36" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S36" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T36" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.45">
@@ -4541,25 +3856,25 @@
         <v>55</v>
       </c>
       <c r="N37" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O37" t="s">
         <v>51</v>
       </c>
       <c r="P37" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="Q37" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R37" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S37" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T37" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="38" spans="2:20" x14ac:dyDescent="0.45">
@@ -4594,25 +3909,25 @@
         <v>50</v>
       </c>
       <c r="N38" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O38" t="s">
         <v>52</v>
       </c>
       <c r="P38" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="Q38" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R38" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S38" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T38" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="39" spans="2:20" x14ac:dyDescent="0.45">
@@ -4647,25 +3962,25 @@
         <v>50</v>
       </c>
       <c r="N39" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O39" t="s">
         <v>54</v>
       </c>
       <c r="P39" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="Q39" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R39" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S39" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T39" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="40" spans="2:20" x14ac:dyDescent="0.45">
@@ -4700,25 +4015,25 @@
         <v>50</v>
       </c>
       <c r="N40" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O40" t="s">
         <v>56</v>
       </c>
       <c r="P40" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="Q40" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R40" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S40" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T40" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="41" spans="2:20" x14ac:dyDescent="0.45">
@@ -4753,25 +4068,25 @@
         <v>73</v>
       </c>
       <c r="N41" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O41" t="s">
         <v>57</v>
       </c>
       <c r="P41" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="Q41" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R41" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S41" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T41" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="42" spans="2:20" x14ac:dyDescent="0.45">
@@ -4806,25 +4121,25 @@
         <v>73</v>
       </c>
       <c r="N42" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O42" t="s">
         <v>59</v>
       </c>
       <c r="P42" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="Q42" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R42" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S42" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T42" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="43" spans="2:20" x14ac:dyDescent="0.45">
@@ -4859,25 +4174,25 @@
         <v>73</v>
       </c>
       <c r="N43" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O43" t="s">
         <v>60</v>
       </c>
       <c r="P43" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="Q43" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R43" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S43" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T43" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.45">
@@ -4912,25 +4227,25 @@
         <v>50</v>
       </c>
       <c r="N44" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O44" t="s">
         <v>61</v>
       </c>
       <c r="P44" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="Q44" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R44" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S44" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T44" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="45" spans="2:20" x14ac:dyDescent="0.45">
@@ -4965,25 +4280,25 @@
         <v>50</v>
       </c>
       <c r="N45" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O45" t="s">
         <v>62</v>
       </c>
       <c r="P45" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="Q45" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R45" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S45" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T45" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="2:20" x14ac:dyDescent="0.45">
@@ -5018,25 +4333,25 @@
         <v>50</v>
       </c>
       <c r="N46" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O46" t="s">
         <v>63</v>
       </c>
       <c r="P46" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="Q46" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R46" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S46" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T46" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="47" spans="2:20" x14ac:dyDescent="0.45">
@@ -5071,25 +4386,25 @@
         <v>50</v>
       </c>
       <c r="N47" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O47" t="s">
         <v>64</v>
       </c>
       <c r="P47" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="Q47" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R47" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S47" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T47" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="48" spans="2:20" x14ac:dyDescent="0.45">
@@ -5124,25 +4439,25 @@
         <v>50</v>
       </c>
       <c r="N48" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O48" t="s">
         <v>65</v>
       </c>
       <c r="P48" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="Q48" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R48" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S48" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T48" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="49" spans="2:20" x14ac:dyDescent="0.45">
@@ -5177,25 +4492,25 @@
         <v>50</v>
       </c>
       <c r="N49" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O49" t="s">
         <v>66</v>
       </c>
       <c r="P49" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="Q49" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R49" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S49" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T49" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="50" spans="2:20" x14ac:dyDescent="0.45">
@@ -5230,25 +4545,25 @@
         <v>50</v>
       </c>
       <c r="N50" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O50" t="s">
         <v>67</v>
       </c>
       <c r="P50" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="Q50" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R50" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S50" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T50" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="51" spans="2:20" x14ac:dyDescent="0.45">
@@ -5283,25 +4598,25 @@
         <v>50</v>
       </c>
       <c r="N51" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O51" t="s">
         <v>68</v>
       </c>
       <c r="P51" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="Q51" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R51" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S51" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T51" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="52" spans="2:20" x14ac:dyDescent="0.45">
@@ -5336,25 +4651,25 @@
         <v>50</v>
       </c>
       <c r="N52" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O52" t="s">
         <v>69</v>
       </c>
       <c r="P52" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="Q52" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R52" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S52" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T52" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="53" spans="2:20" x14ac:dyDescent="0.45">
@@ -5389,25 +4704,25 @@
         <v>50</v>
       </c>
       <c r="N53" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O53" t="s">
         <v>70</v>
       </c>
       <c r="P53" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="Q53" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R53" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S53" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T53" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="54" spans="2:20" x14ac:dyDescent="0.45">
@@ -5442,25 +4757,25 @@
         <v>50</v>
       </c>
       <c r="N54" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O54" t="s">
         <v>71</v>
       </c>
       <c r="P54" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="Q54" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R54" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S54" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T54" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="55" spans="2:20" x14ac:dyDescent="0.45">
@@ -5495,25 +4810,25 @@
         <v>50</v>
       </c>
       <c r="N55" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O55" t="s">
         <v>72</v>
       </c>
       <c r="P55" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="Q55" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R55" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S55" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T55" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="56" spans="2:20" x14ac:dyDescent="0.45">
@@ -5548,25 +4863,25 @@
         <v>50</v>
       </c>
       <c r="N56" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O56" t="s">
         <v>73</v>
       </c>
       <c r="P56" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="Q56" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R56" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S56" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T56" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="57" spans="2:20" x14ac:dyDescent="0.45">
@@ -5601,25 +4916,25 @@
         <v>73</v>
       </c>
       <c r="N57" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O57" t="s">
         <v>74</v>
       </c>
       <c r="P57" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="Q57" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R57" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S57" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T57" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="58" spans="2:20" x14ac:dyDescent="0.45">
@@ -5654,25 +4969,25 @@
         <v>66</v>
       </c>
       <c r="N58" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O58" t="s">
         <v>75</v>
       </c>
       <c r="P58" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="Q58" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R58" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S58" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T58" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="59" spans="2:20" x14ac:dyDescent="0.45">
@@ -5707,25 +5022,25 @@
         <v>50</v>
       </c>
       <c r="N59" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O59" t="s">
         <v>76</v>
       </c>
       <c r="P59" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="Q59" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R59" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S59" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T59" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="60" spans="2:20" x14ac:dyDescent="0.45">
@@ -5760,25 +5075,25 @@
         <v>59</v>
       </c>
       <c r="N60" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O60" t="s">
         <v>77</v>
       </c>
       <c r="P60" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="Q60" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R60" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S60" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T60" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="61" spans="2:20" x14ac:dyDescent="0.45">
@@ -5795,43 +5110,43 @@
         <v>2022</v>
       </c>
       <c r="F61">
-        <v>1.7363561756257695E-2</v>
+        <v>0.16073697168649981</v>
       </c>
       <c r="G61">
         <v>1</v>
       </c>
       <c r="H61">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I61">
-        <v>65</v>
+        <v>55.000000000000014</v>
       </c>
       <c r="J61">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K61">
         <v>100</v>
       </c>
       <c r="N61" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O61" t="s">
         <v>77</v>
       </c>
       <c r="P61" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="Q61" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R61" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S61" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T61" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="62" spans="2:20" x14ac:dyDescent="0.45">
@@ -5848,7 +5163,7 @@
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>1.5875256462864178E-2</v>
+        <v>2.7120229790726307E-2</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -5860,31 +5175,31 @@
         <v>65</v>
       </c>
       <c r="J62">
-        <v>2.4</v>
+        <v>2.3999999999999995</v>
       </c>
       <c r="K62">
         <v>100</v>
       </c>
       <c r="N62" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O62" t="s">
         <v>77</v>
       </c>
       <c r="P62" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="Q62" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R62" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S62" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T62" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="63" spans="2:20" x14ac:dyDescent="0.45">
@@ -5901,13 +5216,13 @@
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>1.2898645876077145E-2</v>
+        <v>2.6458760771440295E-2</v>
       </c>
       <c r="G63">
         <v>1</v>
       </c>
       <c r="H63">
-        <v>3375.0000000000005</v>
+        <v>3375</v>
       </c>
       <c r="I63">
         <v>65</v>
@@ -5919,25 +5234,25 @@
         <v>100</v>
       </c>
       <c r="N63" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O63" t="s">
         <v>77</v>
       </c>
       <c r="P63" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="Q63" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R63" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S63" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T63" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="64" spans="2:20" x14ac:dyDescent="0.45">
@@ -5954,7 +5269,7 @@
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>3.5057858022158397E-2</v>
+        <v>1.7363561756257695E-2</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -5972,25 +5287,25 @@
         <v>100</v>
       </c>
       <c r="N64" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O64" t="s">
         <v>77</v>
       </c>
       <c r="P64" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="Q64" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R64" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S64" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T64" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="65" spans="2:20" x14ac:dyDescent="0.45">
@@ -6007,43 +5322,43 @@
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>2.6458760771440295E-2</v>
+        <v>7.1438654082888797E-2</v>
       </c>
       <c r="G65">
         <v>1</v>
       </c>
       <c r="H65">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I65">
-        <v>65</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J65">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K65">
         <v>100</v>
       </c>
       <c r="N65" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O65" t="s">
         <v>77</v>
       </c>
       <c r="P65" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="Q65" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R65" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S65" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T65" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="66" spans="2:20" x14ac:dyDescent="0.45">
@@ -6060,7 +5375,7 @@
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>3.9688141157160448E-2</v>
+        <v>1.2237176856791137E-2</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -6078,25 +5393,25 @@
         <v>100</v>
       </c>
       <c r="N66" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O66" t="s">
         <v>77</v>
       </c>
       <c r="P66" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="Q66" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R66" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S66" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T66" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="67" spans="2:20" x14ac:dyDescent="0.45">
@@ -6107,49 +5422,49 @@
         <v>78</v>
       </c>
       <c r="D67" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="E67">
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>3.6380796060730414E-2</v>
+        <v>5.8209273697168655E-2</v>
       </c>
       <c r="G67">
         <v>1</v>
       </c>
       <c r="H67">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I67">
-        <v>65</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J67">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K67">
         <v>100</v>
       </c>
       <c r="N67" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O67" t="s">
         <v>77</v>
       </c>
       <c r="P67" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="Q67" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R67" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S67" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T67" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="68" spans="2:20" x14ac:dyDescent="0.45">
@@ -6160,13 +5475,13 @@
         <v>78</v>
       </c>
       <c r="D68" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E68">
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>3.5057858022158397E-2</v>
+        <v>1.7528929011079199E-2</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -6184,25 +5499,25 @@
         <v>100</v>
       </c>
       <c r="N68" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O68" t="s">
         <v>77</v>
       </c>
       <c r="P68" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="Q68" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R68" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S68" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T68" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="69" spans="2:20" x14ac:dyDescent="0.45">
@@ -6213,49 +5528,49 @@
         <v>78</v>
       </c>
       <c r="D69" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E69">
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>7.1438654082888797E-2</v>
+        <v>3.5057858022158397E-2</v>
       </c>
       <c r="G69">
         <v>1</v>
       </c>
       <c r="H69">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I69">
-        <v>55.000000000000007</v>
+        <v>65</v>
       </c>
       <c r="J69">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K69">
         <v>100</v>
       </c>
       <c r="N69" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O69" t="s">
         <v>77</v>
       </c>
       <c r="P69" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="Q69" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R69" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S69" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T69" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="70" spans="2:20" x14ac:dyDescent="0.45">
@@ -6266,49 +5581,49 @@
         <v>78</v>
       </c>
       <c r="D70" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E70">
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>0.16073697168649981</v>
+        <v>3.6380796060730414E-2</v>
       </c>
       <c r="G70">
         <v>1</v>
       </c>
       <c r="H70">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I70">
-        <v>55.000000000000014</v>
+        <v>65</v>
       </c>
       <c r="J70">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K70">
         <v>100</v>
       </c>
       <c r="N70" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O70" t="s">
         <v>77</v>
       </c>
       <c r="P70" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="Q70" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R70" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S70" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T70" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="71" spans="2:20" x14ac:dyDescent="0.45">
@@ -6319,49 +5634,49 @@
         <v>78</v>
       </c>
       <c r="D71" t="s">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="E71">
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>5.8209273697168655E-2</v>
+        <v>3.9688141157160448E-2</v>
       </c>
       <c r="G71">
         <v>1</v>
       </c>
       <c r="H71">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I71">
-        <v>55.000000000000007</v>
+        <v>65</v>
       </c>
       <c r="J71">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K71">
         <v>100</v>
       </c>
       <c r="N71" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O71" t="s">
         <v>77</v>
       </c>
       <c r="P71" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="Q71" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R71" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S71" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T71" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="72" spans="2:20" x14ac:dyDescent="0.45">
@@ -6378,7 +5693,7 @@
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>1.2237176856791137E-2</v>
+        <v>3.5057858022158397E-2</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -6396,25 +5711,25 @@
         <v>100</v>
       </c>
       <c r="N72" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O72" t="s">
         <v>77</v>
       </c>
       <c r="P72" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="Q72" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R72" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S72" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T72" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="73" spans="2:20" x14ac:dyDescent="0.45">
@@ -6431,7 +5746,7 @@
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>1.3229380385720147E-2</v>
+        <v>1.9844070578580224E-2</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -6449,25 +5764,25 @@
         <v>100</v>
       </c>
       <c r="N73" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O73" t="s">
         <v>77</v>
       </c>
       <c r="P73" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="Q73" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R73" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S73" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T73" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="74" spans="2:20" x14ac:dyDescent="0.45">
@@ -6484,7 +5799,7 @@
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>4.365695527287649E-2</v>
+        <v>1.3229380385720147E-2</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -6502,25 +5817,25 @@
         <v>100</v>
       </c>
       <c r="N74" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O74" t="s">
         <v>77</v>
       </c>
       <c r="P74" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="Q74" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R74" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S74" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T74" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="75" spans="2:20" x14ac:dyDescent="0.45">
@@ -6537,7 +5852,7 @@
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>1.7528929011079199E-2</v>
+        <v>4.365695527287649E-2</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -6555,25 +5870,25 @@
         <v>100</v>
       </c>
       <c r="N75" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O75" t="s">
         <v>77</v>
       </c>
       <c r="P75" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="Q75" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R75" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S75" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T75" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="76" spans="2:20" x14ac:dyDescent="0.45">
@@ -6590,43 +5905,43 @@
         <v>2022</v>
       </c>
       <c r="F76">
-        <v>2.1001641362330736E-2</v>
+        <v>5.291752154288059E-2</v>
       </c>
       <c r="G76">
         <v>1</v>
       </c>
       <c r="H76">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I76">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J76">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K76">
         <v>100</v>
       </c>
       <c r="N76" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O76" t="s">
         <v>77</v>
       </c>
       <c r="P76" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="Q76" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R76" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S76" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T76" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="77" spans="2:20" x14ac:dyDescent="0.45">
@@ -6643,43 +5958,43 @@
         <v>2022</v>
       </c>
       <c r="F77">
-        <v>2.7120229790726307E-2</v>
+        <v>8.9298317603610997E-2</v>
       </c>
       <c r="G77">
         <v>1</v>
       </c>
       <c r="H77">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I77">
-        <v>65</v>
+        <v>55.000000000000014</v>
       </c>
       <c r="J77">
-        <v>2.3999999999999995</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K77">
         <v>100</v>
       </c>
       <c r="N77" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O77" t="s">
         <v>77</v>
       </c>
       <c r="P77" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="Q77" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R77" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S77" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T77" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="78" spans="2:20" x14ac:dyDescent="0.45">
@@ -6696,43 +6011,43 @@
         <v>2022</v>
       </c>
       <c r="F78">
-        <v>5.291752154288059E-2</v>
+        <v>1.5875256462864178E-2</v>
       </c>
       <c r="G78">
         <v>1</v>
       </c>
       <c r="H78">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I78">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="J78">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K78">
         <v>100</v>
       </c>
       <c r="N78" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O78" t="s">
         <v>77</v>
       </c>
       <c r="P78" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="Q78" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R78" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S78" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T78" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="79" spans="2:20" x14ac:dyDescent="0.45">
@@ -6749,43 +6064,43 @@
         <v>2022</v>
       </c>
       <c r="F79">
-        <v>8.9298317603610997E-2</v>
+        <v>2.1001641362330736E-2</v>
       </c>
       <c r="G79">
         <v>1</v>
       </c>
       <c r="H79">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I79">
-        <v>55.000000000000014</v>
+        <v>65</v>
       </c>
       <c r="J79">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K79">
         <v>100</v>
       </c>
       <c r="N79" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O79" t="s">
         <v>77</v>
       </c>
       <c r="P79" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="Q79" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R79" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S79" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T79" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="80" spans="2:20" x14ac:dyDescent="0.45">
@@ -6802,13 +6117,13 @@
         <v>2022</v>
       </c>
       <c r="F80">
-        <v>1.9844070578580224E-2</v>
+        <v>1.2898645876077145E-2</v>
       </c>
       <c r="G80">
         <v>1</v>
       </c>
       <c r="H80">
-        <v>3375</v>
+        <v>3375.0000000000005</v>
       </c>
       <c r="I80">
         <v>65</v>
@@ -6820,25 +6135,25 @@
         <v>100</v>
       </c>
       <c r="N80" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O80" t="s">
         <v>98</v>
       </c>
       <c r="P80" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="Q80" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R80" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S80" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T80" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="81" spans="2:20" x14ac:dyDescent="0.45">
@@ -6849,7 +6164,7 @@
         <v>78</v>
       </c>
       <c r="D81" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="E81">
         <v>1929</v>
@@ -6873,25 +6188,25 @@
         <v>126</v>
       </c>
       <c r="N81" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O81" t="s">
         <v>99</v>
       </c>
       <c r="P81" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="Q81" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R81" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S81" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T81" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="82" spans="2:20" x14ac:dyDescent="0.45">
@@ -6902,7 +6217,7 @@
         <v>78</v>
       </c>
       <c r="D82" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E82">
         <v>1968</v>
@@ -6926,25 +6241,25 @@
         <v>100</v>
       </c>
       <c r="N82" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O82" t="s">
         <v>100</v>
       </c>
       <c r="P82" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="Q82" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R82" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S82" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T82" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="83" spans="2:20" x14ac:dyDescent="0.45">
@@ -6955,7 +6270,7 @@
         <v>78</v>
       </c>
       <c r="D83" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E83">
         <v>1965</v>
@@ -6979,25 +6294,25 @@
         <v>100</v>
       </c>
       <c r="N83" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O83" t="s">
         <v>101</v>
       </c>
       <c r="P83" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="Q83" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R83" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S83" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T83" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="84" spans="2:20" x14ac:dyDescent="0.45">
@@ -7008,7 +6323,7 @@
         <v>78</v>
       </c>
       <c r="D84" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E84">
         <v>1992</v>
@@ -7032,25 +6347,25 @@
         <v>100</v>
       </c>
       <c r="N84" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O84" t="s">
         <v>102</v>
       </c>
       <c r="P84" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="Q84" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R84" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S84" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T84" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="85" spans="2:20" x14ac:dyDescent="0.45">
@@ -7061,7 +6376,7 @@
         <v>78</v>
       </c>
       <c r="D85" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="E85">
         <v>1948</v>
@@ -7085,25 +6400,25 @@
         <v>107</v>
       </c>
       <c r="N85" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O85" t="s">
         <v>103</v>
       </c>
       <c r="P85" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="Q85" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R85" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S85" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T85" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="86" spans="2:20" x14ac:dyDescent="0.45">
@@ -7114,7 +6429,7 @@
         <v>78</v>
       </c>
       <c r="D86" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E86">
         <v>1972</v>
@@ -7138,25 +6453,25 @@
         <v>100</v>
       </c>
       <c r="N86" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O86" t="s">
         <v>104</v>
       </c>
       <c r="P86" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="Q86" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R86" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S86" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T86" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="87" spans="2:20" x14ac:dyDescent="0.45">
@@ -7191,25 +6506,25 @@
         <v>103</v>
       </c>
       <c r="N87" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O87" t="s">
         <v>105</v>
       </c>
       <c r="P87" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="Q87" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R87" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S87" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T87" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="88" spans="2:20" x14ac:dyDescent="0.45">
@@ -7244,25 +6559,25 @@
         <v>100</v>
       </c>
       <c r="N88" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O88" t="s">
         <v>106</v>
       </c>
       <c r="P88" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="Q88" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R88" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S88" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T88" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="89" spans="2:20" x14ac:dyDescent="0.45">
@@ -7273,7 +6588,7 @@
         <v>78</v>
       </c>
       <c r="D89" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E89">
         <v>1961</v>
@@ -7297,25 +6612,25 @@
         <v>100</v>
       </c>
       <c r="N89" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O89" t="s">
         <v>107</v>
       </c>
       <c r="P89" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="Q89" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R89" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S89" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T89" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="90" spans="2:20" x14ac:dyDescent="0.45">
@@ -7326,7 +6641,7 @@
         <v>78</v>
       </c>
       <c r="D90" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E90">
         <v>1979</v>
@@ -7350,25 +6665,25 @@
         <v>100</v>
       </c>
       <c r="N90" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O90" t="s">
         <v>108</v>
       </c>
       <c r="P90" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="Q90" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R90" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S90" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T90" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="91" spans="2:20" x14ac:dyDescent="0.45">
@@ -7379,7 +6694,7 @@
         <v>78</v>
       </c>
       <c r="D91" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="E91">
         <v>1984</v>
@@ -7403,25 +6718,25 @@
         <v>100</v>
       </c>
       <c r="N91" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O91" t="s">
         <v>109</v>
       </c>
       <c r="P91" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="Q91" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R91" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S91" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T91" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="92" spans="2:20" x14ac:dyDescent="0.45">
@@ -7456,25 +6771,25 @@
         <v>100</v>
       </c>
       <c r="N92" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O92" t="s">
         <v>110</v>
       </c>
       <c r="P92" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="Q92" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R92" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S92" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T92" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="93" spans="2:20" x14ac:dyDescent="0.45">
@@ -7485,7 +6800,7 @@
         <v>78</v>
       </c>
       <c r="D93" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E93">
         <v>1983</v>
@@ -7509,25 +6824,25 @@
         <v>100</v>
       </c>
       <c r="N93" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O93" t="s">
         <v>111</v>
       </c>
       <c r="P93" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="Q93" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R93" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S93" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T93" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="94" spans="2:20" x14ac:dyDescent="0.45">
@@ -7538,7 +6853,7 @@
         <v>78</v>
       </c>
       <c r="D94" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E94">
         <v>1956</v>
@@ -7562,25 +6877,25 @@
         <v>100</v>
       </c>
       <c r="N94" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O94" t="s">
         <v>112</v>
       </c>
       <c r="P94" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="Q94" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R94" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S94" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T94" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="95" spans="2:20" x14ac:dyDescent="0.45">
@@ -7591,7 +6906,7 @@
         <v>78</v>
       </c>
       <c r="D95" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E95">
         <v>1977</v>
@@ -7615,25 +6930,25 @@
         <v>100</v>
       </c>
       <c r="N95" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O95" t="s">
         <v>113</v>
       </c>
       <c r="P95" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="Q95" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R95" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S95" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T95" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="96" spans="2:20" x14ac:dyDescent="0.45">
@@ -7644,7 +6959,7 @@
         <v>78</v>
       </c>
       <c r="D96" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E96">
         <v>1973</v>
@@ -7668,25 +6983,25 @@
         <v>100</v>
       </c>
       <c r="N96" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O96" t="s">
         <v>114</v>
       </c>
       <c r="P96" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="Q96" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R96" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S96" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T96" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="97" spans="2:20" x14ac:dyDescent="0.45">
@@ -7697,7 +7012,7 @@
         <v>78</v>
       </c>
       <c r="D97" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E97">
         <v>1935</v>
@@ -7721,25 +7036,25 @@
         <v>120</v>
       </c>
       <c r="N97" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O97" t="s">
         <v>115</v>
       </c>
       <c r="P97" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="Q97" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R97" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S97" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T97" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="98" spans="2:20" x14ac:dyDescent="0.45">
@@ -7750,7 +7065,7 @@
         <v>78</v>
       </c>
       <c r="D98" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E98">
         <v>1956</v>
@@ -7774,25 +7089,25 @@
         <v>100</v>
       </c>
       <c r="N98" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O98" t="s">
         <v>116</v>
       </c>
       <c r="P98" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="Q98" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R98" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S98" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T98" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="99" spans="2:20" x14ac:dyDescent="0.45">
@@ -7803,7 +7118,7 @@
         <v>78</v>
       </c>
       <c r="D99" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E99">
         <v>1967</v>
@@ -7827,25 +7142,25 @@
         <v>100</v>
       </c>
       <c r="N99" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O99" t="s">
         <v>117</v>
       </c>
       <c r="P99" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="Q99" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R99" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S99" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T99" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="100" spans="2:20" x14ac:dyDescent="0.45">
@@ -7856,7 +7171,7 @@
         <v>78</v>
       </c>
       <c r="D100" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E100">
         <v>1958</v>
@@ -7880,25 +7195,25 @@
         <v>100</v>
       </c>
       <c r="N100" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O100" t="s">
         <v>118</v>
       </c>
       <c r="P100" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="Q100" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R100" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S100" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T100" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="101" spans="2:20" x14ac:dyDescent="0.45">
@@ -7933,25 +7248,25 @@
         <v>126</v>
       </c>
       <c r="N101" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O101" t="s">
         <v>120</v>
       </c>
       <c r="P101" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="Q101" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R101" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S101" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T101" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="102" spans="2:20" x14ac:dyDescent="0.45">
@@ -7986,25 +7301,25 @@
         <v>100</v>
       </c>
       <c r="N102" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O102" t="s">
         <v>122</v>
       </c>
       <c r="P102" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="Q102" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R102" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S102" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T102" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="103" spans="2:20" x14ac:dyDescent="0.45">
@@ -8015,7 +7330,7 @@
         <v>78</v>
       </c>
       <c r="D103" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="E103">
         <v>1964</v>
@@ -8039,25 +7354,25 @@
         <v>100</v>
       </c>
       <c r="N103" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O103" t="s">
         <v>123</v>
       </c>
       <c r="P103" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="Q103" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R103" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S103" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="T103" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="104" spans="2:20" x14ac:dyDescent="0.45">
@@ -8092,25 +7407,25 @@
         <v>100</v>
       </c>
       <c r="N104" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O104" t="s">
         <v>125</v>
       </c>
       <c r="P104" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="Q104" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R104" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S104" t="s">
-        <v>198</v>
+        <v>279</v>
       </c>
       <c r="T104" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
     </row>
     <row r="105" spans="2:20" x14ac:dyDescent="0.45">
@@ -8121,652 +7436,685 @@
         <v>126</v>
       </c>
       <c r="D105" t="s">
-        <v>24</v>
+        <v>127</v>
       </c>
       <c r="E105">
-        <v>1998</v>
+        <v>2022</v>
       </c>
       <c r="F105">
-        <v>0.377</v>
+        <v>8.3726904507382155E-2</v>
       </c>
       <c r="G105">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H105">
-        <v>1100</v>
+        <v>1035</v>
       </c>
       <c r="I105">
-        <v>35</v>
+        <v>16.5</v>
       </c>
       <c r="J105">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="K105">
-        <v>50</v>
+        <v>33</v>
+      </c>
+      <c r="L105">
+        <v>0.1910967417235313</v>
       </c>
       <c r="N105" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O105" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P105" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="Q105" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R105" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S105" t="s">
-        <v>198</v>
+        <v>279</v>
       </c>
       <c r="T105" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
     </row>
     <row r="106" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B106" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C106" t="s">
         <v>126</v>
       </c>
       <c r="D106" t="s">
-        <v>24</v>
+        <v>129</v>
       </c>
       <c r="E106">
-        <v>1996</v>
+        <v>2024</v>
       </c>
       <c r="F106">
-        <v>7.0000000000000007E-2</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="G106">
-        <v>0.48000000000000004</v>
+        <v>1</v>
       </c>
       <c r="H106">
-        <v>1265</v>
+        <v>1035</v>
       </c>
       <c r="I106">
-        <v>38.5</v>
+        <v>16.5</v>
       </c>
       <c r="J106">
-        <v>3.850000000000001</v>
+        <v>0</v>
       </c>
       <c r="K106">
-        <v>59</v>
+        <v>31</v>
+      </c>
+      <c r="L106">
+        <v>0.1767456226726275</v>
       </c>
       <c r="N106" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O106" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="P106" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="Q106" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R106" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S106" t="s">
-        <v>198</v>
+        <v>279</v>
       </c>
       <c r="T106" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
     </row>
     <row r="107" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B107" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C107" t="s">
         <v>126</v>
       </c>
       <c r="D107" t="s">
-        <v>18</v>
+        <v>131</v>
       </c>
       <c r="E107">
-        <v>2007</v>
+        <v>2026</v>
       </c>
       <c r="F107">
-        <v>0.40300000000000002</v>
+        <v>0.17</v>
       </c>
       <c r="G107">
-        <v>0.52</v>
+        <v>1</v>
       </c>
       <c r="H107">
-        <v>1100</v>
+        <v>1035</v>
       </c>
       <c r="I107">
-        <v>35</v>
+        <v>16.5</v>
       </c>
       <c r="J107">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="K107">
-        <v>50</v>
+        <v>30</v>
+      </c>
+      <c r="L107">
+        <v>0.18349581246367919</v>
       </c>
       <c r="N107" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O107" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="P107" t="s">
-        <v>211</v>
+        <v>188</v>
       </c>
       <c r="Q107" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R107" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S107" t="s">
-        <v>198</v>
+        <v>279</v>
       </c>
       <c r="T107" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
     </row>
     <row r="108" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B108" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C108" t="s">
         <v>126</v>
       </c>
       <c r="D108" t="s">
-        <v>23</v>
+        <v>133</v>
       </c>
       <c r="E108">
-        <v>1987</v>
+        <v>2028</v>
       </c>
       <c r="F108">
-        <v>0.112</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="G108">
-        <v>0.41</v>
+        <v>1</v>
       </c>
       <c r="H108">
-        <v>1265</v>
+        <v>1215</v>
       </c>
       <c r="I108">
-        <v>38.5</v>
+        <v>19.5</v>
       </c>
       <c r="J108">
-        <v>3.8500000000000005</v>
+        <v>0</v>
       </c>
       <c r="K108">
-        <v>68</v>
+        <v>30</v>
+      </c>
+      <c r="L108">
+        <v>0.17721048910943363</v>
       </c>
       <c r="N108" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O108" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="P108" t="s">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="Q108" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R108" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S108" t="s">
-        <v>198</v>
+        <v>279</v>
       </c>
       <c r="T108" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
     </row>
     <row r="109" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B109" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C109" t="s">
         <v>126</v>
       </c>
       <c r="D109" t="s">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="E109">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="F109">
-        <v>0.05</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G109">
-        <v>0.28999999999999998</v>
+        <v>1</v>
       </c>
       <c r="H109">
         <v>1215</v>
       </c>
       <c r="I109">
-        <v>28.6</v>
+        <v>19.5</v>
       </c>
       <c r="J109">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="K109">
-        <v>40</v>
+        <v>32</v>
+      </c>
+      <c r="L109">
+        <v>0.20333316960890149</v>
       </c>
       <c r="N109" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O109" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="P109" t="s">
-        <v>213</v>
+        <v>188</v>
       </c>
       <c r="Q109" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R109" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S109" t="s">
-        <v>198</v>
+        <v>279</v>
       </c>
       <c r="T109" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
     </row>
     <row r="110" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B110" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C110" t="s">
         <v>126</v>
       </c>
       <c r="D110" t="s">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="E110">
-        <v>2013</v>
+        <v>2025</v>
       </c>
       <c r="F110">
-        <v>0.05</v>
+        <v>2.0799999999999999E-2</v>
       </c>
       <c r="G110">
-        <v>0.28999999999999998</v>
+        <v>1</v>
       </c>
       <c r="H110">
         <v>1215</v>
       </c>
       <c r="I110">
-        <v>28.6</v>
+        <v>19.5</v>
       </c>
       <c r="J110">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="K110">
-        <v>40</v>
+        <v>30</v>
+      </c>
+      <c r="L110">
+        <v>0.20333316960890147</v>
       </c>
       <c r="N110" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O110" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="P110" t="s">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="Q110" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R110" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S110" t="s">
-        <v>198</v>
+        <v>279</v>
       </c>
       <c r="T110" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
     </row>
     <row r="111" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B111" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C111" t="s">
         <v>126</v>
       </c>
       <c r="D111" t="s">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="E111">
-        <v>2011</v>
+        <v>2028</v>
       </c>
       <c r="F111">
-        <v>0.105</v>
+        <v>2.4E-2</v>
       </c>
       <c r="G111">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="H111">
-        <v>1035</v>
+        <v>1215</v>
       </c>
       <c r="I111">
-        <v>24.200000000000003</v>
+        <v>19.5</v>
       </c>
       <c r="J111">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="K111">
-        <v>40</v>
+        <v>30</v>
+      </c>
+      <c r="L111">
+        <v>0.20333316960890149</v>
       </c>
       <c r="N111" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O111" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="P111" t="s">
-        <v>215</v>
+        <v>188</v>
       </c>
       <c r="Q111" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R111" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S111" t="s">
-        <v>198</v>
+        <v>279</v>
       </c>
       <c r="T111" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
     </row>
     <row r="112" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B112" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C112" t="s">
         <v>126</v>
       </c>
       <c r="D112" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="E112">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="F112">
-        <v>0.105</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="G112">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="H112">
-        <v>1035</v>
+        <v>1215</v>
       </c>
       <c r="I112">
-        <v>24.200000000000003</v>
+        <v>19.5</v>
       </c>
       <c r="J112">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="K112">
-        <v>40</v>
+        <v>34</v>
+      </c>
+      <c r="L112">
+        <v>0.18888135654523</v>
       </c>
       <c r="N112" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O112" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="P112" t="s">
-        <v>216</v>
+        <v>188</v>
       </c>
       <c r="Q112" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R112" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S112" t="s">
-        <v>198</v>
+        <v>279</v>
       </c>
       <c r="T112" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
     </row>
     <row r="113" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B113" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C113" t="s">
         <v>126</v>
       </c>
       <c r="D113" t="s">
-        <v>24</v>
+        <v>139</v>
       </c>
       <c r="E113">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="F113">
-        <v>0.05</v>
+        <v>1.9E-3</v>
       </c>
       <c r="G113">
-        <v>0.28999999999999998</v>
+        <v>1</v>
       </c>
       <c r="H113">
         <v>1215</v>
       </c>
       <c r="I113">
-        <v>28.6</v>
+        <v>19.5</v>
       </c>
       <c r="J113">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="K113">
-        <v>40</v>
+        <v>34</v>
+      </c>
+      <c r="L113">
+        <v>0.19504090243261779</v>
       </c>
       <c r="N113" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O113" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="P113" t="s">
-        <v>217</v>
+        <v>188</v>
       </c>
       <c r="Q113" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R113" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S113" t="s">
-        <v>198</v>
+        <v>279</v>
       </c>
       <c r="T113" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
     </row>
     <row r="114" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B114" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C114" t="s">
         <v>126</v>
       </c>
       <c r="D114" t="s">
-        <v>24</v>
+        <v>141</v>
       </c>
       <c r="E114">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="F114">
-        <v>0.05</v>
+        <v>8.5460774302680204E-2</v>
       </c>
       <c r="G114">
-        <v>0.28999999999999998</v>
+        <v>1</v>
       </c>
       <c r="H114">
-        <v>1215</v>
+        <v>1035</v>
       </c>
       <c r="I114">
-        <v>28.6</v>
+        <v>16.5</v>
       </c>
       <c r="J114">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="K114">
-        <v>40</v>
+        <v>33</v>
+      </c>
+      <c r="L114">
+        <v>0.1910967417235313</v>
       </c>
       <c r="N114" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O114" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="P114" t="s">
-        <v>218</v>
+        <v>188</v>
       </c>
       <c r="Q114" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R114" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S114" t="s">
-        <v>198</v>
+        <v>279</v>
       </c>
       <c r="T114" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
     </row>
     <row r="115" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B115" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C115" t="s">
         <v>126</v>
       </c>
       <c r="D115" t="s">
-        <v>18</v>
+        <v>143</v>
       </c>
       <c r="E115">
-        <v>2004</v>
+        <v>2015</v>
       </c>
       <c r="F115">
-        <v>5.0999999999999997E-2</v>
+        <v>1.4E-3</v>
       </c>
       <c r="G115">
-        <v>0.28000000000000003</v>
+        <v>1</v>
       </c>
       <c r="H115">
-        <v>1035</v>
+        <v>1215</v>
       </c>
       <c r="I115">
-        <v>24.2</v>
+        <v>19.5</v>
       </c>
       <c r="J115">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="K115">
         <v>40</v>
       </c>
+      <c r="L115">
+        <v>0.19281073694608941</v>
+      </c>
       <c r="N115" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O115" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="P115" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="Q115" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R115" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S115" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="T115" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="116" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B116" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C116" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="D116" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="E116">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="F116">
-        <v>8.3726904507382155E-2</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="G116">
         <v>1</v>
       </c>
       <c r="H116">
-        <v>1035</v>
+        <v>1215</v>
       </c>
       <c r="I116">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="J116">
         <v>0</v>
       </c>
       <c r="K116">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="L116">
-        <v>0.19109674172353133</v>
+        <v>0.19996746694328421</v>
       </c>
       <c r="N116" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O116" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="P116" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="Q116" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R116" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S116" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="T116" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="117" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B117" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C117" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="D117" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="E117">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="F117">
-        <v>5.1999999999999998E-2</v>
+        <v>8.5012321189937637E-2</v>
       </c>
       <c r="G117">
         <v>1</v>
@@ -8781,104 +8129,104 @@
         <v>0</v>
       </c>
       <c r="K117">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L117">
-        <v>0.1767456226726275</v>
+        <v>0.1910967417235313</v>
       </c>
       <c r="N117" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O117" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="P117" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="Q117" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R117" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S117" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="T117" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="118" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B118" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C118" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="D118" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="E118">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="F118">
-        <v>0.17</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="G118">
         <v>1</v>
       </c>
       <c r="H118">
-        <v>1035</v>
+        <v>1215</v>
       </c>
       <c r="I118">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="J118">
         <v>0</v>
       </c>
       <c r="K118">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L118">
-        <v>0.18349581246367919</v>
+        <v>0.1868255198840435</v>
       </c>
       <c r="N118" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O118" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="P118" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="Q118" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R118" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S118" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="T118" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="119" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B119" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C119" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="D119" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="E119">
-        <v>2028</v>
+        <v>2023</v>
       </c>
       <c r="F119">
-        <v>4.9000000000000002E-2</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="G119">
         <v>1</v>
@@ -8893,1251 +8241,635 @@
         <v>0</v>
       </c>
       <c r="K119">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L119">
-        <v>0.17721048910943363</v>
+        <v>0.18218348485866612</v>
       </c>
       <c r="N119" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O119" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="P119" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="Q119" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R119" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S119" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="T119" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="120" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B120" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C120" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="D120" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="E120">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F120">
-        <v>3.9E-2</v>
+        <v>2.745110531926025E-2</v>
       </c>
       <c r="G120">
-        <v>1</v>
-      </c>
-      <c r="H120">
-        <v>1215</v>
-      </c>
-      <c r="I120">
-        <v>19.5</v>
-      </c>
-      <c r="J120">
-        <v>0</v>
-      </c>
-      <c r="K120">
-        <v>32</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="L120">
-        <v>0.20333316960890149</v>
+        <v>0.41172044122569984</v>
       </c>
       <c r="N120" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O120" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="P120" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="Q120" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R120" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S120" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="T120" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="121" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B121" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="C121" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="D121" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="E121">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="F121">
-        <v>2.0799999999999999E-2</v>
+        <v>2.8327438797566478E-2</v>
       </c>
       <c r="G121">
-        <v>1</v>
-      </c>
-      <c r="H121">
-        <v>1215</v>
-      </c>
-      <c r="I121">
-        <v>19.5</v>
-      </c>
-      <c r="J121">
-        <v>0</v>
-      </c>
-      <c r="K121">
-        <v>30</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="L121">
-        <v>0.20333316960890147</v>
+        <v>0.41172044122569984</v>
       </c>
       <c r="N121" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O121" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="P121" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="Q121" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R121" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S121" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="T121" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="122" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B122" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="C122" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="D122" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="E122">
-        <v>2028</v>
+        <v>2007</v>
       </c>
       <c r="F122">
-        <v>2.4E-2</v>
+        <v>5.8000000000000003E-2</v>
       </c>
       <c r="G122">
-        <v>1</v>
-      </c>
-      <c r="H122">
-        <v>1215</v>
-      </c>
-      <c r="I122">
-        <v>19.5</v>
-      </c>
-      <c r="J122">
-        <v>0</v>
-      </c>
-      <c r="K122">
-        <v>30</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="L122">
-        <v>0.20333316960890149</v>
+        <v>0.29996245639681474</v>
       </c>
       <c r="N122" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O122" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="P122" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="Q122" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R122" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S122" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="T122" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="123" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B123" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="C123" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="D123" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="E123">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="F123">
-        <v>2.5000000000000001E-3</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="G123">
-        <v>1</v>
-      </c>
-      <c r="H123">
-        <v>1215</v>
-      </c>
-      <c r="I123">
-        <v>19.5</v>
-      </c>
-      <c r="J123">
-        <v>0</v>
-      </c>
-      <c r="K123">
-        <v>34</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="L123">
-        <v>0.18888135654523</v>
+        <v>0.43764790128670528</v>
       </c>
       <c r="N123" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O123" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="P123" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="Q123" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R123" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S123" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="T123" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="124" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B124" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="C124" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="D124" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="E124">
-        <v>2021</v>
+        <v>2027</v>
       </c>
       <c r="F124">
-        <v>1.9E-3</v>
+        <v>0.155</v>
       </c>
       <c r="G124">
-        <v>1</v>
-      </c>
-      <c r="H124">
-        <v>1215</v>
-      </c>
-      <c r="I124">
-        <v>19.5</v>
-      </c>
-      <c r="J124">
-        <v>0</v>
-      </c>
-      <c r="K124">
-        <v>34</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="L124">
-        <v>0.19504090243261779</v>
+        <v>0.43764790128670528</v>
       </c>
       <c r="N124" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O124" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="P124" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="Q124" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R124" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S124" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="T124" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="125" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B125" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="C125" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="D125" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="E125">
-        <v>2022</v>
+        <v>2011</v>
       </c>
       <c r="F125">
-        <v>8.5460774302680204E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="G125">
-        <v>1</v>
-      </c>
-      <c r="H125">
-        <v>1035</v>
-      </c>
-      <c r="I125">
-        <v>16.5</v>
-      </c>
-      <c r="J125">
-        <v>0</v>
-      </c>
-      <c r="K125">
-        <v>33</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="L125">
-        <v>0.19109674172353133</v>
+        <v>0.30750940020437478</v>
       </c>
       <c r="N125" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O125" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="P125" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="Q125" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R125" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S125" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="T125" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="126" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B126" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="C126" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="D126" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="E126">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="F126">
-        <v>1.4E-3</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="G126">
-        <v>1</v>
-      </c>
-      <c r="H126">
-        <v>1215</v>
-      </c>
-      <c r="I126">
-        <v>19.5</v>
-      </c>
-      <c r="J126">
-        <v>0</v>
-      </c>
-      <c r="K126">
-        <v>40</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="L126">
-        <v>0.19281073694608941</v>
+        <v>0.5665247689951628</v>
       </c>
       <c r="N126" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O126" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="P126" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="Q126" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R126" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S126" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="T126" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="127" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B127" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="C127" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="D127" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="E127">
-        <v>2025</v>
+        <v>2014</v>
       </c>
       <c r="F127">
-        <v>3.6999999999999998E-2</v>
+        <v>0.06</v>
       </c>
       <c r="G127">
-        <v>1</v>
-      </c>
-      <c r="H127">
-        <v>1215</v>
-      </c>
-      <c r="I127">
-        <v>19.5</v>
-      </c>
-      <c r="J127">
-        <v>0</v>
-      </c>
-      <c r="K127">
-        <v>30</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="L127">
-        <v>0.19996746694328421</v>
+        <v>0.5665247689951628</v>
       </c>
       <c r="N127" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O127" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="P127" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="Q127" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R127" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="S127" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="T127" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="128" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B128" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C128" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="D128" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="E128">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F128">
-        <v>8.5012321189937637E-2</v>
+        <v>0.13300000000000001</v>
       </c>
       <c r="G128">
-        <v>1</v>
-      </c>
-      <c r="H128">
-        <v>1035</v>
-      </c>
-      <c r="I128">
-        <v>16.5</v>
-      </c>
-      <c r="J128">
-        <v>0</v>
-      </c>
-      <c r="K128">
-        <v>33</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="L128">
-        <v>0.19109674172353133</v>
-      </c>
-      <c r="N128" t="s">
-        <v>194</v>
-      </c>
-      <c r="O128" t="s">
-        <v>164</v>
-      </c>
-      <c r="P128" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q128" t="s">
-        <v>196</v>
-      </c>
-      <c r="R128" t="s">
-        <v>197</v>
-      </c>
-      <c r="S128" t="s">
-        <v>291</v>
-      </c>
-      <c r="T128" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="129" spans="2:20" x14ac:dyDescent="0.45">
+        <v>0.51800914605060178</v>
+      </c>
+    </row>
+    <row r="129" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B129" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="C129" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="D129" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="E129">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="F129">
-        <v>3.5000000000000003E-2</v>
+        <v>0.11899999999999999</v>
       </c>
       <c r="G129">
-        <v>1</v>
-      </c>
-      <c r="H129">
-        <v>1215</v>
-      </c>
-      <c r="I129">
-        <v>19.5</v>
-      </c>
-      <c r="J129">
-        <v>0</v>
-      </c>
-      <c r="K129">
-        <v>31</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="L129">
-        <v>0.1868255198840435</v>
-      </c>
-      <c r="N129" t="s">
-        <v>194</v>
-      </c>
-      <c r="O129" t="s">
+        <v>0.42476329815466568</v>
+      </c>
+    </row>
+    <row r="130" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B130" t="s">
         <v>167</v>
       </c>
-      <c r="P129" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q129" t="s">
-        <v>196</v>
-      </c>
-      <c r="R129" t="s">
-        <v>197</v>
-      </c>
-      <c r="S129" t="s">
-        <v>291</v>
-      </c>
-      <c r="T129" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="130" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B130" t="s">
-        <v>162</v>
-      </c>
       <c r="C130" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="D130" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="E130">
         <v>2023</v>
       </c>
       <c r="F130">
-        <v>3.0999999999999999E-3</v>
+        <v>0.10299999999999999</v>
       </c>
       <c r="G130">
-        <v>1</v>
-      </c>
-      <c r="H130">
-        <v>1215</v>
-      </c>
-      <c r="I130">
-        <v>19.5</v>
-      </c>
-      <c r="J130">
-        <v>0</v>
-      </c>
-      <c r="K130">
-        <v>32</v>
+        <v>0.33123000000000008</v>
       </c>
       <c r="L130">
-        <v>0.18218348485866612</v>
-      </c>
-      <c r="N130" t="s">
-        <v>194</v>
-      </c>
-      <c r="O130" t="s">
+        <v>0.42476329815466574</v>
+      </c>
+    </row>
+    <row r="131" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B131" t="s">
         <v>169</v>
       </c>
-      <c r="P130" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q130" t="s">
-        <v>196</v>
-      </c>
-      <c r="R130" t="s">
-        <v>197</v>
-      </c>
-      <c r="S130" t="s">
-        <v>291</v>
-      </c>
-      <c r="T130" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="131" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B131" t="s">
-        <v>164</v>
-      </c>
       <c r="C131" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="D131" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E131">
-        <v>2022</v>
+        <v>2011</v>
       </c>
       <c r="F131">
-        <v>2.745110531926025E-2</v>
+        <v>6.4000000000000001E-2</v>
       </c>
       <c r="G131">
         <v>0.33123000000000002</v>
       </c>
       <c r="L131">
-        <v>0.41172044122569984</v>
-      </c>
-      <c r="N131" t="s">
-        <v>194</v>
-      </c>
-      <c r="O131" t="s">
+        <v>0.30197167613346337</v>
+      </c>
+    </row>
+    <row r="132" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B132" t="s">
         <v>171</v>
       </c>
-      <c r="P131" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q131" t="s">
-        <v>196</v>
-      </c>
-      <c r="R131" t="s">
-        <v>197</v>
-      </c>
-      <c r="S131" t="s">
-        <v>291</v>
-      </c>
-      <c r="T131" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="132" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B132" t="s">
-        <v>167</v>
-      </c>
       <c r="C132" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="D132" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E132">
-        <v>2022</v>
+        <v>1999</v>
       </c>
       <c r="F132">
-        <v>2.8327438797566478E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="G132">
         <v>0.33123000000000002</v>
       </c>
       <c r="L132">
-        <v>0.41172044122569984</v>
-      </c>
-      <c r="N132" t="s">
-        <v>194</v>
-      </c>
-      <c r="O132" t="s">
-        <v>173</v>
-      </c>
-      <c r="P132" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q132" t="s">
-        <v>196</v>
-      </c>
-      <c r="R132" t="s">
-        <v>197</v>
-      </c>
-      <c r="S132" t="s">
-        <v>291</v>
-      </c>
-      <c r="T132" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="133" spans="2:20" x14ac:dyDescent="0.45">
+        <v>0.40395409929757359</v>
+      </c>
+    </row>
+    <row r="133" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B133" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C133" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="D133" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E133">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="F133">
-        <v>5.8000000000000003E-2</v>
+        <v>0.127</v>
       </c>
       <c r="G133">
         <v>0.33123000000000002</v>
       </c>
       <c r="L133">
-        <v>0.29996245639681474</v>
-      </c>
-      <c r="N133" t="s">
-        <v>194</v>
-      </c>
-      <c r="O133" t="s">
-        <v>175</v>
-      </c>
-      <c r="P133" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q133" t="s">
-        <v>196</v>
-      </c>
-      <c r="R133" t="s">
-        <v>197</v>
-      </c>
-      <c r="S133" t="s">
-        <v>291</v>
-      </c>
-      <c r="T133" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="134" spans="2:20" x14ac:dyDescent="0.45">
+        <v>0.40395409929757359</v>
+      </c>
+    </row>
+    <row r="134" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B134" t="s">
         <v>171</v>
       </c>
       <c r="C134" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="D134" t="s">
         <v>172</v>
       </c>
       <c r="E134">
-        <v>2023</v>
+        <v>2007</v>
       </c>
       <c r="F134">
-        <v>4.2999999999999997E-2</v>
+        <v>9.2999999999999999E-2</v>
       </c>
       <c r="G134">
         <v>0.33123000000000002</v>
       </c>
       <c r="L134">
-        <v>0.43764790128670528</v>
-      </c>
-      <c r="N134" t="s">
-        <v>194</v>
-      </c>
-      <c r="O134" t="s">
-        <v>177</v>
-      </c>
-      <c r="P134" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q134" t="s">
-        <v>196</v>
-      </c>
-      <c r="R134" t="s">
-        <v>197</v>
-      </c>
-      <c r="S134" t="s">
-        <v>291</v>
-      </c>
-      <c r="T134" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="135" spans="2:20" x14ac:dyDescent="0.45">
+        <v>0.40395409929757353</v>
+      </c>
+    </row>
+    <row r="135" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B135" t="s">
         <v>171</v>
       </c>
       <c r="C135" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="D135" t="s">
         <v>172</v>
       </c>
       <c r="E135">
-        <v>2027</v>
+        <v>2009</v>
       </c>
       <c r="F135">
-        <v>0.155</v>
+        <v>0.03</v>
       </c>
       <c r="G135">
         <v>0.33123000000000002</v>
       </c>
       <c r="L135">
-        <v>0.43764790128670528</v>
-      </c>
-      <c r="N135" t="s">
-        <v>194</v>
-      </c>
-      <c r="O135" t="s">
-        <v>179</v>
-      </c>
-      <c r="P135" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q135" t="s">
-        <v>196</v>
-      </c>
-      <c r="R135" t="s">
-        <v>197</v>
-      </c>
-      <c r="S135" t="s">
-        <v>291</v>
-      </c>
-      <c r="T135" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="136" spans="2:20" x14ac:dyDescent="0.45">
+        <v>0.40395409929757359</v>
+      </c>
+    </row>
+    <row r="136" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B136" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C136" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="D136" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E136">
         <v>2011</v>
       </c>
       <c r="F136">
-        <v>3.5999999999999997E-2</v>
+        <v>1.6E-2</v>
       </c>
       <c r="G136">
         <v>0.33123000000000002</v>
       </c>
       <c r="L136">
-        <v>0.30750940020437478</v>
-      </c>
-      <c r="N136" t="s">
-        <v>194</v>
-      </c>
-      <c r="O136" t="s">
-        <v>181</v>
-      </c>
-      <c r="P136" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q136" t="s">
-        <v>196</v>
-      </c>
-      <c r="R136" t="s">
-        <v>197</v>
-      </c>
-      <c r="S136" t="s">
-        <v>291</v>
-      </c>
-      <c r="T136" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="137" spans="2:20" x14ac:dyDescent="0.45">
+        <v>0.40395409929757359</v>
+      </c>
+    </row>
+    <row r="137" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B137" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C137" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="D137" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E137">
-        <v>2009</v>
+        <v>2022</v>
       </c>
       <c r="F137">
-        <v>0.14299999999999999</v>
+        <v>2.7221455883173235E-2</v>
       </c>
       <c r="G137">
         <v>0.33123000000000002</v>
       </c>
       <c r="L137">
-        <v>0.5665247689951628</v>
-      </c>
-      <c r="N137" t="s">
-        <v>194</v>
-      </c>
-      <c r="O137" t="s">
-        <v>183</v>
-      </c>
-      <c r="P137" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q137" t="s">
-        <v>196</v>
-      </c>
-      <c r="R137" t="s">
-        <v>197</v>
-      </c>
-      <c r="S137" t="s">
-        <v>291</v>
-      </c>
-      <c r="T137" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="138" spans="2:20" x14ac:dyDescent="0.45">
+        <v>0.41172044122569984</v>
+      </c>
+    </row>
+    <row r="138" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B138" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C138" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="D138" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E138">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="F138">
-        <v>0.06</v>
+        <v>0.17599999999999999</v>
       </c>
       <c r="G138">
         <v>0.33123000000000002</v>
       </c>
       <c r="L138">
-        <v>0.5665247689951628</v>
-      </c>
-      <c r="N138" t="s">
-        <v>194</v>
-      </c>
-      <c r="O138" t="s">
-        <v>185</v>
-      </c>
-      <c r="P138" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q138" t="s">
-        <v>196</v>
-      </c>
-      <c r="R138" t="s">
-        <v>197</v>
-      </c>
-      <c r="S138" t="s">
-        <v>291</v>
-      </c>
-      <c r="T138" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="139" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B139" t="s">
-        <v>177</v>
-      </c>
-      <c r="C139" t="s">
-        <v>165</v>
-      </c>
-      <c r="D139" t="s">
-        <v>178</v>
-      </c>
-      <c r="E139">
-        <v>2021</v>
-      </c>
-      <c r="F139">
-        <v>0.13300000000000001</v>
-      </c>
-      <c r="G139">
-        <v>0.33123000000000002</v>
-      </c>
-      <c r="L139">
-        <v>0.51800914605060178</v>
-      </c>
-    </row>
-    <row r="140" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B140" t="s">
-        <v>179</v>
-      </c>
-      <c r="C140" t="s">
-        <v>165</v>
-      </c>
-      <c r="D140" t="s">
-        <v>180</v>
-      </c>
-      <c r="E140">
-        <v>2021</v>
-      </c>
-      <c r="F140">
-        <v>0.11899999999999999</v>
-      </c>
-      <c r="G140">
-        <v>0.33123000000000002</v>
-      </c>
-      <c r="L140">
-        <v>0.42476329815466568</v>
-      </c>
-    </row>
-    <row r="141" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B141" t="s">
-        <v>179</v>
-      </c>
-      <c r="C141" t="s">
-        <v>165</v>
-      </c>
-      <c r="D141" t="s">
-        <v>180</v>
-      </c>
-      <c r="E141">
-        <v>2023</v>
-      </c>
-      <c r="F141">
-        <v>0.10299999999999999</v>
-      </c>
-      <c r="G141">
-        <v>0.33123000000000008</v>
-      </c>
-      <c r="L141">
-        <v>0.42476329815466574</v>
-      </c>
-    </row>
-    <row r="142" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B142" t="s">
-        <v>181</v>
-      </c>
-      <c r="C142" t="s">
-        <v>165</v>
-      </c>
-      <c r="D142" t="s">
-        <v>182</v>
-      </c>
-      <c r="E142">
-        <v>2011</v>
-      </c>
-      <c r="F142">
-        <v>6.4000000000000001E-2</v>
-      </c>
-      <c r="G142">
-        <v>0.33123000000000002</v>
-      </c>
-      <c r="L142">
-        <v>0.30197167613346337</v>
-      </c>
-    </row>
-    <row r="143" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B143" t="s">
-        <v>183</v>
-      </c>
-      <c r="C143" t="s">
-        <v>165</v>
-      </c>
-      <c r="D143" t="s">
-        <v>184</v>
-      </c>
-      <c r="E143">
-        <v>1999</v>
-      </c>
-      <c r="F143">
-        <v>3.2000000000000001E-2</v>
-      </c>
-      <c r="G143">
-        <v>0.33123000000000002</v>
-      </c>
-      <c r="L143">
-        <v>0.40395409929757359</v>
-      </c>
-    </row>
-    <row r="144" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B144" t="s">
-        <v>183</v>
-      </c>
-      <c r="C144" t="s">
-        <v>165</v>
-      </c>
-      <c r="D144" t="s">
-        <v>184</v>
-      </c>
-      <c r="E144">
-        <v>2004</v>
-      </c>
-      <c r="F144">
-        <v>0.127</v>
-      </c>
-      <c r="G144">
-        <v>0.33123000000000002</v>
-      </c>
-      <c r="L144">
-        <v>0.40395409929757359</v>
-      </c>
-    </row>
-    <row r="145" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B145" t="s">
-        <v>183</v>
-      </c>
-      <c r="C145" t="s">
-        <v>165</v>
-      </c>
-      <c r="D145" t="s">
-        <v>184</v>
-      </c>
-      <c r="E145">
-        <v>2007</v>
-      </c>
-      <c r="F145">
-        <v>9.2999999999999999E-2</v>
-      </c>
-      <c r="G145">
-        <v>0.33123000000000002</v>
-      </c>
-      <c r="L145">
-        <v>0.40395409929757353</v>
-      </c>
-    </row>
-    <row r="146" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B146" t="s">
-        <v>183</v>
-      </c>
-      <c r="C146" t="s">
-        <v>165</v>
-      </c>
-      <c r="D146" t="s">
-        <v>184</v>
-      </c>
-      <c r="E146">
-        <v>2009</v>
-      </c>
-      <c r="F146">
-        <v>0.03</v>
-      </c>
-      <c r="G146">
-        <v>0.33123000000000002</v>
-      </c>
-      <c r="L146">
-        <v>0.40395409929757359</v>
-      </c>
-    </row>
-    <row r="147" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B147" t="s">
-        <v>183</v>
-      </c>
-      <c r="C147" t="s">
-        <v>165</v>
-      </c>
-      <c r="D147" t="s">
-        <v>184</v>
-      </c>
-      <c r="E147">
-        <v>2011</v>
-      </c>
-      <c r="F147">
-        <v>1.6E-2</v>
-      </c>
-      <c r="G147">
-        <v>0.33123000000000002</v>
-      </c>
-      <c r="L147">
-        <v>0.40395409929757359</v>
-      </c>
-    </row>
-    <row r="148" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B148" t="s">
-        <v>183</v>
-      </c>
-      <c r="C148" t="s">
-        <v>165</v>
-      </c>
-      <c r="D148" t="s">
-        <v>184</v>
-      </c>
-      <c r="E148">
-        <v>2022</v>
-      </c>
-      <c r="F148">
-        <v>2.7221455883173235E-2</v>
-      </c>
-      <c r="G148">
-        <v>0.33123000000000002</v>
-      </c>
-      <c r="L148">
-        <v>0.41172044122569984</v>
-      </c>
-    </row>
-    <row r="149" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B149" t="s">
-        <v>185</v>
-      </c>
-      <c r="C149" t="s">
-        <v>165</v>
-      </c>
-      <c r="D149" t="s">
-        <v>186</v>
-      </c>
-      <c r="E149">
-        <v>2024</v>
-      </c>
-      <c r="F149">
-        <v>0.17599999999999999</v>
-      </c>
-      <c r="G149">
-        <v>0.33123000000000002</v>
-      </c>
-      <c r="L149">
         <v>0.28243194746500749</v>
       </c>
     </row>

--- a/VerveStacks_NZL_grids/vt_vervestacks_NZL_v1.xlsx
+++ b/VerveStacks_NZL_grids/vt_vervestacks_NZL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{618646BF-9561-48D1-9AFD-6E74B6DEF9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{44AAD9E9-4A63-48F8-A834-2E5CD277BDAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1FB2EE62-C25B-4F4B-9480-7362BD69667A}"/>
+    <workbookView xWindow="2940" yWindow="2940" windowWidth="21600" windowHeight="12682" xr2:uid="{C89B5F03-8170-4862-9780-52D30BF45DF2}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="297">
   <si>
     <t>~fi_t</t>
   </si>
@@ -276,63 +276,63 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_w270018358-220</t>
+  </si>
+  <si>
+    <t>e_w93556808-220</t>
+  </si>
+  <si>
+    <t>e_NZ13-220</t>
+  </si>
+  <si>
+    <t>e_NZ33-220</t>
+  </si>
+  <si>
+    <t>e_NZ22-220</t>
+  </si>
+  <si>
     <t>e_w412589726-220</t>
   </si>
   <si>
+    <t>e_NZ35-220</t>
+  </si>
+  <si>
+    <t>e_w180514007-220</t>
+  </si>
+  <si>
+    <t>e_w89664063-220</t>
+  </si>
+  <si>
+    <t>e_NZ40-220</t>
+  </si>
+  <si>
     <t>e_NZ12-220</t>
   </si>
   <si>
+    <t>e_NZ14-220</t>
+  </si>
+  <si>
+    <t>e_w272522517-220</t>
+  </si>
+  <si>
+    <t>e_w89636266-220</t>
+  </si>
+  <si>
     <t>e_NZ30-220</t>
   </si>
   <si>
     <t>e_w89637173-220</t>
   </si>
   <si>
-    <t>e_NZ40-220</t>
-  </si>
-  <si>
-    <t>e_w93556808-220</t>
-  </si>
-  <si>
-    <t>e_w272522517-220</t>
-  </si>
-  <si>
-    <t>e_w89636266-220</t>
+    <t>e_w89411122-220</t>
+  </si>
+  <si>
+    <t>e_NZ11-220</t>
   </si>
   <si>
     <t>e_w89637174-220</t>
   </si>
   <si>
-    <t>e_w89411122-220</t>
-  </si>
-  <si>
-    <t>e_NZ35-220</t>
-  </si>
-  <si>
-    <t>e_NZ22-220</t>
-  </si>
-  <si>
-    <t>e_NZ13-220</t>
-  </si>
-  <si>
-    <t>e_NZ33-220</t>
-  </si>
-  <si>
-    <t>e_w180514007-220</t>
-  </si>
-  <si>
-    <t>e_w89664063-220</t>
-  </si>
-  <si>
-    <t>e_NZ11-220</t>
-  </si>
-  <si>
-    <t>e_NZ14-220</t>
-  </si>
-  <si>
-    <t>e_w270018358-220</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000602849</t>
   </si>
   <si>
@@ -414,154 +414,100 @@
     <t>e_w169512273-220</t>
   </si>
   <si>
-    <t>ep_solar_pv_025</t>
+    <t>ep_solar_pv_001</t>
   </si>
   <si>
     <t>solar</t>
   </si>
   <si>
-    <t>elc_spv-NZL_0025</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_044</t>
-  </si>
-  <si>
-    <t>elc_spv-NZL_0044</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_051</t>
-  </si>
-  <si>
-    <t>elc_spv-NZL_0051</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_056</t>
-  </si>
-  <si>
-    <t>elc_spv-NZL_0056</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_058</t>
-  </si>
-  <si>
-    <t>elc_spv-NZL_0058</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_062</t>
-  </si>
-  <si>
-    <t>elc_spv-NZL_0062</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_064</t>
-  </si>
-  <si>
-    <t>elc_spv-NZL_0064</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_086</t>
-  </si>
-  <si>
-    <t>elc_spv-NZL_0086</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_088</t>
-  </si>
-  <si>
-    <t>elc_spv-NZL_0088</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_100</t>
-  </si>
-  <si>
-    <t>elc_spv-NZL_0100</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_102</t>
-  </si>
-  <si>
-    <t>elc_spv-NZL_0102</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_106</t>
-  </si>
-  <si>
-    <t>elc_spv-NZL_0106</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_110</t>
-  </si>
-  <si>
-    <t>elc_spv-NZL_0110</t>
-  </si>
-  <si>
-    <t>ep_windon_wind_000</t>
+    <t>elc_spv_001</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_002</t>
+  </si>
+  <si>
+    <t>elc_spv_002</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_003</t>
+  </si>
+  <si>
+    <t>elc_spv_003</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_004</t>
+  </si>
+  <si>
+    <t>elc_spv_004</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_006</t>
+  </si>
+  <si>
+    <t>elc_spv_006</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_007</t>
+  </si>
+  <si>
+    <t>elc_spv_007</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_012</t>
+  </si>
+  <si>
+    <t>elc_spv_012</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_014</t>
+  </si>
+  <si>
+    <t>elc_spv_014</t>
+  </si>
+  <si>
+    <t>ep_windon_wind</t>
   </si>
   <si>
     <t>windon</t>
   </si>
   <si>
-    <t>elc_won-NZL_0000</t>
-  </si>
-  <si>
-    <t>ep_windon_wind_004</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0004</t>
-  </si>
-  <si>
-    <t>ep_windon_wind_010</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0010</t>
-  </si>
-  <si>
-    <t>ep_windon_wind_016</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0016</t>
-  </si>
-  <si>
-    <t>ep_windon_wind_023</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0023</t>
-  </si>
-  <si>
-    <t>ep_windon_wind_068</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0068</t>
-  </si>
-  <si>
-    <t>ep_windon_wind_069</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0069</t>
-  </si>
-  <si>
-    <t>ep_windon_wind_080</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0080</t>
-  </si>
-  <si>
-    <t>ep_windon_wind_086</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0086</t>
-  </si>
-  <si>
-    <t>ep_windon_wind_091</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0091</t>
-  </si>
-  <si>
-    <t>ep_windon_wind_104</t>
-  </si>
-  <si>
-    <t>elc_won-NZL_0104</t>
+    <t>ELC</t>
+  </si>
+  <si>
+    <t>ep_windon_wind_001</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>ep_windon_wind_002</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>ep_windon_wind_003</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>ep_windon_wind_005</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>ep_windon_wind_007</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>ep_windon_wind_009</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
   </si>
   <si>
     <t>~fi_process</t>
@@ -618,15 +564,15 @@
     <t>Huntly power station_4</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/188180344-220_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/167293888-220_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - relation/17609399-220_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/188180344-220_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Stratford power station_CC1</t>
   </si>
   <si>
@@ -744,66 +690,66 @@
     <t>Wairakei geothermal power plant_A</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/180514007-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ12-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89411122-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/89664063-220_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/89637174-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ30-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/87928925-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ40-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ14-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/270018358-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ35-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89637173-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/272522517-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ33-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ11-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/412589726-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ13-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ22-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/89636266-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/89411122-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/412589726-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/272522517-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ33-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ30-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89637173-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ12-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ22-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ11-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/180514007-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89637174-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ14-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ13-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ35-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/270018358-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ40-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - way/93556808-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/87928925-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Arapuni hydroelectric plant_</t>
   </si>
   <si>
@@ -954,13 +900,13 @@
     <t>ccs retrofit of -- Glenbrook power station_1</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - relation/17609399-220_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/167293888-220_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/188180344-220_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - relation/17609399-220_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- McKee power station_2</t>
@@ -1352,7 +1298,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E8770C3-F466-4319-97C6-DE174508C341}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F12542B-9072-4BBC-A849-6F448F15ED35}">
   <dimension ref="B9:T27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1361,7 +1307,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.45">
@@ -1387,42 +1333,42 @@
         <v>9</v>
       </c>
       <c r="I10" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="J10" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="K10" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="L10" t="s">
         <v>10</v>
       </c>
       <c r="N10" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="O10" t="s">
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="Q10" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="R10" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="S10" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="T10" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
@@ -1455,30 +1401,30 @@
         <v>20</v>
       </c>
       <c r="N11" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O11" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="P11" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="Q11" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R11" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S11" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T11" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -1511,30 +1457,30 @@
         <v>20</v>
       </c>
       <c r="N12" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O12" t="s">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="P12" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="Q12" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R12" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S12" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T12" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>285</v>
+        <v>267</v>
       </c>
       <c r="C13" t="s">
         <v>17</v>
@@ -1567,30 +1513,30 @@
         <v>20</v>
       </c>
       <c r="N13" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O13" t="s">
-        <v>285</v>
+        <v>267</v>
       </c>
       <c r="P13" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="Q13" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R13" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S13" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T13" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="C14" t="s">
         <v>22</v>
@@ -1623,30 +1569,30 @@
         <v>20</v>
       </c>
       <c r="N14" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O14" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="P14" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="Q14" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R14" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S14" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T14" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="C15" t="s">
         <v>22</v>
@@ -1679,30 +1625,30 @@
         <v>20</v>
       </c>
       <c r="N15" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O15" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="P15" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="Q15" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R15" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S15" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T15" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="C16" t="s">
         <v>22</v>
@@ -1735,30 +1681,30 @@
         <v>20</v>
       </c>
       <c r="N16" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O16" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="P16" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="Q16" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R16" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S16" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T16" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="C17" t="s">
         <v>22</v>
@@ -1791,36 +1737,36 @@
         <v>20</v>
       </c>
       <c r="N17" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O17" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="P17" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="Q17" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R17" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S17" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T17" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="C18" t="s">
         <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E18">
         <v>0.50749999999999995</v>
@@ -1847,36 +1793,36 @@
         <v>20</v>
       </c>
       <c r="N18" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O18" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="P18" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="Q18" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R18" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S18" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T18" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="C19" t="s">
         <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E19">
         <v>0.50749999999999995</v>
@@ -1903,30 +1849,30 @@
         <v>20</v>
       </c>
       <c r="N19" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O19" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="P19" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="Q19" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R19" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S19" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T19" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="C20" t="s">
         <v>22</v>
@@ -1959,30 +1905,30 @@
         <v>20</v>
       </c>
       <c r="N20" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O20" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="P20" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="Q20" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R20" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S20" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T20" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="C21" t="s">
         <v>22</v>
@@ -2015,30 +1961,30 @@
         <v>20</v>
       </c>
       <c r="N21" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O21" t="s">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="P21" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="Q21" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R21" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S21" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T21" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>292</v>
+        <v>274</v>
       </c>
       <c r="C22" t="s">
         <v>22</v>
@@ -2071,30 +2017,30 @@
         <v>20</v>
       </c>
       <c r="N22" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O22" t="s">
-        <v>292</v>
+        <v>274</v>
       </c>
       <c r="P22" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="Q22" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R22" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S22" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T22" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>293</v>
+        <v>275</v>
       </c>
       <c r="C23" t="s">
         <v>22</v>
@@ -2127,30 +2073,30 @@
         <v>20</v>
       </c>
       <c r="N23" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O23" t="s">
-        <v>293</v>
+        <v>275</v>
       </c>
       <c r="P23" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="Q23" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R23" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S23" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T23" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="C24" t="s">
         <v>22</v>
@@ -2183,30 +2129,30 @@
         <v>20</v>
       </c>
       <c r="N24" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O24" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="P24" t="s">
-        <v>311</v>
+        <v>293</v>
       </c>
       <c r="Q24" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R24" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S24" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T24" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="C25" t="s">
         <v>22</v>
@@ -2239,30 +2185,30 @@
         <v>20</v>
       </c>
       <c r="N25" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O25" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="P25" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
       <c r="Q25" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R25" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S25" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T25" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="C26" t="s">
         <v>22</v>
@@ -2295,30 +2241,30 @@
         <v>20</v>
       </c>
       <c r="N26" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O26" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="P26" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="Q26" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R26" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S26" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T26" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="C27" t="s">
         <v>22</v>
@@ -2351,25 +2297,25 @@
         <v>20</v>
       </c>
       <c r="N27" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O27" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="P27" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="Q27" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R27" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S27" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T27" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2378,8 +2324,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73EBEADB-A272-436E-AC28-143A06BF3090}">
-  <dimension ref="B9:T138"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFA3FB72-804A-4A8D-83E1-8329E12C2E67}">
+  <dimension ref="B9:T137"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="9" spans="2:20" x14ac:dyDescent="0.45">
@@ -2387,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.45">
@@ -2425,25 +2371,25 @@
         <v>11</v>
       </c>
       <c r="N10" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="O10" t="s">
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="Q10" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="R10" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="S10" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="T10" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.45">
@@ -2478,25 +2424,25 @@
         <v>50</v>
       </c>
       <c r="N11" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O11" t="s">
         <v>12</v>
       </c>
       <c r="P11" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="Q11" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R11" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S11" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T11" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.45">
@@ -2531,25 +2477,25 @@
         <v>58</v>
       </c>
       <c r="N12" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O12" t="s">
         <v>15</v>
       </c>
       <c r="P12" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="Q12" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R12" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S12" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T12" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.45">
@@ -2584,25 +2530,25 @@
         <v>52</v>
       </c>
       <c r="N13" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O13" t="s">
         <v>16</v>
       </c>
       <c r="P13" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="Q13" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R13" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S13" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T13" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.45">
@@ -2637,25 +2583,25 @@
         <v>52</v>
       </c>
       <c r="N14" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O14" t="s">
         <v>19</v>
       </c>
       <c r="P14" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="Q14" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R14" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S14" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T14" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.45">
@@ -2690,25 +2636,25 @@
         <v>52</v>
       </c>
       <c r="N15" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O15" t="s">
         <v>20</v>
       </c>
       <c r="P15" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="Q15" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R15" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S15" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T15" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.45">
@@ -2719,49 +2665,49 @@
         <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E16">
         <v>2022</v>
       </c>
       <c r="F16">
-        <v>3.9117357695010534E-2</v>
+        <v>0.1585650035137034</v>
       </c>
       <c r="G16">
-        <v>0.56000000000000005</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H16">
-        <v>1350</v>
+        <v>1150</v>
       </c>
       <c r="I16">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="J16">
-        <v>3.5999999999999996</v>
+        <v>3.3000000000000003</v>
       </c>
       <c r="K16">
         <v>50</v>
       </c>
       <c r="N16" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O16" t="s">
         <v>21</v>
       </c>
       <c r="P16" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="Q16" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R16" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S16" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T16" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.45">
@@ -2772,49 +2718,49 @@
         <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E17">
         <v>2022</v>
       </c>
       <c r="F17">
-        <v>0.1585650035137034</v>
+        <v>3.9117357695010534E-2</v>
       </c>
       <c r="G17">
-        <v>0.57999999999999996</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H17">
-        <v>1150</v>
+        <v>1350</v>
       </c>
       <c r="I17">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J17">
-        <v>3.3000000000000003</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="K17">
         <v>50</v>
       </c>
       <c r="N17" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O17" t="s">
         <v>21</v>
       </c>
       <c r="P17" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="Q17" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R17" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S17" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T17" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.45">
@@ -2849,25 +2795,25 @@
         <v>50</v>
       </c>
       <c r="N18" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O18" t="s">
         <v>21</v>
       </c>
       <c r="P18" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="Q18" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R18" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S18" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T18" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.45">
@@ -2902,25 +2848,25 @@
         <v>50</v>
       </c>
       <c r="N19" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O19" t="s">
         <v>25</v>
       </c>
       <c r="P19" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="Q19" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R19" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S19" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T19" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.45">
@@ -2955,25 +2901,25 @@
         <v>59</v>
       </c>
       <c r="N20" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O20" t="s">
         <v>26</v>
       </c>
       <c r="P20" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="Q20" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R20" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S20" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T20" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.45">
@@ -3008,25 +2954,25 @@
         <v>50</v>
       </c>
       <c r="N21" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O21" t="s">
         <v>27</v>
       </c>
       <c r="P21" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="Q21" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R21" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S21" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T21" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.45">
@@ -3061,25 +3007,25 @@
         <v>68</v>
       </c>
       <c r="N22" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O22" t="s">
         <v>28</v>
       </c>
       <c r="P22" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="Q22" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R22" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S22" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T22" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.45">
@@ -3114,25 +3060,25 @@
         <v>40</v>
       </c>
       <c r="N23" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O23" t="s">
         <v>29</v>
       </c>
       <c r="P23" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="Q23" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R23" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S23" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T23" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.45">
@@ -3167,25 +3113,25 @@
         <v>40</v>
       </c>
       <c r="N24" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O24" t="s">
         <v>30</v>
       </c>
       <c r="P24" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="Q24" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R24" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S24" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T24" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.45">
@@ -3220,25 +3166,25 @@
         <v>40</v>
       </c>
       <c r="N25" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O25" t="s">
         <v>31</v>
       </c>
       <c r="P25" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="Q25" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R25" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S25" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T25" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.45">
@@ -3273,25 +3219,25 @@
         <v>40</v>
       </c>
       <c r="N26" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O26" t="s">
         <v>32</v>
       </c>
       <c r="P26" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="Q26" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R26" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S26" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T26" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.45">
@@ -3326,25 +3272,25 @@
         <v>40</v>
       </c>
       <c r="N27" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O27" t="s">
         <v>33</v>
       </c>
       <c r="P27" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="Q27" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R27" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S27" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T27" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.45">
@@ -3379,25 +3325,25 @@
         <v>40</v>
       </c>
       <c r="N28" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O28" t="s">
         <v>34</v>
       </c>
       <c r="P28" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="Q28" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R28" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S28" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T28" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.45">
@@ -3432,25 +3378,25 @@
         <v>40</v>
       </c>
       <c r="N29" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O29" t="s">
         <v>35</v>
       </c>
       <c r="P29" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="Q29" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R29" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S29" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T29" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.45">
@@ -3485,25 +3431,25 @@
         <v>50</v>
       </c>
       <c r="N30" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O30" t="s">
         <v>36</v>
       </c>
       <c r="P30" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="Q30" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R30" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S30" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T30" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.45">
@@ -3538,25 +3484,25 @@
         <v>55</v>
       </c>
       <c r="N31" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O31" t="s">
         <v>39</v>
       </c>
       <c r="P31" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="Q31" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R31" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S31" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T31" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" spans="2:20" x14ac:dyDescent="0.45">
@@ -3591,25 +3537,25 @@
         <v>50</v>
       </c>
       <c r="N32" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O32" t="s">
         <v>41</v>
       </c>
       <c r="P32" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="Q32" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R32" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S32" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T32" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33" spans="2:20" x14ac:dyDescent="0.45">
@@ -3644,25 +3590,25 @@
         <v>50</v>
       </c>
       <c r="N33" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O33" t="s">
         <v>43</v>
       </c>
       <c r="P33" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="Q33" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R33" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S33" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T33" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="2:20" x14ac:dyDescent="0.45">
@@ -3697,25 +3643,25 @@
         <v>50</v>
       </c>
       <c r="N34" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O34" t="s">
         <v>45</v>
       </c>
       <c r="P34" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="Q34" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R34" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S34" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T34" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.45">
@@ -3750,25 +3696,25 @@
         <v>66</v>
       </c>
       <c r="N35" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O35" t="s">
         <v>47</v>
       </c>
       <c r="P35" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="Q35" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R35" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S35" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T35" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36" spans="2:20" x14ac:dyDescent="0.45">
@@ -3803,25 +3749,25 @@
         <v>58</v>
       </c>
       <c r="N36" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O36" t="s">
         <v>49</v>
       </c>
       <c r="P36" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="Q36" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R36" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S36" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T36" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.45">
@@ -3856,25 +3802,25 @@
         <v>55</v>
       </c>
       <c r="N37" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O37" t="s">
         <v>51</v>
       </c>
       <c r="P37" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="Q37" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R37" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S37" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T37" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" spans="2:20" x14ac:dyDescent="0.45">
@@ -3909,25 +3855,25 @@
         <v>50</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O38" t="s">
         <v>52</v>
       </c>
       <c r="P38" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="Q38" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R38" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S38" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T38" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="39" spans="2:20" x14ac:dyDescent="0.45">
@@ -3962,25 +3908,25 @@
         <v>50</v>
       </c>
       <c r="N39" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O39" t="s">
         <v>54</v>
       </c>
       <c r="P39" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="Q39" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R39" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S39" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T39" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40" spans="2:20" x14ac:dyDescent="0.45">
@@ -4015,25 +3961,25 @@
         <v>50</v>
       </c>
       <c r="N40" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O40" t="s">
         <v>56</v>
       </c>
       <c r="P40" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="Q40" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R40" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S40" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T40" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="41" spans="2:20" x14ac:dyDescent="0.45">
@@ -4068,25 +4014,25 @@
         <v>73</v>
       </c>
       <c r="N41" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O41" t="s">
         <v>57</v>
       </c>
       <c r="P41" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="Q41" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R41" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S41" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T41" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" spans="2:20" x14ac:dyDescent="0.45">
@@ -4121,25 +4067,25 @@
         <v>73</v>
       </c>
       <c r="N42" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O42" t="s">
         <v>59</v>
       </c>
       <c r="P42" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="Q42" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R42" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S42" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T42" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="43" spans="2:20" x14ac:dyDescent="0.45">
@@ -4174,25 +4120,25 @@
         <v>73</v>
       </c>
       <c r="N43" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O43" t="s">
         <v>60</v>
       </c>
       <c r="P43" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="Q43" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R43" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S43" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T43" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.45">
@@ -4227,25 +4173,25 @@
         <v>50</v>
       </c>
       <c r="N44" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O44" t="s">
         <v>61</v>
       </c>
       <c r="P44" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="Q44" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R44" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S44" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T44" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="45" spans="2:20" x14ac:dyDescent="0.45">
@@ -4280,25 +4226,25 @@
         <v>50</v>
       </c>
       <c r="N45" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O45" t="s">
         <v>62</v>
       </c>
       <c r="P45" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="Q45" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R45" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S45" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T45" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="46" spans="2:20" x14ac:dyDescent="0.45">
@@ -4333,25 +4279,25 @@
         <v>50</v>
       </c>
       <c r="N46" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O46" t="s">
         <v>63</v>
       </c>
       <c r="P46" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="Q46" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R46" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S46" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T46" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="47" spans="2:20" x14ac:dyDescent="0.45">
@@ -4386,25 +4332,25 @@
         <v>50</v>
       </c>
       <c r="N47" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O47" t="s">
         <v>64</v>
       </c>
       <c r="P47" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="Q47" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R47" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S47" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T47" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" spans="2:20" x14ac:dyDescent="0.45">
@@ -4439,25 +4385,25 @@
         <v>50</v>
       </c>
       <c r="N48" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O48" t="s">
         <v>65</v>
       </c>
       <c r="P48" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="Q48" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R48" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S48" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T48" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49" spans="2:20" x14ac:dyDescent="0.45">
@@ -4492,25 +4438,25 @@
         <v>50</v>
       </c>
       <c r="N49" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O49" t="s">
         <v>66</v>
       </c>
       <c r="P49" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="Q49" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R49" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S49" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T49" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="50" spans="2:20" x14ac:dyDescent="0.45">
@@ -4545,25 +4491,25 @@
         <v>50</v>
       </c>
       <c r="N50" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O50" t="s">
         <v>67</v>
       </c>
       <c r="P50" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="Q50" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R50" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S50" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T50" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="51" spans="2:20" x14ac:dyDescent="0.45">
@@ -4598,25 +4544,25 @@
         <v>50</v>
       </c>
       <c r="N51" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O51" t="s">
         <v>68</v>
       </c>
       <c r="P51" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="Q51" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R51" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S51" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T51" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="52" spans="2:20" x14ac:dyDescent="0.45">
@@ -4651,25 +4597,25 @@
         <v>50</v>
       </c>
       <c r="N52" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O52" t="s">
         <v>69</v>
       </c>
       <c r="P52" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="Q52" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R52" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S52" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T52" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="53" spans="2:20" x14ac:dyDescent="0.45">
@@ -4704,25 +4650,25 @@
         <v>50</v>
       </c>
       <c r="N53" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O53" t="s">
         <v>70</v>
       </c>
       <c r="P53" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="Q53" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R53" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S53" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T53" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="54" spans="2:20" x14ac:dyDescent="0.45">
@@ -4757,25 +4703,25 @@
         <v>50</v>
       </c>
       <c r="N54" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O54" t="s">
         <v>71</v>
       </c>
       <c r="P54" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="Q54" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R54" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S54" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T54" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="55" spans="2:20" x14ac:dyDescent="0.45">
@@ -4810,25 +4756,25 @@
         <v>50</v>
       </c>
       <c r="N55" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O55" t="s">
         <v>72</v>
       </c>
       <c r="P55" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="Q55" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R55" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S55" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T55" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="56" spans="2:20" x14ac:dyDescent="0.45">
@@ -4863,25 +4809,25 @@
         <v>50</v>
       </c>
       <c r="N56" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O56" t="s">
         <v>73</v>
       </c>
       <c r="P56" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="Q56" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R56" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S56" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T56" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="57" spans="2:20" x14ac:dyDescent="0.45">
@@ -4916,25 +4862,25 @@
         <v>73</v>
       </c>
       <c r="N57" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O57" t="s">
         <v>74</v>
       </c>
       <c r="P57" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="Q57" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R57" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S57" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T57" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="58" spans="2:20" x14ac:dyDescent="0.45">
@@ -4969,25 +4915,25 @@
         <v>66</v>
       </c>
       <c r="N58" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O58" t="s">
         <v>75</v>
       </c>
       <c r="P58" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="Q58" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R58" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S58" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T58" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="59" spans="2:20" x14ac:dyDescent="0.45">
@@ -5022,25 +4968,25 @@
         <v>50</v>
       </c>
       <c r="N59" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O59" t="s">
         <v>76</v>
       </c>
       <c r="P59" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="Q59" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R59" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S59" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T59" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="60" spans="2:20" x14ac:dyDescent="0.45">
@@ -5075,25 +5021,25 @@
         <v>59</v>
       </c>
       <c r="N60" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O60" t="s">
         <v>77</v>
       </c>
       <c r="P60" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="Q60" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R60" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S60" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T60" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="61" spans="2:20" x14ac:dyDescent="0.45">
@@ -5110,43 +5056,43 @@
         <v>2022</v>
       </c>
       <c r="F61">
-        <v>0.16073697168649981</v>
+        <v>1.2898645876077145E-2</v>
       </c>
       <c r="G61">
         <v>1</v>
       </c>
       <c r="H61">
-        <v>2875</v>
+        <v>3375.0000000000005</v>
       </c>
       <c r="I61">
-        <v>55.000000000000014</v>
+        <v>65</v>
       </c>
       <c r="J61">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K61">
         <v>100</v>
       </c>
       <c r="N61" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O61" t="s">
         <v>77</v>
       </c>
       <c r="P61" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="Q61" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R61" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S61" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T61" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="62" spans="2:20" x14ac:dyDescent="0.45">
@@ -5163,7 +5109,7 @@
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>2.7120229790726307E-2</v>
+        <v>1.2237176856791137E-2</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -5175,31 +5121,31 @@
         <v>65</v>
       </c>
       <c r="J62">
-        <v>2.3999999999999995</v>
+        <v>2.4</v>
       </c>
       <c r="K62">
         <v>100</v>
       </c>
       <c r="N62" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O62" t="s">
         <v>77</v>
       </c>
       <c r="P62" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="Q62" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R62" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S62" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T62" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="63" spans="2:20" x14ac:dyDescent="0.45">
@@ -5216,7 +5162,7 @@
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>2.6458760771440295E-2</v>
+        <v>1.3229380385720147E-2</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -5234,25 +5180,25 @@
         <v>100</v>
       </c>
       <c r="N63" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O63" t="s">
         <v>77</v>
       </c>
       <c r="P63" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="Q63" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R63" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S63" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T63" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="64" spans="2:20" x14ac:dyDescent="0.45">
@@ -5269,7 +5215,7 @@
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>1.7363561756257695E-2</v>
+        <v>4.365695527287649E-2</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -5287,25 +5233,25 @@
         <v>100</v>
       </c>
       <c r="N64" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O64" t="s">
         <v>77</v>
       </c>
       <c r="P64" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="Q64" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R64" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S64" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T64" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="65" spans="2:20" x14ac:dyDescent="0.45">
@@ -5322,43 +5268,43 @@
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>7.1438654082888797E-2</v>
+        <v>1.9844070578580224E-2</v>
       </c>
       <c r="G65">
         <v>1</v>
       </c>
       <c r="H65">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I65">
-        <v>55.000000000000007</v>
+        <v>65</v>
       </c>
       <c r="J65">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K65">
         <v>100</v>
       </c>
       <c r="N65" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O65" t="s">
         <v>77</v>
       </c>
       <c r="P65" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="Q65" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R65" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S65" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T65" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="66" spans="2:20" x14ac:dyDescent="0.45">
@@ -5375,43 +5321,43 @@
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>1.2237176856791137E-2</v>
+        <v>0.16073697168649981</v>
       </c>
       <c r="G66">
         <v>1</v>
       </c>
       <c r="H66">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I66">
-        <v>65</v>
+        <v>55.000000000000014</v>
       </c>
       <c r="J66">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K66">
         <v>100</v>
       </c>
       <c r="N66" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O66" t="s">
         <v>77</v>
       </c>
       <c r="P66" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="Q66" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R66" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S66" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T66" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="67" spans="2:20" x14ac:dyDescent="0.45">
@@ -5422,49 +5368,49 @@
         <v>78</v>
       </c>
       <c r="D67" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="E67">
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>5.8209273697168655E-2</v>
+        <v>3.5057858022158397E-2</v>
       </c>
       <c r="G67">
         <v>1</v>
       </c>
       <c r="H67">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I67">
-        <v>55.000000000000007</v>
+        <v>65</v>
       </c>
       <c r="J67">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K67">
         <v>100</v>
       </c>
       <c r="N67" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O67" t="s">
         <v>77</v>
       </c>
       <c r="P67" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="Q67" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R67" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S67" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T67" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="68" spans="2:20" x14ac:dyDescent="0.45">
@@ -5475,49 +5421,49 @@
         <v>78</v>
       </c>
       <c r="D68" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E68">
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>1.7528929011079199E-2</v>
+        <v>5.291752154288059E-2</v>
       </c>
       <c r="G68">
         <v>1</v>
       </c>
       <c r="H68">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I68">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J68">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K68">
         <v>100</v>
       </c>
       <c r="N68" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O68" t="s">
         <v>77</v>
       </c>
       <c r="P68" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="Q68" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R68" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S68" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T68" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="69" spans="2:20" x14ac:dyDescent="0.45">
@@ -5528,49 +5474,49 @@
         <v>78</v>
       </c>
       <c r="D69" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E69">
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>3.5057858022158397E-2</v>
+        <v>8.9298317603610997E-2</v>
       </c>
       <c r="G69">
         <v>1</v>
       </c>
       <c r="H69">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I69">
-        <v>65</v>
+        <v>55.000000000000014</v>
       </c>
       <c r="J69">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K69">
         <v>100</v>
       </c>
       <c r="N69" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O69" t="s">
         <v>77</v>
       </c>
       <c r="P69" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="Q69" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R69" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S69" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T69" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="70" spans="2:20" x14ac:dyDescent="0.45">
@@ -5581,49 +5527,49 @@
         <v>78</v>
       </c>
       <c r="D70" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E70">
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>3.6380796060730414E-2</v>
+        <v>7.1438654082888797E-2</v>
       </c>
       <c r="G70">
         <v>1</v>
       </c>
       <c r="H70">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I70">
-        <v>65</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J70">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K70">
         <v>100</v>
       </c>
       <c r="N70" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O70" t="s">
         <v>77</v>
       </c>
       <c r="P70" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="Q70" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R70" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S70" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T70" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="71" spans="2:20" x14ac:dyDescent="0.45">
@@ -5634,49 +5580,49 @@
         <v>78</v>
       </c>
       <c r="D71" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="E71">
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>3.9688141157160448E-2</v>
+        <v>5.8209273697168655E-2</v>
       </c>
       <c r="G71">
         <v>1</v>
       </c>
       <c r="H71">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I71">
-        <v>65</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J71">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K71">
         <v>100</v>
       </c>
       <c r="N71" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O71" t="s">
         <v>77</v>
       </c>
       <c r="P71" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="Q71" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R71" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S71" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T71" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="72" spans="2:20" x14ac:dyDescent="0.45">
@@ -5693,7 +5639,7 @@
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>3.5057858022158397E-2</v>
+        <v>2.7120229790726307E-2</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -5705,31 +5651,31 @@
         <v>65</v>
       </c>
       <c r="J72">
-        <v>2.4</v>
+        <v>2.3999999999999995</v>
       </c>
       <c r="K72">
         <v>100</v>
       </c>
       <c r="N72" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O72" t="s">
         <v>77</v>
       </c>
       <c r="P72" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="Q72" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R72" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S72" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T72" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="73" spans="2:20" x14ac:dyDescent="0.45">
@@ -5746,7 +5692,7 @@
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>1.9844070578580224E-2</v>
+        <v>2.1001641362330736E-2</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -5764,25 +5710,25 @@
         <v>100</v>
       </c>
       <c r="N73" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O73" t="s">
         <v>77</v>
       </c>
       <c r="P73" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="Q73" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R73" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S73" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T73" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="74" spans="2:20" x14ac:dyDescent="0.45">
@@ -5799,7 +5745,7 @@
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>1.3229380385720147E-2</v>
+        <v>1.7528929011079199E-2</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -5817,25 +5763,25 @@
         <v>100</v>
       </c>
       <c r="N74" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O74" t="s">
         <v>77</v>
       </c>
       <c r="P74" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="Q74" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R74" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S74" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T74" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="75" spans="2:20" x14ac:dyDescent="0.45">
@@ -5852,7 +5798,7 @@
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>4.365695527287649E-2</v>
+        <v>3.5057858022158397E-2</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -5870,25 +5816,25 @@
         <v>100</v>
       </c>
       <c r="N75" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O75" t="s">
         <v>77</v>
       </c>
       <c r="P75" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="Q75" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R75" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S75" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T75" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="76" spans="2:20" x14ac:dyDescent="0.45">
@@ -5905,43 +5851,43 @@
         <v>2022</v>
       </c>
       <c r="F76">
-        <v>5.291752154288059E-2</v>
+        <v>2.6458760771440295E-2</v>
       </c>
       <c r="G76">
         <v>1</v>
       </c>
       <c r="H76">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I76">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="J76">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K76">
         <v>100</v>
       </c>
       <c r="N76" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O76" t="s">
         <v>77</v>
       </c>
       <c r="P76" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="Q76" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R76" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S76" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T76" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="77" spans="2:20" x14ac:dyDescent="0.45">
@@ -5958,43 +5904,43 @@
         <v>2022</v>
       </c>
       <c r="F77">
-        <v>8.9298317603610997E-2</v>
+        <v>1.7363561756257695E-2</v>
       </c>
       <c r="G77">
         <v>1</v>
       </c>
       <c r="H77">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I77">
-        <v>55.000000000000014</v>
+        <v>65</v>
       </c>
       <c r="J77">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K77">
         <v>100</v>
       </c>
       <c r="N77" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O77" t="s">
         <v>77</v>
       </c>
       <c r="P77" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="Q77" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R77" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S77" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T77" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="78" spans="2:20" x14ac:dyDescent="0.45">
@@ -6011,7 +5957,7 @@
         <v>2022</v>
       </c>
       <c r="F78">
-        <v>1.5875256462864178E-2</v>
+        <v>3.9688141157160448E-2</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -6029,25 +5975,25 @@
         <v>100</v>
       </c>
       <c r="N78" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O78" t="s">
         <v>77</v>
       </c>
       <c r="P78" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="Q78" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R78" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S78" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T78" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="79" spans="2:20" x14ac:dyDescent="0.45">
@@ -6064,7 +6010,7 @@
         <v>2022</v>
       </c>
       <c r="F79">
-        <v>2.1001641362330736E-2</v>
+        <v>1.5875256462864178E-2</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -6082,25 +6028,25 @@
         <v>100</v>
       </c>
       <c r="N79" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O79" t="s">
         <v>77</v>
       </c>
       <c r="P79" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="Q79" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R79" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S79" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T79" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="80" spans="2:20" x14ac:dyDescent="0.45">
@@ -6117,13 +6063,13 @@
         <v>2022</v>
       </c>
       <c r="F80">
-        <v>1.2898645876077145E-2</v>
+        <v>3.6380796060730414E-2</v>
       </c>
       <c r="G80">
         <v>1</v>
       </c>
       <c r="H80">
-        <v>3375.0000000000005</v>
+        <v>3375</v>
       </c>
       <c r="I80">
         <v>65</v>
@@ -6135,25 +6081,25 @@
         <v>100</v>
       </c>
       <c r="N80" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O80" t="s">
         <v>98</v>
       </c>
       <c r="P80" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="Q80" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R80" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S80" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T80" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="81" spans="2:20" x14ac:dyDescent="0.45">
@@ -6164,7 +6110,7 @@
         <v>78</v>
       </c>
       <c r="D81" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="E81">
         <v>1929</v>
@@ -6188,25 +6134,25 @@
         <v>126</v>
       </c>
       <c r="N81" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O81" t="s">
         <v>99</v>
       </c>
       <c r="P81" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="Q81" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R81" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S81" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T81" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="82" spans="2:20" x14ac:dyDescent="0.45">
@@ -6217,7 +6163,7 @@
         <v>78</v>
       </c>
       <c r="D82" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="E82">
         <v>1968</v>
@@ -6241,25 +6187,25 @@
         <v>100</v>
       </c>
       <c r="N82" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O82" t="s">
         <v>100</v>
       </c>
       <c r="P82" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="Q82" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R82" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S82" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T82" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="83" spans="2:20" x14ac:dyDescent="0.45">
@@ -6270,7 +6216,7 @@
         <v>78</v>
       </c>
       <c r="D83" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E83">
         <v>1965</v>
@@ -6294,25 +6240,25 @@
         <v>100</v>
       </c>
       <c r="N83" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O83" t="s">
         <v>101</v>
       </c>
       <c r="P83" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="Q83" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R83" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S83" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T83" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="84" spans="2:20" x14ac:dyDescent="0.45">
@@ -6323,7 +6269,7 @@
         <v>78</v>
       </c>
       <c r="D84" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E84">
         <v>1992</v>
@@ -6347,25 +6293,25 @@
         <v>100</v>
       </c>
       <c r="N84" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O84" t="s">
         <v>102</v>
       </c>
       <c r="P84" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="Q84" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R84" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S84" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T84" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="85" spans="2:20" x14ac:dyDescent="0.45">
@@ -6376,7 +6322,7 @@
         <v>78</v>
       </c>
       <c r="D85" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E85">
         <v>1948</v>
@@ -6400,25 +6346,25 @@
         <v>107</v>
       </c>
       <c r="N85" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O85" t="s">
         <v>103</v>
       </c>
       <c r="P85" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="Q85" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R85" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S85" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T85" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="86" spans="2:20" x14ac:dyDescent="0.45">
@@ -6429,7 +6375,7 @@
         <v>78</v>
       </c>
       <c r="D86" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E86">
         <v>1972</v>
@@ -6453,25 +6399,25 @@
         <v>100</v>
       </c>
       <c r="N86" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O86" t="s">
         <v>104</v>
       </c>
       <c r="P86" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="Q86" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R86" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S86" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T86" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="87" spans="2:20" x14ac:dyDescent="0.45">
@@ -6506,25 +6452,25 @@
         <v>103</v>
       </c>
       <c r="N87" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O87" t="s">
         <v>105</v>
       </c>
       <c r="P87" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="Q87" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R87" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S87" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T87" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="88" spans="2:20" x14ac:dyDescent="0.45">
@@ -6559,25 +6505,25 @@
         <v>100</v>
       </c>
       <c r="N88" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O88" t="s">
         <v>106</v>
       </c>
       <c r="P88" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="Q88" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R88" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S88" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T88" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="89" spans="2:20" x14ac:dyDescent="0.45">
@@ -6588,7 +6534,7 @@
         <v>78</v>
       </c>
       <c r="D89" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E89">
         <v>1961</v>
@@ -6612,25 +6558,25 @@
         <v>100</v>
       </c>
       <c r="N89" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O89" t="s">
         <v>107</v>
       </c>
       <c r="P89" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="Q89" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R89" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S89" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T89" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="90" spans="2:20" x14ac:dyDescent="0.45">
@@ -6641,7 +6587,7 @@
         <v>78</v>
       </c>
       <c r="D90" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E90">
         <v>1979</v>
@@ -6665,25 +6611,25 @@
         <v>100</v>
       </c>
       <c r="N90" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O90" t="s">
         <v>108</v>
       </c>
       <c r="P90" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="Q90" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R90" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S90" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T90" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="91" spans="2:20" x14ac:dyDescent="0.45">
@@ -6694,7 +6640,7 @@
         <v>78</v>
       </c>
       <c r="D91" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E91">
         <v>1984</v>
@@ -6718,25 +6664,25 @@
         <v>100</v>
       </c>
       <c r="N91" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O91" t="s">
         <v>109</v>
       </c>
       <c r="P91" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="Q91" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R91" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S91" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T91" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="92" spans="2:20" x14ac:dyDescent="0.45">
@@ -6747,7 +6693,7 @@
         <v>78</v>
       </c>
       <c r="D92" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E92">
         <v>1985</v>
@@ -6771,25 +6717,25 @@
         <v>100</v>
       </c>
       <c r="N92" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O92" t="s">
         <v>110</v>
       </c>
       <c r="P92" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="Q92" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R92" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S92" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T92" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="93" spans="2:20" x14ac:dyDescent="0.45">
@@ -6800,7 +6746,7 @@
         <v>78</v>
       </c>
       <c r="D93" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E93">
         <v>1983</v>
@@ -6824,25 +6770,25 @@
         <v>100</v>
       </c>
       <c r="N93" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O93" t="s">
         <v>111</v>
       </c>
       <c r="P93" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="Q93" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R93" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S93" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T93" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="94" spans="2:20" x14ac:dyDescent="0.45">
@@ -6853,7 +6799,7 @@
         <v>78</v>
       </c>
       <c r="D94" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E94">
         <v>1956</v>
@@ -6877,25 +6823,25 @@
         <v>100</v>
       </c>
       <c r="N94" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O94" t="s">
         <v>112</v>
       </c>
       <c r="P94" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="Q94" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R94" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S94" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T94" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="95" spans="2:20" x14ac:dyDescent="0.45">
@@ -6906,7 +6852,7 @@
         <v>78</v>
       </c>
       <c r="D95" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="E95">
         <v>1977</v>
@@ -6930,25 +6876,25 @@
         <v>100</v>
       </c>
       <c r="N95" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O95" t="s">
         <v>113</v>
       </c>
       <c r="P95" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="Q95" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R95" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S95" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T95" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="96" spans="2:20" x14ac:dyDescent="0.45">
@@ -6959,7 +6905,7 @@
         <v>78</v>
       </c>
       <c r="D96" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="E96">
         <v>1973</v>
@@ -6983,25 +6929,25 @@
         <v>100</v>
       </c>
       <c r="N96" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O96" t="s">
         <v>114</v>
       </c>
       <c r="P96" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="Q96" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R96" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S96" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T96" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="97" spans="2:20" x14ac:dyDescent="0.45">
@@ -7012,7 +6958,7 @@
         <v>78</v>
       </c>
       <c r="D97" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="E97">
         <v>1935</v>
@@ -7036,25 +6982,25 @@
         <v>120</v>
       </c>
       <c r="N97" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O97" t="s">
         <v>115</v>
       </c>
       <c r="P97" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="Q97" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R97" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S97" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T97" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="98" spans="2:20" x14ac:dyDescent="0.45">
@@ -7065,7 +7011,7 @@
         <v>78</v>
       </c>
       <c r="D98" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E98">
         <v>1956</v>
@@ -7089,25 +7035,25 @@
         <v>100</v>
       </c>
       <c r="N98" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O98" t="s">
         <v>116</v>
       </c>
       <c r="P98" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="Q98" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R98" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S98" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T98" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="99" spans="2:20" x14ac:dyDescent="0.45">
@@ -7118,7 +7064,7 @@
         <v>78</v>
       </c>
       <c r="D99" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="E99">
         <v>1967</v>
@@ -7142,25 +7088,25 @@
         <v>100</v>
       </c>
       <c r="N99" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O99" t="s">
         <v>117</v>
       </c>
       <c r="P99" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="Q99" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R99" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S99" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T99" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="100" spans="2:20" x14ac:dyDescent="0.45">
@@ -7171,7 +7117,7 @@
         <v>78</v>
       </c>
       <c r="D100" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E100">
         <v>1958</v>
@@ -7195,25 +7141,25 @@
         <v>100</v>
       </c>
       <c r="N100" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O100" t="s">
         <v>118</v>
       </c>
       <c r="P100" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="Q100" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R100" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S100" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T100" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="101" spans="2:20" x14ac:dyDescent="0.45">
@@ -7248,25 +7194,25 @@
         <v>126</v>
       </c>
       <c r="N101" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O101" t="s">
         <v>120</v>
       </c>
       <c r="P101" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="Q101" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R101" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S101" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T101" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="102" spans="2:20" x14ac:dyDescent="0.45">
@@ -7301,25 +7247,25 @@
         <v>100</v>
       </c>
       <c r="N102" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O102" t="s">
         <v>122</v>
       </c>
       <c r="P102" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="Q102" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R102" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S102" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T102" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="103" spans="2:20" x14ac:dyDescent="0.45">
@@ -7330,7 +7276,7 @@
         <v>78</v>
       </c>
       <c r="D103" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="E103">
         <v>1964</v>
@@ -7354,25 +7300,25 @@
         <v>100</v>
       </c>
       <c r="N103" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O103" t="s">
         <v>123</v>
       </c>
       <c r="P103" t="s">
-        <v>278</v>
+        <v>260</v>
       </c>
       <c r="Q103" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R103" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S103" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="T103" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="104" spans="2:20" x14ac:dyDescent="0.45">
@@ -7407,25 +7353,25 @@
         <v>100</v>
       </c>
       <c r="N104" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O104" t="s">
         <v>125</v>
       </c>
       <c r="P104" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="Q104" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R104" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S104" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="T104" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="105" spans="2:20" x14ac:dyDescent="0.45">
@@ -7442,7 +7388,7 @@
         <v>2022</v>
       </c>
       <c r="F105">
-        <v>8.3726904507382155E-2</v>
+        <v>8.5012321189937637E-2</v>
       </c>
       <c r="G105">
         <v>1</v>
@@ -7463,154 +7409,154 @@
         <v>0.1910967417235313</v>
       </c>
       <c r="N105" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O105" t="s">
         <v>128</v>
       </c>
       <c r="P105" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="Q105" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R105" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S105" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="T105" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="106" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B106" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C106" t="s">
         <v>126</v>
       </c>
       <c r="D106" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E106">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F106">
-        <v>5.1999999999999998E-2</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="G106">
         <v>1</v>
       </c>
       <c r="H106">
-        <v>1035</v>
+        <v>1215</v>
       </c>
       <c r="I106">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="J106">
         <v>0</v>
       </c>
       <c r="K106">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L106">
-        <v>0.1767456226726275</v>
+        <v>0.18218348485866612</v>
       </c>
       <c r="N106" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O106" t="s">
         <v>130</v>
       </c>
       <c r="P106" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="Q106" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R106" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S106" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="T106" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="107" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B107" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C107" t="s">
         <v>126</v>
       </c>
       <c r="D107" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E107">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="F107">
-        <v>0.17</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="G107">
         <v>1</v>
       </c>
       <c r="H107">
-        <v>1035</v>
+        <v>1215</v>
       </c>
       <c r="I107">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="J107">
         <v>0</v>
       </c>
       <c r="K107">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L107">
-        <v>0.18349581246367919</v>
+        <v>0.1868255198840435</v>
       </c>
       <c r="N107" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O107" t="s">
         <v>132</v>
       </c>
       <c r="P107" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="Q107" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R107" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S107" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="T107" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="108" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B108" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C108" t="s">
         <v>126</v>
       </c>
       <c r="D108" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E108">
-        <v>2028</v>
+        <v>2023</v>
       </c>
       <c r="F108">
-        <v>4.9000000000000002E-2</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G108">
         <v>1</v>
@@ -7625,48 +7571,48 @@
         <v>0</v>
       </c>
       <c r="K108">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L108">
-        <v>0.17721048910943363</v>
+        <v>0.20333316960890149</v>
       </c>
       <c r="N108" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O108" t="s">
         <v>134</v>
       </c>
       <c r="P108" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="Q108" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R108" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S108" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="T108" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="109" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B109" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C109" t="s">
         <v>126</v>
       </c>
       <c r="D109" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E109">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="F109">
-        <v>3.9E-2</v>
+        <v>2.0799999999999999E-2</v>
       </c>
       <c r="G109">
         <v>1</v>
@@ -7681,48 +7627,48 @@
         <v>0</v>
       </c>
       <c r="K109">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L109">
-        <v>0.20333316960890149</v>
+        <v>0.20333316960890147</v>
       </c>
       <c r="N109" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O109" t="s">
         <v>136</v>
       </c>
       <c r="P109" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="Q109" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R109" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S109" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="T109" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="110" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B110" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C110" t="s">
         <v>126</v>
       </c>
       <c r="D110" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E110">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="F110">
-        <v>2.0799999999999999E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="G110">
         <v>1</v>
@@ -7740,45 +7686,45 @@
         <v>30</v>
       </c>
       <c r="L110">
-        <v>0.20333316960890147</v>
+        <v>0.20333316960890149</v>
       </c>
       <c r="N110" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O110" t="s">
         <v>138</v>
       </c>
       <c r="P110" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="Q110" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R110" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S110" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="T110" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="111" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B111" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C111" t="s">
         <v>126</v>
       </c>
       <c r="D111" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E111">
-        <v>2028</v>
+        <v>2015</v>
       </c>
       <c r="F111">
-        <v>2.4E-2</v>
+        <v>1.4E-3</v>
       </c>
       <c r="G111">
         <v>1</v>
@@ -7793,104 +7739,104 @@
         <v>0</v>
       </c>
       <c r="K111">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L111">
-        <v>0.20333316960890149</v>
+        <v>0.19281073694608941</v>
       </c>
       <c r="N111" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O111" t="s">
         <v>140</v>
       </c>
       <c r="P111" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="Q111" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R111" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S111" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="T111" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="112" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B112" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C112" t="s">
         <v>126</v>
       </c>
       <c r="D112" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E112">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="F112">
-        <v>2.5000000000000001E-3</v>
+        <v>8.5460774302680204E-2</v>
       </c>
       <c r="G112">
         <v>1</v>
       </c>
       <c r="H112">
-        <v>1215</v>
+        <v>1035</v>
       </c>
       <c r="I112">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="J112">
         <v>0</v>
       </c>
       <c r="K112">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L112">
-        <v>0.18888135654523</v>
+        <v>0.1910967417235313</v>
       </c>
       <c r="N112" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O112" t="s">
         <v>142</v>
       </c>
       <c r="P112" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="Q112" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R112" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S112" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="T112" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="113" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B113" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C113" t="s">
         <v>126</v>
       </c>
       <c r="D113" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="E113">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="F113">
-        <v>1.9E-3</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="G113">
         <v>1</v>
@@ -7905,104 +7851,104 @@
         <v>0</v>
       </c>
       <c r="K113">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L113">
-        <v>0.19504090243261779</v>
+        <v>0.19996746694328421</v>
       </c>
       <c r="N113" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O113" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P113" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="Q113" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R113" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S113" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="T113" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="114" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B114" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C114" t="s">
         <v>126</v>
       </c>
       <c r="D114" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="E114">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F114">
-        <v>8.5460774302680204E-2</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="G114">
         <v>1</v>
       </c>
       <c r="H114">
-        <v>1035</v>
+        <v>1215</v>
       </c>
       <c r="I114">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="J114">
         <v>0</v>
       </c>
       <c r="K114">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L114">
-        <v>0.1910967417235313</v>
+        <v>0.18888135654523</v>
       </c>
       <c r="N114" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O114" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P114" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="Q114" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R114" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S114" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="T114" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="115" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B115" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C115" t="s">
         <v>126</v>
       </c>
       <c r="D115" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="E115">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="F115">
-        <v>1.4E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="G115">
         <v>1</v>
@@ -8017,104 +7963,104 @@
         <v>0</v>
       </c>
       <c r="K115">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L115">
-        <v>0.19281073694608941</v>
+        <v>0.19504090243261779</v>
       </c>
       <c r="N115" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O115" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P115" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="Q115" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R115" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S115" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="T115" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="116" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B116" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C116" t="s">
         <v>126</v>
       </c>
       <c r="D116" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="E116">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="F116">
-        <v>3.6999999999999998E-2</v>
+        <v>8.3726904507382155E-2</v>
       </c>
       <c r="G116">
         <v>1</v>
       </c>
       <c r="H116">
-        <v>1215</v>
+        <v>1035</v>
       </c>
       <c r="I116">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="J116">
         <v>0</v>
       </c>
       <c r="K116">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L116">
-        <v>0.19996746694328421</v>
+        <v>0.1910967417235313</v>
       </c>
       <c r="N116" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O116" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P116" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="Q116" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R116" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S116" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="T116" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="117" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B117" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C117" t="s">
         <v>126</v>
       </c>
       <c r="D117" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E117">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F117">
-        <v>8.5012321189937637E-2</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="G117">
         <v>1</v>
@@ -8129,104 +8075,104 @@
         <v>0</v>
       </c>
       <c r="K117">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L117">
-        <v>0.1910967417235313</v>
+        <v>0.1767456226726275</v>
       </c>
       <c r="N117" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O117" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P117" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="Q117" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R117" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S117" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="T117" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="118" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B118" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C118" t="s">
         <v>126</v>
       </c>
       <c r="D118" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="E118">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="F118">
-        <v>3.5000000000000003E-2</v>
+        <v>0.17</v>
       </c>
       <c r="G118">
         <v>1</v>
       </c>
       <c r="H118">
-        <v>1215</v>
+        <v>1035</v>
       </c>
       <c r="I118">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="J118">
         <v>0</v>
       </c>
       <c r="K118">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L118">
-        <v>0.1868255198840435</v>
+        <v>0.18349581246367919</v>
       </c>
       <c r="N118" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O118" t="s">
         <v>155</v>
       </c>
       <c r="P118" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="Q118" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R118" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S118" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="T118" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="119" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B119" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="C119" t="s">
         <v>126</v>
       </c>
       <c r="D119" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="E119">
-        <v>2023</v>
+        <v>2028</v>
       </c>
       <c r="F119">
-        <v>3.0999999999999999E-3</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="G119">
         <v>1</v>
@@ -8241,42 +8187,21 @@
         <v>0</v>
       </c>
       <c r="K119">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L119">
-        <v>0.18218348485866612</v>
-      </c>
-      <c r="N119" t="s">
-        <v>182</v>
-      </c>
-      <c r="O119" t="s">
-        <v>157</v>
-      </c>
-      <c r="P119" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q119" t="s">
-        <v>184</v>
-      </c>
-      <c r="R119" t="s">
-        <v>185</v>
-      </c>
-      <c r="S119" t="s">
-        <v>279</v>
-      </c>
-      <c r="T119" t="s">
-        <v>187</v>
+        <v>0.17721048910943363</v>
       </c>
     </row>
     <row r="120" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B120" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="C120" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D120" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="E120">
         <v>2022</v>
@@ -8288,393 +8213,225 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L120">
-        <v>0.41172044122569984</v>
-      </c>
-      <c r="N120" t="s">
-        <v>182</v>
-      </c>
-      <c r="O120" t="s">
-        <v>159</v>
-      </c>
-      <c r="P120" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q120" t="s">
-        <v>184</v>
-      </c>
-      <c r="R120" t="s">
-        <v>185</v>
-      </c>
-      <c r="S120" t="s">
-        <v>279</v>
-      </c>
-      <c r="T120" t="s">
-        <v>187</v>
+        <v>0.40791539999667453</v>
       </c>
     </row>
     <row r="121" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B121" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C121" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D121" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="E121">
-        <v>2022</v>
+        <v>2009</v>
       </c>
       <c r="F121">
-        <v>2.8327438797566478E-2</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="G121">
         <v>0.33123000000000002</v>
       </c>
       <c r="L121">
-        <v>0.41172044122569984</v>
-      </c>
-      <c r="N121" t="s">
-        <v>182</v>
-      </c>
-      <c r="O121" t="s">
-        <v>161</v>
-      </c>
-      <c r="P121" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q121" t="s">
-        <v>184</v>
-      </c>
-      <c r="R121" t="s">
-        <v>185</v>
-      </c>
-      <c r="S121" t="s">
-        <v>279</v>
-      </c>
-      <c r="T121" t="s">
-        <v>187</v>
+        <v>0.5665247689951628</v>
       </c>
     </row>
     <row r="122" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B122" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C122" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D122" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="E122">
-        <v>2007</v>
+        <v>2014</v>
       </c>
       <c r="F122">
-        <v>5.8000000000000003E-2</v>
+        <v>0.06</v>
       </c>
       <c r="G122">
         <v>0.33123000000000002</v>
       </c>
       <c r="L122">
-        <v>0.29996245639681474</v>
-      </c>
-      <c r="N122" t="s">
-        <v>182</v>
-      </c>
-      <c r="O122" t="s">
-        <v>163</v>
-      </c>
-      <c r="P122" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q122" t="s">
-        <v>184</v>
-      </c>
-      <c r="R122" t="s">
-        <v>185</v>
-      </c>
-      <c r="S122" t="s">
-        <v>279</v>
-      </c>
-      <c r="T122" t="s">
-        <v>187</v>
+        <v>0.5665247689951628</v>
       </c>
     </row>
     <row r="123" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B123" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="C123" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D123" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="E123">
-        <v>2023</v>
+        <v>1999</v>
       </c>
       <c r="F123">
-        <v>4.2999999999999997E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="G123">
         <v>0.33123000000000002</v>
       </c>
       <c r="L123">
-        <v>0.43764790128670528</v>
-      </c>
-      <c r="N123" t="s">
-        <v>182</v>
-      </c>
-      <c r="O123" t="s">
-        <v>165</v>
-      </c>
-      <c r="P123" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q123" t="s">
-        <v>184</v>
-      </c>
-      <c r="R123" t="s">
-        <v>185</v>
-      </c>
-      <c r="S123" t="s">
-        <v>279</v>
-      </c>
-      <c r="T123" t="s">
-        <v>187</v>
+        <v>0.40395409929757359</v>
       </c>
     </row>
     <row r="124" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B124" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="C124" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D124" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="E124">
-        <v>2027</v>
+        <v>2004</v>
       </c>
       <c r="F124">
-        <v>0.155</v>
+        <v>0.127</v>
       </c>
       <c r="G124">
         <v>0.33123000000000002</v>
       </c>
       <c r="L124">
-        <v>0.43764790128670528</v>
-      </c>
-      <c r="N124" t="s">
-        <v>182</v>
-      </c>
-      <c r="O124" t="s">
-        <v>167</v>
-      </c>
-      <c r="P124" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q124" t="s">
-        <v>184</v>
-      </c>
-      <c r="R124" t="s">
-        <v>185</v>
-      </c>
-      <c r="S124" t="s">
-        <v>279</v>
-      </c>
-      <c r="T124" t="s">
-        <v>187</v>
+        <v>0.40395409929757359</v>
       </c>
     </row>
     <row r="125" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B125" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="C125" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D125" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="E125">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="F125">
-        <v>3.5999999999999997E-2</v>
+        <v>9.2999999999999999E-2</v>
       </c>
       <c r="G125">
         <v>0.33123000000000002</v>
       </c>
       <c r="L125">
-        <v>0.30750940020437478</v>
-      </c>
-      <c r="N125" t="s">
-        <v>182</v>
-      </c>
-      <c r="O125" t="s">
-        <v>169</v>
-      </c>
-      <c r="P125" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q125" t="s">
-        <v>184</v>
-      </c>
-      <c r="R125" t="s">
-        <v>185</v>
-      </c>
-      <c r="S125" t="s">
-        <v>279</v>
-      </c>
-      <c r="T125" t="s">
-        <v>187</v>
+        <v>0.40395409929757353</v>
       </c>
     </row>
     <row r="126" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B126" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="C126" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D126" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="E126">
         <v>2009</v>
       </c>
       <c r="F126">
-        <v>0.14299999999999999</v>
+        <v>0.03</v>
       </c>
       <c r="G126">
         <v>0.33123000000000002</v>
       </c>
       <c r="L126">
-        <v>0.5665247689951628</v>
-      </c>
-      <c r="N126" t="s">
-        <v>182</v>
-      </c>
-      <c r="O126" t="s">
-        <v>171</v>
-      </c>
-      <c r="P126" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q126" t="s">
-        <v>184</v>
-      </c>
-      <c r="R126" t="s">
-        <v>185</v>
-      </c>
-      <c r="S126" t="s">
-        <v>279</v>
-      </c>
-      <c r="T126" t="s">
-        <v>187</v>
+        <v>0.40395409929757359</v>
       </c>
     </row>
     <row r="127" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B127" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="C127" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D127" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="E127">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="F127">
-        <v>0.06</v>
+        <v>1.6E-2</v>
       </c>
       <c r="G127">
         <v>0.33123000000000002</v>
       </c>
       <c r="L127">
-        <v>0.5665247689951628</v>
-      </c>
-      <c r="N127" t="s">
-        <v>182</v>
-      </c>
-      <c r="O127" t="s">
-        <v>173</v>
-      </c>
-      <c r="P127" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q127" t="s">
-        <v>184</v>
-      </c>
-      <c r="R127" t="s">
-        <v>185</v>
-      </c>
-      <c r="S127" t="s">
-        <v>279</v>
-      </c>
-      <c r="T127" t="s">
-        <v>187</v>
+        <v>0.40395409929757359</v>
       </c>
     </row>
     <row r="128" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B128" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="C128" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D128" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="E128">
         <v>2021</v>
       </c>
       <c r="F128">
-        <v>0.13300000000000001</v>
+        <v>0.252</v>
       </c>
       <c r="G128">
         <v>0.33123000000000002</v>
       </c>
       <c r="L128">
-        <v>0.51800914605060178</v>
+        <v>0.4739763845441875</v>
       </c>
     </row>
     <row r="129" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B129" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="C129" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D129" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="E129">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="F129">
-        <v>0.11899999999999999</v>
+        <v>2.7221455883173235E-2</v>
       </c>
       <c r="G129">
         <v>0.33123000000000002</v>
       </c>
       <c r="L129">
-        <v>0.42476329815466568</v>
+        <v>0.40791539999667453</v>
       </c>
     </row>
     <row r="130" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B130" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="C130" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D130" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="E130">
         <v>2023</v>
@@ -8691,13 +8448,13 @@
     </row>
     <row r="131" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B131" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="C131" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D131" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="E131">
         <v>2011</v>
@@ -8714,163 +8471,140 @@
     </row>
     <row r="132" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B132" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="C132" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D132" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="E132">
-        <v>1999</v>
+        <v>2024</v>
       </c>
       <c r="F132">
-        <v>3.2000000000000001E-2</v>
+        <v>0.17599999999999999</v>
       </c>
       <c r="G132">
         <v>0.33123000000000002</v>
       </c>
       <c r="L132">
-        <v>0.40395409929757359</v>
+        <v>0.28243194746500749</v>
       </c>
     </row>
     <row r="133" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B133" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="C133" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D133" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="E133">
-        <v>2004</v>
+        <v>2011</v>
       </c>
       <c r="F133">
-        <v>0.127</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="G133">
         <v>0.33123000000000002</v>
       </c>
       <c r="L133">
-        <v>0.40395409929757359</v>
+        <v>0.30750940020437478</v>
       </c>
     </row>
     <row r="134" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B134" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="C134" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D134" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="E134">
         <v>2007</v>
       </c>
       <c r="F134">
-        <v>9.2999999999999999E-2</v>
+        <v>5.8000000000000003E-2</v>
       </c>
       <c r="G134">
         <v>0.33123000000000002</v>
       </c>
       <c r="L134">
-        <v>0.40395409929757353</v>
+        <v>0.29996245639681474</v>
       </c>
     </row>
     <row r="135" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B135" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="C135" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D135" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="E135">
-        <v>2009</v>
+        <v>2022</v>
       </c>
       <c r="F135">
-        <v>0.03</v>
+        <v>2.8327438797566478E-2</v>
       </c>
       <c r="G135">
         <v>0.33123000000000002</v>
       </c>
       <c r="L135">
-        <v>0.40395409929757359</v>
+        <v>0.40791539999667453</v>
       </c>
     </row>
     <row r="136" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B136" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="C136" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D136" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="E136">
-        <v>2011</v>
+        <v>2023</v>
       </c>
       <c r="F136">
-        <v>1.6E-2</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="G136">
         <v>0.33123000000000002</v>
       </c>
       <c r="L136">
-        <v>0.40395409929757359</v>
+        <v>0.43764790128670528</v>
       </c>
     </row>
     <row r="137" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B137" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="C137" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D137" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="E137">
-        <v>2022</v>
+        <v>2027</v>
       </c>
       <c r="F137">
-        <v>2.7221455883173235E-2</v>
+        <v>0.155</v>
       </c>
       <c r="G137">
         <v>0.33123000000000002</v>
       </c>
       <c r="L137">
-        <v>0.41172044122569984</v>
-      </c>
-    </row>
-    <row r="138" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B138" t="s">
-        <v>173</v>
-      </c>
-      <c r="C138" t="s">
-        <v>153</v>
-      </c>
-      <c r="D138" t="s">
-        <v>174</v>
-      </c>
-      <c r="E138">
-        <v>2024</v>
-      </c>
-      <c r="F138">
-        <v>0.17599999999999999</v>
-      </c>
-      <c r="G138">
-        <v>0.33123000000000002</v>
-      </c>
-      <c r="L138">
-        <v>0.28243194746500749</v>
+        <v>0.43764790128670528</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_NZL_grids/vt_vervestacks_NZL_v1.xlsx
+++ b/VerveStacks_NZL_grids/vt_vervestacks_NZL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{44AAD9E9-4A63-48F8-A834-2E5CD277BDAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E56E1724-7127-4D36-9437-C0AF4C362248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2940" windowWidth="21600" windowHeight="12682" xr2:uid="{C89B5F03-8170-4862-9780-52D30BF45DF2}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{7F0C3FA2-7296-4EA1-A29C-64BE412F87DF}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -279,60 +279,60 @@
     <t>e_w270018358-220</t>
   </si>
   <si>
+    <t>e_w89637173-220</t>
+  </si>
+  <si>
+    <t>e_NZ13-220</t>
+  </si>
+  <si>
+    <t>e_NZ33-220</t>
+  </si>
+  <si>
+    <t>e_NZ12-220</t>
+  </si>
+  <si>
     <t>e_w93556808-220</t>
   </si>
   <si>
-    <t>e_NZ13-220</t>
-  </si>
-  <si>
-    <t>e_NZ33-220</t>
+    <t>e_w89664063-220</t>
+  </si>
+  <si>
+    <t>e_NZ11-220</t>
+  </si>
+  <si>
+    <t>e_NZ35-220</t>
+  </si>
+  <si>
+    <t>e_NZ14-220</t>
+  </si>
+  <si>
+    <t>e_w272522517-220</t>
+  </si>
+  <si>
+    <t>e_w89636266-220</t>
+  </si>
+  <si>
+    <t>e_w89637174-220</t>
+  </si>
+  <si>
+    <t>e_NZ40-220</t>
+  </si>
+  <si>
+    <t>e_w89411122-220</t>
+  </si>
+  <si>
+    <t>e_NZ30-220</t>
   </si>
   <si>
     <t>e_NZ22-220</t>
   </si>
   <si>
+    <t>e_w180514007-220</t>
+  </si>
+  <si>
     <t>e_w412589726-220</t>
   </si>
   <si>
-    <t>e_NZ35-220</t>
-  </si>
-  <si>
-    <t>e_w180514007-220</t>
-  </si>
-  <si>
-    <t>e_w89664063-220</t>
-  </si>
-  <si>
-    <t>e_NZ40-220</t>
-  </si>
-  <si>
-    <t>e_NZ12-220</t>
-  </si>
-  <si>
-    <t>e_NZ14-220</t>
-  </si>
-  <si>
-    <t>e_w272522517-220</t>
-  </si>
-  <si>
-    <t>e_w89636266-220</t>
-  </si>
-  <si>
-    <t>e_NZ30-220</t>
-  </si>
-  <si>
-    <t>e_w89637173-220</t>
-  </si>
-  <si>
-    <t>e_w89411122-220</t>
-  </si>
-  <si>
-    <t>e_NZ11-220</t>
-  </si>
-  <si>
-    <t>e_w89637174-220</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000602849</t>
   </si>
   <si>
@@ -690,66 +690,66 @@
     <t>Wairakei geothermal power plant_A</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - NZ11-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ22-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/180514007-220_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/89637174-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ30-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89637173-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/272522517-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ33-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/93556808-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89411122-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89664063-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/412589726-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ35-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ14-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ40-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/270018358-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/87928925-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - NZ12-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/89411122-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89664063-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89637174-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ30-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/87928925-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ40-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ14-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/270018358-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ35-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89637173-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/272522517-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ33-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ11-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/412589726-220_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - way/89636266-220_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - NZ13-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - NZ22-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89636266-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/93556808-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Arapuni hydroelectric plant_</t>
   </si>
   <si>
@@ -900,13 +900,13 @@
     <t>ccs retrofit of -- Glenbrook power station_1</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/188180344-220_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - relation/17609399-220_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/167293888-220_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/188180344-220_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- McKee power station_2</t>
@@ -1298,7 +1298,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F12542B-9072-4BBC-A849-6F448F15ED35}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA2276F-6712-44E6-BC65-80EB1D503AEA}">
   <dimension ref="B9:T27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2324,7 +2324,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFA3FB72-804A-4A8D-83E1-8329E12C2E67}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DBD113F-6069-4187-8851-69C3821306A9}">
   <dimension ref="B9:T137"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5109,7 +5109,7 @@
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>1.2237176856791137E-2</v>
+        <v>1.7363561756257695E-2</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -5156,25 +5156,25 @@
         <v>78</v>
       </c>
       <c r="D63" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="E63">
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>1.3229380385720147E-2</v>
+        <v>5.8209273697168655E-2</v>
       </c>
       <c r="G63">
         <v>1</v>
       </c>
       <c r="H63">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I63">
-        <v>65</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J63">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K63">
         <v>100</v>
@@ -5209,13 +5209,13 @@
         <v>78</v>
       </c>
       <c r="D64" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E64">
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>4.365695527287649E-2</v>
+        <v>1.3229380385720147E-2</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -5262,13 +5262,13 @@
         <v>78</v>
       </c>
       <c r="D65" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E65">
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>1.9844070578580224E-2</v>
+        <v>4.365695527287649E-2</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -5315,25 +5315,25 @@
         <v>78</v>
       </c>
       <c r="D66" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E66">
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>0.16073697168649981</v>
+        <v>2.7120229790726307E-2</v>
       </c>
       <c r="G66">
         <v>1</v>
       </c>
       <c r="H66">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I66">
-        <v>55.000000000000014</v>
+        <v>65</v>
       </c>
       <c r="J66">
-        <v>2.2000000000000002</v>
+        <v>2.3999999999999995</v>
       </c>
       <c r="K66">
         <v>100</v>
@@ -5368,13 +5368,13 @@
         <v>78</v>
       </c>
       <c r="D67" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E67">
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>3.5057858022158397E-2</v>
+        <v>1.2237176856791137E-2</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -5421,13 +5421,13 @@
         <v>78</v>
       </c>
       <c r="D68" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E68">
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>5.291752154288059E-2</v>
+        <v>8.9298317603610997E-2</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -5436,7 +5436,7 @@
         <v>2875</v>
       </c>
       <c r="I68">
-        <v>55</v>
+        <v>55.000000000000014</v>
       </c>
       <c r="J68">
         <v>2.2000000000000002</v>
@@ -5474,25 +5474,25 @@
         <v>78</v>
       </c>
       <c r="D69" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E69">
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>8.9298317603610997E-2</v>
+        <v>1.5875256462864178E-2</v>
       </c>
       <c r="G69">
         <v>1</v>
       </c>
       <c r="H69">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I69">
-        <v>55.000000000000014</v>
+        <v>65</v>
       </c>
       <c r="J69">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K69">
         <v>100</v>
@@ -5527,25 +5527,25 @@
         <v>78</v>
       </c>
       <c r="D70" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E70">
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>7.1438654082888797E-2</v>
+        <v>3.5057858022158397E-2</v>
       </c>
       <c r="G70">
         <v>1</v>
       </c>
       <c r="H70">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I70">
-        <v>55.000000000000007</v>
+        <v>65</v>
       </c>
       <c r="J70">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K70">
         <v>100</v>
@@ -5580,25 +5580,25 @@
         <v>78</v>
       </c>
       <c r="D71" t="s">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="E71">
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>5.8209273697168655E-2</v>
+        <v>2.1001641362330736E-2</v>
       </c>
       <c r="G71">
         <v>1</v>
       </c>
       <c r="H71">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I71">
-        <v>55.000000000000007</v>
+        <v>65</v>
       </c>
       <c r="J71">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K71">
         <v>100</v>
@@ -5639,7 +5639,7 @@
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>2.7120229790726307E-2</v>
+        <v>1.7528929011079199E-2</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -5651,7 +5651,7 @@
         <v>65</v>
       </c>
       <c r="J72">
-        <v>2.3999999999999995</v>
+        <v>2.4</v>
       </c>
       <c r="K72">
         <v>100</v>
@@ -5692,7 +5692,7 @@
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>2.1001641362330736E-2</v>
+        <v>3.5057858022158397E-2</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -5745,7 +5745,7 @@
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>1.7528929011079199E-2</v>
+        <v>3.6380796060730414E-2</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -5798,19 +5798,19 @@
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>3.5057858022158397E-2</v>
+        <v>7.1438654082888797E-2</v>
       </c>
       <c r="G75">
         <v>1</v>
       </c>
       <c r="H75">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I75">
-        <v>65</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J75">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K75">
         <v>100</v>
@@ -5851,7 +5851,7 @@
         <v>2022</v>
       </c>
       <c r="F76">
-        <v>2.6458760771440295E-2</v>
+        <v>3.9688141157160448E-2</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -5904,7 +5904,7 @@
         <v>2022</v>
       </c>
       <c r="F77">
-        <v>1.7363561756257695E-2</v>
+        <v>2.6458760771440295E-2</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -5957,7 +5957,7 @@
         <v>2022</v>
       </c>
       <c r="F78">
-        <v>3.9688141157160448E-2</v>
+        <v>1.9844070578580224E-2</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -6010,19 +6010,19 @@
         <v>2022</v>
       </c>
       <c r="F79">
-        <v>1.5875256462864178E-2</v>
+        <v>5.291752154288059E-2</v>
       </c>
       <c r="G79">
         <v>1</v>
       </c>
       <c r="H79">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I79">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J79">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K79">
         <v>100</v>
@@ -6063,19 +6063,19 @@
         <v>2022</v>
       </c>
       <c r="F80">
-        <v>3.6380796060730414E-2</v>
+        <v>0.16073697168649981</v>
       </c>
       <c r="G80">
         <v>1</v>
       </c>
       <c r="H80">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I80">
-        <v>65</v>
+        <v>55.000000000000014</v>
       </c>
       <c r="J80">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K80">
         <v>100</v>
@@ -6110,7 +6110,7 @@
         <v>78</v>
       </c>
       <c r="D81" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E81">
         <v>1929</v>
@@ -6163,7 +6163,7 @@
         <v>78</v>
       </c>
       <c r="D82" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E82">
         <v>1968</v>
@@ -6216,7 +6216,7 @@
         <v>78</v>
       </c>
       <c r="D83" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E83">
         <v>1965</v>
@@ -6269,7 +6269,7 @@
         <v>78</v>
       </c>
       <c r="D84" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E84">
         <v>1992</v>
@@ -6322,7 +6322,7 @@
         <v>78</v>
       </c>
       <c r="D85" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E85">
         <v>1948</v>
@@ -6375,7 +6375,7 @@
         <v>78</v>
       </c>
       <c r="D86" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="E86">
         <v>1972</v>
@@ -6534,7 +6534,7 @@
         <v>78</v>
       </c>
       <c r="D89" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E89">
         <v>1961</v>
@@ -6640,7 +6640,7 @@
         <v>78</v>
       </c>
       <c r="D91" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E91">
         <v>1984</v>
@@ -6693,7 +6693,7 @@
         <v>78</v>
       </c>
       <c r="D92" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E92">
         <v>1985</v>
@@ -6746,7 +6746,7 @@
         <v>78</v>
       </c>
       <c r="D93" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="E93">
         <v>1983</v>
@@ -6799,7 +6799,7 @@
         <v>78</v>
       </c>
       <c r="D94" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E94">
         <v>1956</v>
@@ -6852,7 +6852,7 @@
         <v>78</v>
       </c>
       <c r="D95" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E95">
         <v>1977</v>
@@ -6905,7 +6905,7 @@
         <v>78</v>
       </c>
       <c r="D96" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E96">
         <v>1973</v>
@@ -6958,7 +6958,7 @@
         <v>78</v>
       </c>
       <c r="D97" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="E97">
         <v>1935</v>
@@ -7011,7 +7011,7 @@
         <v>78</v>
       </c>
       <c r="D98" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E98">
         <v>1956</v>
@@ -7117,7 +7117,7 @@
         <v>78</v>
       </c>
       <c r="D100" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E100">
         <v>1958</v>

--- a/VerveStacks_NZL_grids/vt_vervestacks_NZL_v1.xlsx
+++ b/VerveStacks_NZL_grids/vt_vervestacks_NZL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E56E1724-7127-4D36-9437-C0AF4C362248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5AD43D4F-3EF4-4B4B-9140-789AAA07EFC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{7F0C3FA2-7296-4EA1-A29C-64BE412F87DF}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{682BA2C7-1A05-4773-A614-9941F5E3667E}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -276,63 +276,63 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_w89411122-220</t>
+  </si>
+  <si>
+    <t>e_w180514007-220</t>
+  </si>
+  <si>
+    <t>e_w89636266-220</t>
+  </si>
+  <si>
+    <t>e_w89637174-220</t>
+  </si>
+  <si>
+    <t>e_w93556808-220</t>
+  </si>
+  <si>
+    <t>e_NZ13-220</t>
+  </si>
+  <si>
+    <t>e_NZ11-220</t>
+  </si>
+  <si>
+    <t>e_NZ35-220</t>
+  </si>
+  <si>
+    <t>e_NZ30-220</t>
+  </si>
+  <si>
+    <t>e_w89637173-220</t>
+  </si>
+  <si>
+    <t>e_NZ33-220</t>
+  </si>
+  <si>
+    <t>e_NZ22-220</t>
+  </si>
+  <si>
     <t>e_w270018358-220</t>
   </si>
   <si>
-    <t>e_w89637173-220</t>
-  </si>
-  <si>
-    <t>e_NZ13-220</t>
-  </si>
-  <si>
-    <t>e_NZ33-220</t>
-  </si>
-  <si>
     <t>e_NZ12-220</t>
   </si>
   <si>
-    <t>e_w93556808-220</t>
+    <t>e_NZ14-220</t>
+  </si>
+  <si>
+    <t>e_w412589726-220</t>
+  </si>
+  <si>
+    <t>e_NZ40-220</t>
   </si>
   <si>
     <t>e_w89664063-220</t>
   </si>
   <si>
-    <t>e_NZ11-220</t>
-  </si>
-  <si>
-    <t>e_NZ35-220</t>
-  </si>
-  <si>
-    <t>e_NZ14-220</t>
-  </si>
-  <si>
     <t>e_w272522517-220</t>
   </si>
   <si>
-    <t>e_w89636266-220</t>
-  </si>
-  <si>
-    <t>e_w89637174-220</t>
-  </si>
-  <si>
-    <t>e_NZ40-220</t>
-  </si>
-  <si>
-    <t>e_w89411122-220</t>
-  </si>
-  <si>
-    <t>e_NZ30-220</t>
-  </si>
-  <si>
-    <t>e_NZ22-220</t>
-  </si>
-  <si>
-    <t>e_w180514007-220</t>
-  </si>
-  <si>
-    <t>e_w412589726-220</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000602849</t>
   </si>
   <si>
@@ -690,61 +690,61 @@
     <t>Wairakei geothermal power plant_A</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - NZ30-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/87928925-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89637173-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ33-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/412589726-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89664063-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89411122-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/180514007-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89637174-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/93556808-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ22-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ12-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89636266-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/272522517-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ40-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - NZ35-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/270018358-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - NZ11-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - NZ22-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/180514007-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89637174-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ30-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89637173-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/272522517-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ33-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/93556808-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89411122-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89664063-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/412589726-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ35-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - NZ14-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ40-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/270018358-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/87928925-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - NZ12-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89636266-220_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - NZ13-220_Missing Hydro Capacity</t>
@@ -1298,7 +1298,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA2276F-6712-44E6-BC65-80EB1D503AEA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86F60C3E-4B2F-4F26-A2AF-EEE91F5CE5CB}">
   <dimension ref="B9:T27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2324,7 +2324,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DBD113F-6069-4187-8851-69C3821306A9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3C3ADCA-1B63-4610-BCEF-F26AA71CDA5C}">
   <dimension ref="B9:T137"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5056,13 +5056,13 @@
         <v>2022</v>
       </c>
       <c r="F61">
-        <v>1.2898645876077145E-2</v>
+        <v>3.9688141157160448E-2</v>
       </c>
       <c r="G61">
         <v>1</v>
       </c>
       <c r="H61">
-        <v>3375.0000000000005</v>
+        <v>3375</v>
       </c>
       <c r="I61">
         <v>65</v>
@@ -5109,19 +5109,19 @@
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>1.7363561756257695E-2</v>
+        <v>5.291752154288059E-2</v>
       </c>
       <c r="G62">
         <v>1</v>
       </c>
       <c r="H62">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I62">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J62">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K62">
         <v>100</v>
@@ -5156,25 +5156,25 @@
         <v>78</v>
       </c>
       <c r="D63" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="E63">
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>5.8209273697168655E-2</v>
+        <v>3.5057858022158397E-2</v>
       </c>
       <c r="G63">
         <v>1</v>
       </c>
       <c r="H63">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I63">
-        <v>55.000000000000007</v>
+        <v>65</v>
       </c>
       <c r="J63">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K63">
         <v>100</v>
@@ -5209,13 +5209,13 @@
         <v>78</v>
       </c>
       <c r="D64" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E64">
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>1.3229380385720147E-2</v>
+        <v>3.6380796060730414E-2</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -5262,13 +5262,13 @@
         <v>78</v>
       </c>
       <c r="D65" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E65">
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>4.365695527287649E-2</v>
+        <v>1.2237176856791137E-2</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -5315,13 +5315,13 @@
         <v>78</v>
       </c>
       <c r="D66" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E66">
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>2.7120229790726307E-2</v>
+        <v>1.3229380385720147E-2</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -5333,7 +5333,7 @@
         <v>65</v>
       </c>
       <c r="J66">
-        <v>2.3999999999999995</v>
+        <v>2.4</v>
       </c>
       <c r="K66">
         <v>100</v>
@@ -5368,13 +5368,13 @@
         <v>78</v>
       </c>
       <c r="D67" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E67">
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>1.2237176856791137E-2</v>
+        <v>1.5875256462864178E-2</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -5421,25 +5421,25 @@
         <v>78</v>
       </c>
       <c r="D68" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E68">
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>8.9298317603610997E-2</v>
+        <v>3.5057858022158397E-2</v>
       </c>
       <c r="G68">
         <v>1</v>
       </c>
       <c r="H68">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I68">
-        <v>55.000000000000014</v>
+        <v>65</v>
       </c>
       <c r="J68">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K68">
         <v>100</v>
@@ -5474,13 +5474,13 @@
         <v>78</v>
       </c>
       <c r="D69" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E69">
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>1.5875256462864178E-2</v>
+        <v>2.6458760771440295E-2</v>
       </c>
       <c r="G69">
         <v>1</v>
@@ -5527,13 +5527,13 @@
         <v>78</v>
       </c>
       <c r="D70" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E70">
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>3.5057858022158397E-2</v>
+        <v>1.7363561756257695E-2</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -5580,13 +5580,13 @@
         <v>78</v>
       </c>
       <c r="D71" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E71">
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>2.1001641362330736E-2</v>
+        <v>4.365695527287649E-2</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -5633,13 +5633,13 @@
         <v>78</v>
       </c>
       <c r="D72" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E72">
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>1.7528929011079199E-2</v>
+        <v>1.9844070578580224E-2</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -5686,19 +5686,19 @@
         <v>78</v>
       </c>
       <c r="D73" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E73">
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>3.5057858022158397E-2</v>
+        <v>1.2898645876077145E-2</v>
       </c>
       <c r="G73">
         <v>1</v>
       </c>
       <c r="H73">
-        <v>3375</v>
+        <v>3375.0000000000005</v>
       </c>
       <c r="I73">
         <v>65</v>
@@ -5739,13 +5739,13 @@
         <v>78</v>
       </c>
       <c r="D74" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E74">
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>3.6380796060730414E-2</v>
+        <v>2.7120229790726307E-2</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -5757,7 +5757,7 @@
         <v>65</v>
       </c>
       <c r="J74">
-        <v>2.4</v>
+        <v>2.3999999999999995</v>
       </c>
       <c r="K74">
         <v>100</v>
@@ -5792,25 +5792,25 @@
         <v>78</v>
       </c>
       <c r="D75" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E75">
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>7.1438654082888797E-2</v>
+        <v>2.1001641362330736E-2</v>
       </c>
       <c r="G75">
         <v>1</v>
       </c>
       <c r="H75">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I75">
-        <v>55.000000000000007</v>
+        <v>65</v>
       </c>
       <c r="J75">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K75">
         <v>100</v>
@@ -5845,25 +5845,25 @@
         <v>78</v>
       </c>
       <c r="D76" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E76">
         <v>2022</v>
       </c>
       <c r="F76">
-        <v>3.9688141157160448E-2</v>
+        <v>0.16073697168649981</v>
       </c>
       <c r="G76">
         <v>1</v>
       </c>
       <c r="H76">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I76">
-        <v>65</v>
+        <v>55.000000000000014</v>
       </c>
       <c r="J76">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K76">
         <v>100</v>
@@ -5898,25 +5898,25 @@
         <v>78</v>
       </c>
       <c r="D77" t="s">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="E77">
         <v>2022</v>
       </c>
       <c r="F77">
-        <v>2.6458760771440295E-2</v>
+        <v>5.8209273697168655E-2</v>
       </c>
       <c r="G77">
         <v>1</v>
       </c>
       <c r="H77">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I77">
-        <v>65</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J77">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K77">
         <v>100</v>
@@ -5957,19 +5957,19 @@
         <v>2022</v>
       </c>
       <c r="F78">
-        <v>1.9844070578580224E-2</v>
+        <v>7.1438654082888797E-2</v>
       </c>
       <c r="G78">
         <v>1</v>
       </c>
       <c r="H78">
-        <v>3375</v>
+        <v>2875</v>
       </c>
       <c r="I78">
-        <v>65</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J78">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K78">
         <v>100</v>
@@ -6010,7 +6010,7 @@
         <v>2022</v>
       </c>
       <c r="F79">
-        <v>5.291752154288059E-2</v>
+        <v>8.9298317603610997E-2</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -6019,7 +6019,7 @@
         <v>2875</v>
       </c>
       <c r="I79">
-        <v>55</v>
+        <v>55.000000000000014</v>
       </c>
       <c r="J79">
         <v>2.2000000000000002</v>
@@ -6063,19 +6063,19 @@
         <v>2022</v>
       </c>
       <c r="F80">
-        <v>0.16073697168649981</v>
+        <v>1.7528929011079199E-2</v>
       </c>
       <c r="G80">
         <v>1</v>
       </c>
       <c r="H80">
-        <v>2875</v>
+        <v>3375</v>
       </c>
       <c r="I80">
-        <v>55.000000000000014</v>
+        <v>65</v>
       </c>
       <c r="J80">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="K80">
         <v>100</v>
@@ -6110,7 +6110,7 @@
         <v>78</v>
       </c>
       <c r="D81" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="E81">
         <v>1929</v>
@@ -6163,7 +6163,7 @@
         <v>78</v>
       </c>
       <c r="D82" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E82">
         <v>1968</v>
@@ -6216,7 +6216,7 @@
         <v>78</v>
       </c>
       <c r="D83" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E83">
         <v>1965</v>
@@ -6269,7 +6269,7 @@
         <v>78</v>
       </c>
       <c r="D84" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E84">
         <v>1992</v>
@@ -6322,7 +6322,7 @@
         <v>78</v>
       </c>
       <c r="D85" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E85">
         <v>1948</v>
@@ -6375,7 +6375,7 @@
         <v>78</v>
       </c>
       <c r="D86" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E86">
         <v>1972</v>
@@ -6534,7 +6534,7 @@
         <v>78</v>
       </c>
       <c r="D89" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="E89">
         <v>1961</v>
@@ -6587,7 +6587,7 @@
         <v>78</v>
       </c>
       <c r="D90" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="E90">
         <v>1979</v>
@@ -6640,7 +6640,7 @@
         <v>78</v>
       </c>
       <c r="D91" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E91">
         <v>1984</v>
@@ -6693,7 +6693,7 @@
         <v>78</v>
       </c>
       <c r="D92" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="E92">
         <v>1985</v>
@@ -6746,7 +6746,7 @@
         <v>78</v>
       </c>
       <c r="D93" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E93">
         <v>1983</v>
@@ -6799,7 +6799,7 @@
         <v>78</v>
       </c>
       <c r="D94" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="E94">
         <v>1956</v>
@@ -6852,7 +6852,7 @@
         <v>78</v>
       </c>
       <c r="D95" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E95">
         <v>1977</v>
@@ -6905,7 +6905,7 @@
         <v>78</v>
       </c>
       <c r="D96" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="E96">
         <v>1973</v>
@@ -6958,7 +6958,7 @@
         <v>78</v>
       </c>
       <c r="D97" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E97">
         <v>1935</v>
@@ -7011,7 +7011,7 @@
         <v>78</v>
       </c>
       <c r="D98" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E98">
         <v>1956</v>
@@ -7064,7 +7064,7 @@
         <v>78</v>
       </c>
       <c r="D99" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E99">
         <v>1967</v>
@@ -7117,7 +7117,7 @@
         <v>78</v>
       </c>
       <c r="D100" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E100">
         <v>1958</v>
@@ -7276,7 +7276,7 @@
         <v>78</v>
       </c>
       <c r="D103" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="E103">
         <v>1964</v>
@@ -8213,7 +8213,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L120">
-        <v>0.40791539999667453</v>
+        <v>0.40791539999667442</v>
       </c>
     </row>
     <row r="121" spans="2:20" x14ac:dyDescent="0.45">
@@ -8420,7 +8420,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L129">
-        <v>0.40791539999667453</v>
+        <v>0.40791539999667442</v>
       </c>
     </row>
     <row r="130" spans="2:12" x14ac:dyDescent="0.45">
@@ -8558,7 +8558,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L135">
-        <v>0.40791539999667453</v>
+        <v>0.40791539999667442</v>
       </c>
     </row>
     <row r="136" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_NZL_grids/vt_vervestacks_NZL_v1.xlsx
+++ b/VerveStacks_NZL_grids/vt_vervestacks_NZL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E5D2C2B-50C7-4AB9-BF7C-9D901CF98BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{83E06EF9-0126-4468-A08B-8FF9A9FEDAFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4B9C2A2B-69F9-4FAC-AD6B-6210EE6D74DD}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{16BB6A0B-CA1A-4643-A595-7B47B2AFB646}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -971,7 +971,7 @@
     <t>windoff</t>
   </si>
   <si>
-    <t>elc_wof_030</t>
+    <t>elc_wof_021</t>
   </si>
   <si>
     <t>en_a_windoff_wind_G100000921456</t>
@@ -1729,7 +1729,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EEC1E24-1392-4288-9BB1-B5C26D14821F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A17C96E-9B93-4F97-839F-637F60E1B8BA}">
   <dimension ref="B9:T34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3147,7 +3147,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D68A9EB-C782-40BD-BAB5-F17EB804F93D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D28903D-DAAF-4C1B-8CB5-9C7BAC8D0874}">
   <dimension ref="B9:T66"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6297,7 +6297,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14802F05-E485-4036-813F-DF87832C6F65}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB55E4C3-B83F-4E11-BD59-9819D1821C6C}">
   <dimension ref="B9:T139"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11185,7 +11185,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L107">
-        <v>0.18061797552648504</v>
+        <v>0.18061797552648506</v>
       </c>
       <c r="N107" t="s">
         <v>191</v>
@@ -11229,7 +11229,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L108">
-        <v>0.18061797552648504</v>
+        <v>0.18061797552648506</v>
       </c>
       <c r="N108" t="s">
         <v>191</v>
@@ -11273,7 +11273,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L109">
-        <v>0.18061797552648504</v>
+        <v>0.18061797552648506</v>
       </c>
       <c r="N109" t="s">
         <v>191</v>
@@ -11989,7 +11989,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L122">
-        <v>0.35036392604929723</v>
+        <v>0.35036392604929728</v>
       </c>
       <c r="N122" t="s">
         <v>191</v>
@@ -12033,7 +12033,7 @@
         <v>0.33122999999999997</v>
       </c>
       <c r="L123">
-        <v>0.35036392604929723</v>
+        <v>0.35036392604929728</v>
       </c>
       <c r="N123" t="s">
         <v>191</v>
@@ -12077,7 +12077,7 @@
         <v>0.33123000000000008</v>
       </c>
       <c r="L124">
-        <v>0.35036392604929723</v>
+        <v>0.35036392604929728</v>
       </c>
       <c r="N124" t="s">
         <v>191</v>
@@ -12254,7 +12254,7 @@
         <v>183</v>
       </c>
       <c r="P127" t="s">
-        <v>291</v>
+        <v>192</v>
       </c>
       <c r="Q127" t="s">
         <v>193</v>
@@ -12310,7 +12310,7 @@
         <v>183</v>
       </c>
       <c r="P128" t="s">
-        <v>192</v>
+        <v>291</v>
       </c>
       <c r="Q128" t="s">
         <v>193</v>
@@ -12716,7 +12716,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC24323D-E99B-4142-AF91-D9D8FE84F2F8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38DA4678-28DF-430D-B8CB-9387EC1EDE2E}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
